--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>1.55</v>
       </c>
       <c r="M10" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
-        <v>1.5</v>
+        <v>7.2</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1743,7 +1743,7 @@
         <v>2.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.55</v>
+        <v>5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="N11" t="n">
-        <v>7.2</v>
+        <v>1.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
         <v>2.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
         <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M16" t="n">
         <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>4.05</v>
+        <v>3.35</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,16 +2643,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="N18" t="n">
-        <v>3.9</v>
+        <v>3.19</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="M22" t="n">
-        <v>3.42</v>
+        <v>3.9</v>
       </c>
       <c r="N22" t="n">
-        <v>3.19</v>
+        <v>3.6</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,16 +3288,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>3.01</v>
       </c>
       <c r="N37" t="n">
-        <v>2.85</v>
+        <v>3.26</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,16 +2643,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="N21" t="n">
-        <v>3.9</v>
+        <v>3.19</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,14 +3249,14 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="M22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N22" t="n">
         <v>3.9</v>
       </c>
-      <c r="N22" t="n">
-        <v>3.6</v>
-      </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
@@ -3288,16 +3288,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="M37" t="n">
-        <v>3.01</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>3.26</v>
+        <v>2.85</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="M39" t="n">
-        <v>3.5</v>
+        <v>3.01</v>
       </c>
       <c r="N39" t="n">
-        <v>2.85</v>
+        <v>3.26</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Z39" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5</v>
+        <v>1.55</v>
       </c>
       <c r="M11" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>1.5</v>
+        <v>7.2</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
         <v>2.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M15" t="n">
         <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>4.05</v>
+        <v>3.35</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
         <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,16 +2643,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="M19" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="N19" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,16 +2901,16 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N22" t="n">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.72</v>
+        <v>2.85</v>
       </c>
       <c r="M34" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N34" t="n">
-        <v>4.9</v>
+        <v>2.55</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
         <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M16" t="n">
         <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>4.05</v>
+        <v>3.35</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,16 +2772,16 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,14 +2862,14 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="M19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N19" t="n">
         <v>3.9</v>
       </c>
-      <c r="N19" t="n">
-        <v>3.6</v>
-      </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
@@ -2901,16 +2901,16 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="N20" t="n">
-        <v>3.9</v>
+        <v>3.19</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>1.55</v>
       </c>
       <c r="M9" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>1.5</v>
+        <v>7.2</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1614,7 +1614,7 @@
         <v>2.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.55</v>
+        <v>5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="N11" t="n">
-        <v>7.2</v>
+        <v>1.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1872,7 +1872,7 @@
         <v>2.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M15" t="n">
         <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>4.05</v>
+        <v>3.35</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
         <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.95</v>
+        <v>5.9</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="N19" t="n">
-        <v>3.9</v>
+        <v>1.47</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="M20" t="n">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="N20" t="n">
-        <v>3.19</v>
+        <v>4.05</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,49 +3378,49 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z23" t="n">
         <v>1.85</v>
-      </c>
-      <c r="M23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.97</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4443,16 +4443,16 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5616,10 +5616,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5829,10 +5829,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="M42" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
         <v>2.65</v>
@@ -5871,7 +5871,7 @@
         <v>2.25</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="M43" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="N43" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45950.375</v>
+        <v>45950.29166666666</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45950.38541666666</v>
+        <v>45950.33333333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45950.45833333334</v>
+        <v>45950.375</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45950.47916666666</v>
+        <v>45950.38541666666</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45950.5</v>
+        <v>45950.41666666666</v>
       </c>
     </row>
     <row r="10">
@@ -1660,27 +1660,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45950.5</v>
+        <v>45950.45833333334</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45950.5</v>
+        <v>45950.47916666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.25</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>3.45</v>
+        <v>7.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,16 +1992,16 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45950.52083333334</v>
+        <v>45950.47916666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45950.54166666666</v>
+        <v>45950.5</v>
       </c>
     </row>
     <row r="14">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45950.54166666666</v>
+        <v>45950.5</v>
       </c>
     </row>
     <row r="15">
@@ -2305,27 +2305,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2379,10 +2379,10 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45950.5625</v>
+        <v>45950.5</v>
       </c>
     </row>
     <row r="16">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N16" t="n">
-        <v>4.05</v>
+        <v>3.45</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45950.5625</v>
+        <v>45950.52083333334</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45950.58333333334</v>
+        <v>45950.54166666666</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.6</v>
+        <v>4.05</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2766,22 +2766,22 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45950.58333333334</v>
+        <v>45950.5625</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.9</v>
+        <v>2.25</v>
       </c>
       <c r="M19" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>1.47</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2895,16 +2895,16 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45950.58333333334</v>
+        <v>45950.5625</v>
       </c>
     </row>
     <row r="20">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="M20" t="n">
-        <v>3.7</v>
+        <v>3.36</v>
       </c>
       <c r="N20" t="n">
-        <v>4.05</v>
+        <v>3.67</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.97</v>
+        <v>1.76</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,16 +3159,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="N23" t="n">
-        <v>3.9</v>
+        <v>3.19</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3466,27 +3466,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.7</v>
+        <v>5.4</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>3.99</v>
       </c>
       <c r="N24" t="n">
-        <v>2.55</v>
+        <v>1.46</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45950.59027777778</v>
+        <v>45950.58333333334</v>
       </c>
     </row>
     <row r="25">
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.15</v>
+        <v>1.84</v>
       </c>
       <c r="M25" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N25" t="n">
-        <v>1.98</v>
+        <v>3.63</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45950.60416666666</v>
+        <v>45950.58333333334</v>
       </c>
     </row>
     <row r="26">
@@ -3724,27 +3724,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45950.625</v>
+        <v>45950.59027777778</v>
       </c>
     </row>
     <row r="27">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45950.625</v>
+        <v>45950.60416666666</v>
       </c>
     </row>
     <row r="28">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4443,16 +4443,16 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45950.64583333334</v>
+        <v>45950.625</v>
       </c>
     </row>
     <row r="32">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4572,16 +4572,16 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45950.65625</v>
+        <v>45950.64583333334</v>
       </c>
     </row>
     <row r="35">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.85</v>
+        <v>1.67</v>
       </c>
       <c r="M36" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>2.55</v>
+        <v>4.33</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.41</v>
+        <v>2.88</v>
       </c>
       <c r="M37" t="n">
-        <v>3.01</v>
+        <v>3.1</v>
       </c>
       <c r="N37" t="n">
-        <v>3.26</v>
+        <v>2.49</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45950.66666666666</v>
+        <v>45950.65625</v>
       </c>
     </row>
     <row r="38">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="M38" t="n">
-        <v>3.5</v>
+        <v>3.01</v>
       </c>
       <c r="N38" t="n">
-        <v>2.85</v>
+        <v>3.26</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="M41" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="N41" t="n">
-        <v>3.7</v>
+        <v>3.53</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.65</v>
+        <v>2.51</v>
       </c>
       <c r="M42" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="N42" t="n">
-        <v>2.65</v>
+        <v>2.51</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.55</v>
+        <v>5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="N13" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2130,7 +2130,7 @@
         <v>2.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5</v>
+        <v>1.55</v>
       </c>
       <c r="M14" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2259,7 +2259,7 @@
         <v>2.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M18" t="n">
         <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>4.05</v>
+        <v>3.35</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
         <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="M20" t="n">
-        <v>3.36</v>
+        <v>3.69</v>
       </c>
       <c r="N20" t="n">
-        <v>3.67</v>
+        <v>3.89</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,16 +3030,16 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.94</v>
+        <v>1.57</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.69</v>
+        <v>5.4</v>
       </c>
       <c r="M21" t="n">
-        <v>3.69</v>
+        <v>3.99</v>
       </c>
       <c r="N21" t="n">
-        <v>3.89</v>
+        <v>1.46</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,16 +3159,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.25</v>
+        <v>1.82</v>
       </c>
       <c r="M23" t="n">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="N23" t="n">
-        <v>3.19</v>
+        <v>3.67</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5.4</v>
+        <v>2.25</v>
       </c>
       <c r="M24" t="n">
-        <v>3.99</v>
+        <v>3.42</v>
       </c>
       <c r="N24" t="n">
-        <v>1.46</v>
+        <v>3.19</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4572,16 +4572,16 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4701,16 +4701,16 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.88</v>
+        <v>1.67</v>
       </c>
       <c r="M37" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="N37" t="n">
-        <v>2.49</v>
+        <v>4.33</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.01</v>
+        <v>2.51</v>
       </c>
       <c r="M41" t="n">
-        <v>2.94</v>
+        <v>3.09</v>
       </c>
       <c r="N41" t="n">
-        <v>3.53</v>
+        <v>2.51</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5742,7 +5742,7 @@
         <v>2.25</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.51</v>
+        <v>2.01</v>
       </c>
       <c r="M42" t="n">
-        <v>3.09</v>
+        <v>2.94</v>
       </c>
       <c r="N42" t="n">
-        <v>2.51</v>
+        <v>3.53</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
         <v>2.25</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5</v>
+        <v>1.55</v>
       </c>
       <c r="M13" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2130,7 +2130,7 @@
         <v>2.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N14" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
         <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M19" t="n">
         <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>4.05</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>5.4</v>
+        <v>1.84</v>
       </c>
       <c r="M21" t="n">
-        <v>3.99</v>
+        <v>3.33</v>
       </c>
       <c r="N21" t="n">
-        <v>1.46</v>
+        <v>3.63</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="M22" t="n">
-        <v>3.33</v>
+        <v>3.36</v>
       </c>
       <c r="N22" t="n">
-        <v>3.63</v>
+        <v>3.67</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.82</v>
+        <v>5.4</v>
       </c>
       <c r="M23" t="n">
-        <v>3.36</v>
+        <v>3.99</v>
       </c>
       <c r="N23" t="n">
-        <v>3.67</v>
+        <v>1.46</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.13</v>
+        <v>2.55</v>
       </c>
       <c r="M33" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="N33" t="n">
-        <v>3.77</v>
+        <v>2.55</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4701,16 +4701,16 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4830,16 +4830,16 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.55</v>
+        <v>5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="N13" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2130,7 +2130,7 @@
         <v>2.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5</v>
+        <v>1.55</v>
       </c>
       <c r="M15" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2388,7 +2388,7 @@
         <v>2.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M18" t="n">
         <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>4.05</v>
+        <v>3.35</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
         <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.84</v>
+        <v>5.4</v>
       </c>
       <c r="M21" t="n">
-        <v>3.33</v>
+        <v>3.99</v>
       </c>
       <c r="N21" t="n">
-        <v>3.63</v>
+        <v>1.46</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="M22" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="N22" t="n">
-        <v>3.67</v>
+        <v>3.19</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>5.4</v>
+        <v>1.82</v>
       </c>
       <c r="M23" t="n">
-        <v>3.99</v>
+        <v>3.36</v>
       </c>
       <c r="N23" t="n">
-        <v>1.46</v>
+        <v>3.67</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="M25" t="n">
-        <v>3.42</v>
+        <v>3.33</v>
       </c>
       <c r="N25" t="n">
-        <v>3.19</v>
+        <v>3.63</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Z25" t="n">
         <v>1.85</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.55</v>
+        <v>2.13</v>
       </c>
       <c r="M33" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="N33" t="n">
-        <v>2.55</v>
+        <v>3.77</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4701,16 +4701,16 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4830,16 +4830,16 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="M38" t="n">
-        <v>3.01</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>3.26</v>
+        <v>2.85</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="M39" t="n">
-        <v>3.5</v>
+        <v>3.01</v>
       </c>
       <c r="N39" t="n">
-        <v>2.85</v>
+        <v>3.26</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Z39" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="M13" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="N13" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.2</v>
+        <v>1.55</v>
       </c>
       <c r="M14" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.55</v>
+        <v>5</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="N15" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2388,7 +2388,7 @@
         <v>2.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
         <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M19" t="n">
         <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>4.05</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>5.4</v>
+        <v>1.84</v>
       </c>
       <c r="M21" t="n">
-        <v>3.99</v>
+        <v>3.33</v>
       </c>
       <c r="N21" t="n">
-        <v>1.46</v>
+        <v>3.63</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.13</v>
+        <v>3.45</v>
       </c>
       <c r="M33" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="N33" t="n">
-        <v>3.77</v>
+        <v>2.02</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4701,16 +4701,16 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4830,16 +4830,16 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.88</v>
+        <v>1.67</v>
       </c>
       <c r="M35" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="N35" t="n">
-        <v>2.49</v>
+        <v>4.33</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.67</v>
+        <v>2.88</v>
       </c>
       <c r="M36" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N36" t="n">
-        <v>4.33</v>
+        <v>2.49</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.51</v>
+        <v>2.01</v>
       </c>
       <c r="M41" t="n">
-        <v>3.09</v>
+        <v>2.94</v>
       </c>
       <c r="N41" t="n">
-        <v>2.51</v>
+        <v>3.53</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5742,7 +5742,7 @@
         <v>2.25</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.01</v>
+        <v>2.51</v>
       </c>
       <c r="M42" t="n">
-        <v>2.94</v>
+        <v>3.09</v>
       </c>
       <c r="N42" t="n">
-        <v>3.53</v>
+        <v>2.51</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5871,7 +5871,7 @@
         <v>2.25</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK43"/>
+  <dimension ref="A1:AK48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45950.33333333334</v>
+        <v>45950.375</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45950.375</v>
+        <v>45950.38541666666</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45950.38541666666</v>
+        <v>45950.41666666666</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45950.41666666666</v>
+        <v>45950.45833333334</v>
       </c>
     </row>
     <row r="10">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.55</v>
+        <v>5</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="N14" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2259,7 +2259,7 @@
         <v>2.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5</v>
+        <v>1.55</v>
       </c>
       <c r="M15" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2766,10 +2766,10 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45950.5625</v>
+        <v>45950.54166666666</v>
       </c>
     </row>
     <row r="19">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
         <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.69</v>
+        <v>2.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.69</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>3.89</v>
+        <v>3.35</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3024,22 +3024,22 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45950.58333333334</v>
+        <v>45950.5625</v>
       </c>
     </row>
     <row r="21">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3724,27 +3724,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.38</v>
+        <v>5.4</v>
       </c>
       <c r="M26" t="n">
-        <v>3.26</v>
+        <v>3.99</v>
       </c>
       <c r="N26" t="n">
-        <v>2.54</v>
+        <v>1.46</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45950.59027777778</v>
+        <v>45950.58333333334</v>
       </c>
     </row>
     <row r="27">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.72</v>
+        <v>1.69</v>
       </c>
       <c r="M27" t="n">
-        <v>3.08</v>
+        <v>3.69</v>
       </c>
       <c r="N27" t="n">
-        <v>1.9</v>
+        <v>3.89</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.63</v>
+        <v>2.15</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45950.60416666666</v>
+        <v>45950.58333333334</v>
       </c>
     </row>
     <row r="28">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45950.625</v>
+        <v>45950.58333333334</v>
       </c>
     </row>
     <row r="29">
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45950.625</v>
+        <v>45950.59027777778</v>
       </c>
     </row>
     <row r="30">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45950.625</v>
+        <v>45950.60416666666</v>
       </c>
     </row>
     <row r="31">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45950.64583333334</v>
+        <v>45950.625</v>
       </c>
     </row>
     <row r="33">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45950.64583333334</v>
+        <v>45950.625</v>
       </c>
     </row>
     <row r="34">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4830,16 +4830,16 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45950.64583333334</v>
+        <v>45950.625</v>
       </c>
     </row>
     <row r="35">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.67</v>
+        <v>2.55</v>
       </c>
       <c r="M35" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>4.33</v>
+        <v>2.38</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45950.65625</v>
+        <v>45950.625</v>
       </c>
     </row>
     <row r="36">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.88</v>
+        <v>2.13</v>
       </c>
       <c r="M36" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="N36" t="n">
-        <v>2.49</v>
+        <v>3.77</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5088,16 +5088,16 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45950.65625</v>
+        <v>45950.64583333334</v>
       </c>
     </row>
     <row r="37">
@@ -5143,27 +5143,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45950.65625</v>
+        <v>45950.64583333334</v>
       </c>
     </row>
     <row r="38">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="M38" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="N38" t="n">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45950.66666666666</v>
+        <v>45950.64583333334</v>
       </c>
     </row>
     <row r="39">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.41</v>
+        <v>2.88</v>
       </c>
       <c r="M39" t="n">
-        <v>3.01</v>
+        <v>3.1</v>
       </c>
       <c r="N39" t="n">
-        <v>3.26</v>
+        <v>2.49</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45950.66666666666</v>
+        <v>45950.65625</v>
       </c>
     </row>
     <row r="40">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5616,10 +5616,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45950.67708333334</v>
+        <v>45950.65625</v>
       </c>
     </row>
     <row r="41">
@@ -5659,27 +5659,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.01</v>
+        <v>1.67</v>
       </c>
       <c r="M41" t="n">
-        <v>2.94</v>
+        <v>3.45</v>
       </c>
       <c r="N41" t="n">
-        <v>3.53</v>
+        <v>4.33</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45950.79166666666</v>
+        <v>45950.65625</v>
       </c>
     </row>
     <row r="42">
@@ -5788,27 +5788,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.51</v>
+        <v>2.41</v>
       </c>
       <c r="M42" t="n">
-        <v>3.09</v>
+        <v>3.01</v>
       </c>
       <c r="N42" t="n">
-        <v>2.51</v>
+        <v>3.26</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45950.79166666666</v>
+        <v>45950.66666666666</v>
       </c>
     </row>
     <row r="43">
@@ -5917,126 +5917,771 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Kenya Kenyan Premier League</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Gor Mahia</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Posta Rangers</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" s="3" t="n">
+        <v>45950.66666666666</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>West Ham United</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Brentford</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N44" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" s="3" t="n">
+        <v>45950.66666666666</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Iceland Úrvalsdeild</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Fram</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Stjarnan</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M45" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="N45" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" s="3" t="n">
+        <v>45950.67708333334</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" s="3" t="n">
+        <v>45950.79166666666</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Ferroviária</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Paysandu</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M47" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="3" t="n">
+        <v>45950.79166666666</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Santos</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Vitória</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="inlineStr">
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L43" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M43" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N43" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" t="n">
+      <c r="L48" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M48" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="N48" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
         <v>2.17</v>
       </c>
-      <c r="Z43" t="n">
+      <c r="Z48" t="n">
         <v>1.7</v>
       </c>
-      <c r="AA43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK43" s="3" t="n">
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" s="3" t="n">
         <v>45950.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5</v>
+        <v>1.55</v>
       </c>
       <c r="M14" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.55</v>
+        <v>5</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="N15" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M19" t="n">
         <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>4.05</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
         <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.84</v>
+        <v>5.4</v>
       </c>
       <c r="M21" t="n">
-        <v>3.33</v>
+        <v>3.99</v>
       </c>
       <c r="N21" t="n">
-        <v>3.63</v>
+        <v>1.46</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.25</v>
+        <v>1.82</v>
       </c>
       <c r="M22" t="n">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="N22" t="n">
-        <v>3.19</v>
+        <v>3.67</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="M23" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="N23" t="n">
-        <v>3.67</v>
+        <v>3.19</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="M27" t="n">
-        <v>3.69</v>
+        <v>3.33</v>
       </c>
       <c r="N27" t="n">
-        <v>3.89</v>
+        <v>3.63</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.13</v>
+        <v>3.45</v>
       </c>
       <c r="M36" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="N36" t="n">
-        <v>3.77</v>
+        <v>2.02</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5088,16 +5088,16 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.45</v>
+        <v>2.13</v>
       </c>
       <c r="M37" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="N37" t="n">
-        <v>2.02</v>
+        <v>3.77</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5217,16 +5217,16 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="N13" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N14" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5</v>
+        <v>1.55</v>
       </c>
       <c r="M15" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
         <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M20" t="n">
         <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>4.05</v>
+        <v>3.35</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>5.4</v>
+        <v>1.73</v>
       </c>
       <c r="M21" t="n">
-        <v>3.99</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>1.46</v>
+        <v>4.3</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>3.69</v>
       </c>
       <c r="N24" t="n">
-        <v>4.3</v>
+        <v>3.89</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.69</v>
+        <v>5.4</v>
       </c>
       <c r="M25" t="n">
-        <v>3.69</v>
+        <v>3.99</v>
       </c>
       <c r="N25" t="n">
-        <v>3.89</v>
+        <v>1.46</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="M27" t="n">
-        <v>3.33</v>
+        <v>3.36</v>
       </c>
       <c r="N27" t="n">
-        <v>3.63</v>
+        <v>3.67</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.45</v>
+        <v>2.13</v>
       </c>
       <c r="M36" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="N36" t="n">
-        <v>2.02</v>
+        <v>3.77</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5088,16 +5088,16 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.13</v>
+        <v>3.45</v>
       </c>
       <c r="M37" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="N37" t="n">
-        <v>3.77</v>
+        <v>2.02</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5217,16 +5217,16 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="M13" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="N13" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.2</v>
+        <v>1.55</v>
       </c>
       <c r="M14" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.55</v>
+        <v>5</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="N15" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M19" t="n">
         <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>4.05</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
         <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,16 +3288,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="M24" t="n">
-        <v>3.69</v>
+        <v>3.36</v>
       </c>
       <c r="N24" t="n">
-        <v>3.89</v>
+        <v>3.67</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.57</v>
+        <v>1.94</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="M27" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="N27" t="n">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="M28" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>3.63</v>
+        <v>4.3</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.45</v>
+        <v>2.55</v>
       </c>
       <c r="M37" t="n">
         <v>3.15</v>
       </c>
       <c r="N37" t="n">
-        <v>2.02</v>
+        <v>2.55</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.55</v>
+        <v>3.45</v>
       </c>
       <c r="M38" t="n">
         <v>3.15</v>
       </c>
       <c r="N38" t="n">
-        <v>2.55</v>
+        <v>2.02</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.88</v>
+        <v>1.67</v>
       </c>
       <c r="M39" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="N39" t="n">
-        <v>2.49</v>
+        <v>4.33</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.67</v>
+        <v>2.88</v>
       </c>
       <c r="M40" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N40" t="n">
-        <v>4.33</v>
+        <v>2.49</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="M42" t="n">
-        <v>3.5</v>
+        <v>3.01</v>
       </c>
       <c r="N42" t="n">
-        <v>2.85</v>
+        <v>3.26</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Z42" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="M43" t="n">
-        <v>3.01</v>
+        <v>3.5</v>
       </c>
       <c r="N43" t="n">
-        <v>3.26</v>
+        <v>2.85</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.51</v>
+        <v>2.01</v>
       </c>
       <c r="M46" t="n">
-        <v>3.09</v>
+        <v>2.94</v>
       </c>
       <c r="N46" t="n">
-        <v>2.51</v>
+        <v>3.53</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6387,7 +6387,7 @@
         <v>2.25</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.01</v>
+        <v>2.51</v>
       </c>
       <c r="M47" t="n">
-        <v>2.94</v>
+        <v>3.09</v>
       </c>
       <c r="N47" t="n">
-        <v>3.53</v>
+        <v>2.51</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6516,7 +6516,7 @@
         <v>2.25</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.2</v>
+        <v>1.55</v>
       </c>
       <c r="M13" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N14" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
         <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M20" t="n">
         <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>4.05</v>
+        <v>3.35</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="M22" t="n">
-        <v>3.69</v>
+        <v>3.33</v>
       </c>
       <c r="N22" t="n">
-        <v>3.89</v>
+        <v>3.63</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,16 +3288,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.25</v>
+        <v>1.69</v>
       </c>
       <c r="M23" t="n">
-        <v>3.42</v>
+        <v>3.69</v>
       </c>
       <c r="N23" t="n">
-        <v>3.19</v>
+        <v>3.89</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="M27" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="N27" t="n">
-        <v>3.63</v>
+        <v>4.3</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N13" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.2</v>
+        <v>1.55</v>
       </c>
       <c r="M14" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.69</v>
+        <v>2.25</v>
       </c>
       <c r="M23" t="n">
-        <v>3.69</v>
+        <v>3.42</v>
       </c>
       <c r="N23" t="n">
-        <v>3.89</v>
+        <v>3.19</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,16 +3417,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="M24" t="n">
-        <v>3.36</v>
+        <v>3.69</v>
       </c>
       <c r="N24" t="n">
-        <v>3.67</v>
+        <v>3.89</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.94</v>
+        <v>1.57</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>5.4</v>
+        <v>1.82</v>
       </c>
       <c r="M25" t="n">
-        <v>3.99</v>
+        <v>3.36</v>
       </c>
       <c r="N25" t="n">
-        <v>1.46</v>
+        <v>3.67</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.73</v>
+        <v>5.4</v>
       </c>
       <c r="M27" t="n">
-        <v>3.25</v>
+        <v>3.99</v>
       </c>
       <c r="N27" t="n">
-        <v>4.3</v>
+        <v>1.46</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.13</v>
+        <v>2.55</v>
       </c>
       <c r="M36" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="N36" t="n">
-        <v>3.77</v>
+        <v>2.55</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5088,16 +5088,16 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.55</v>
+        <v>2.13</v>
       </c>
       <c r="M37" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="N37" t="n">
-        <v>2.55</v>
+        <v>3.77</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5217,16 +5217,16 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.65</v>
+        <v>3.07</v>
       </c>
       <c r="M45" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="N45" t="n">
-        <v>2.35</v>
+        <v>1.86</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.2</v>
+        <v>1.55</v>
       </c>
       <c r="M13" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N14" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M19" t="n">
         <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>4.05</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
         <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.25</v>
+        <v>5.4</v>
       </c>
       <c r="M23" t="n">
-        <v>3.42</v>
+        <v>3.99</v>
       </c>
       <c r="N23" t="n">
-        <v>3.19</v>
+        <v>1.46</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.69</v>
+        <v>2.25</v>
       </c>
       <c r="M24" t="n">
-        <v>3.69</v>
+        <v>3.42</v>
       </c>
       <c r="N24" t="n">
-        <v>3.89</v>
+        <v>3.19</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,16 +3546,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="M25" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="N25" t="n">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.4</v>
+        <v>1.82</v>
       </c>
       <c r="M27" t="n">
-        <v>3.99</v>
+        <v>3.36</v>
       </c>
       <c r="N27" t="n">
-        <v>1.46</v>
+        <v>3.67</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="M28" t="n">
-        <v>3.33</v>
+        <v>3.69</v>
       </c>
       <c r="N28" t="n">
-        <v>3.63</v>
+        <v>3.89</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.55</v>
+        <v>2.13</v>
       </c>
       <c r="M36" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="N36" t="n">
-        <v>2.55</v>
+        <v>3.77</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5088,16 +5088,16 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.13</v>
+        <v>3.45</v>
       </c>
       <c r="M37" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="N37" t="n">
-        <v>3.77</v>
+        <v>2.02</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5217,16 +5217,16 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.45</v>
+        <v>2.55</v>
       </c>
       <c r="M38" t="n">
         <v>3.15</v>
       </c>
       <c r="N38" t="n">
-        <v>2.02</v>
+        <v>2.55</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.88</v>
+        <v>1.67</v>
       </c>
       <c r="M39" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="N39" t="n">
-        <v>2.49</v>
+        <v>4.33</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -936,52 +936,52 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.33</v>
+        <v>2.48</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="N11" t="n">
-        <v>7.5</v>
+        <v>2.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.48</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.4</v>
+        <v>7.5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N13" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.2</v>
+        <v>1.55</v>
       </c>
       <c r="M14" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="M24" t="n">
-        <v>3.42</v>
+        <v>3.33</v>
       </c>
       <c r="N24" t="n">
-        <v>3.19</v>
+        <v>3.63</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Z24" t="n">
         <v>1.85</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="M25" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>3.63</v>
+        <v>4.3</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="M27" t="n">
-        <v>3.36</v>
+        <v>3.69</v>
       </c>
       <c r="N27" t="n">
-        <v>3.67</v>
+        <v>3.89</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.94</v>
+        <v>1.57</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.69</v>
+        <v>2.25</v>
       </c>
       <c r="M28" t="n">
-        <v>3.69</v>
+        <v>3.42</v>
       </c>
       <c r="N28" t="n">
-        <v>3.89</v>
+        <v>3.19</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,16 +4062,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="M37" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>2.02</v>
+        <v>1.78</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="M38" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N38" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="M42" t="n">
-        <v>3.01</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>3.26</v>
+        <v>2.85</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="M43" t="n">
-        <v>3.5</v>
+        <v>3.01</v>
       </c>
       <c r="N43" t="n">
-        <v>2.85</v>
+        <v>3.26</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Z43" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA45" t="n">
         <v>2.03</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.01</v>
+        <v>2.51</v>
       </c>
       <c r="M46" t="n">
-        <v>2.94</v>
+        <v>3.09</v>
       </c>
       <c r="N46" t="n">
-        <v>3.53</v>
+        <v>2.51</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6387,7 +6387,7 @@
         <v>2.25</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.51</v>
+        <v>2.01</v>
       </c>
       <c r="M47" t="n">
-        <v>3.09</v>
+        <v>2.94</v>
       </c>
       <c r="N47" t="n">
-        <v>2.51</v>
+        <v>3.53</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6516,7 +6516,7 @@
         <v>2.25</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK48"/>
+  <dimension ref="A1:AK49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -939,13 +939,13 @@
         <v>3.2</v>
       </c>
       <c r="P4" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="Q4" t="n">
         <v>3.25</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
         <v>2.52</v>
@@ -960,10 +960,10 @@
         <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="X4" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="Y4" t="n">
         <v>2.09</v>
@@ -975,29 +975,29 @@
         <v>3.58</v>
       </c>
       <c r="AB4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
         <v>1.21</v>
       </c>
-      <c r="AC4" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH4" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45950.45833333334</v>
+        <v>45950.41666666666</v>
       </c>
     </row>
     <row r="10">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="M10" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X10" t="n">
         <v>2.9</v>
       </c>
-      <c r="N10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
       <c r="Y10" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45950.47916666666</v>
+        <v>45950.45833333334</v>
       </c>
     </row>
     <row r="12">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="N12" t="n">
         <v>7.5</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.2</v>
+        <v>2.48</v>
       </c>
       <c r="M13" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="N13" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.73</v>
+        <v>2.08</v>
       </c>
       <c r="Z13" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45950.5</v>
+        <v>45950.47916666666</v>
       </c>
     </row>
     <row r="14">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.55</v>
+        <v>5.7</v>
       </c>
       <c r="M14" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="O14" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X14" t="n">
         <v>3.5</v>
       </c>
-      <c r="N14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
       <c r="Y14" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="M15" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5.49</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2434,27 +2434,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="N16" t="n">
-        <v>3.45</v>
+        <v>1.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2508,16 +2508,16 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45950.52083333334</v>
+        <v>45950.5</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45950.54166666666</v>
+        <v>45950.52083333334</v>
       </c>
     </row>
     <row r="18">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2895,10 +2895,10 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45950.5625</v>
+        <v>45950.54166666666</v>
       </c>
     </row>
     <row r="20">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,37 +2991,37 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M20" t="n">
         <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>4.05</v>
+        <v>3.35</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
         <v>1.55</v>
@@ -3030,22 +3030,22 @@
         <v>2.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3079,27 +3079,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>3.36</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>3.67</v>
+        <v>4.05</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.94</v>
+        <v>2.97</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.76</v>
+        <v>1.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45950.58333333334</v>
+        <v>45950.5625</v>
       </c>
     </row>
     <row r="22">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>5.4</v>
+        <v>1.82</v>
       </c>
       <c r="M22" t="n">
-        <v>3.99</v>
+        <v>3.36</v>
       </c>
       <c r="N22" t="n">
-        <v>1.46</v>
+        <v>3.67</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,77 +3507,77 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="M24" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>3.63</v>
+        <v>4.3</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.85</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.73</v>
+        <v>5.4</v>
       </c>
       <c r="M25" t="n">
-        <v>3.25</v>
+        <v>3.99</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3</v>
+        <v>1.46</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>5.73</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="M28" t="n">
-        <v>3.42</v>
+        <v>3.33</v>
       </c>
       <c r="N28" t="n">
-        <v>3.19</v>
+        <v>3.63</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Z28" t="n">
         <v>1.85</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4111,27 +4111,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="M29" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45950.59027777778</v>
+        <v>45950.58333333334</v>
       </c>
     </row>
     <row r="30">
@@ -4240,27 +4240,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.72</v>
+        <v>2.38</v>
       </c>
       <c r="M30" t="n">
-        <v>3.08</v>
+        <v>3.26</v>
       </c>
       <c r="N30" t="n">
-        <v>1.9</v>
+        <v>2.54</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45950.60416666666</v>
+        <v>45950.59027777778</v>
       </c>
     </row>
     <row r="31">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45950.625</v>
+        <v>45950.60416666666</v>
       </c>
     </row>
     <row r="32">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.13</v>
+        <v>2.85</v>
       </c>
       <c r="M36" t="n">
-        <v>2.98</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>3.77</v>
+        <v>2.3</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5088,16 +5088,16 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45950.64583333334</v>
+        <v>45950.625</v>
       </c>
     </row>
     <row r="37">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.7</v>
+        <v>2.13</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="N37" t="n">
-        <v>1.78</v>
+        <v>3.77</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5217,16 +5217,16 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,49 +5313,49 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M38" t="n">
         <v>3.25</v>
       </c>
-      <c r="M38" t="n">
-        <v>3.05</v>
-      </c>
       <c r="N38" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
         <v>2.25</v>
       </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Z38" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.67</v>
+        <v>3.25</v>
       </c>
       <c r="M39" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="N39" t="n">
-        <v>4.33</v>
+        <v>2.25</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45950.65625</v>
+        <v>45950.64583333334</v>
       </c>
     </row>
     <row r="40">
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5788,27 +5788,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45950.66666666666</v>
+        <v>45950.65625</v>
       </c>
     </row>
     <row r="43">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="M43" t="n">
-        <v>3.01</v>
+        <v>3.5</v>
       </c>
       <c r="N43" t="n">
-        <v>3.26</v>
+        <v>2.85</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6175,27 +6175,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stjarnan</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,16 +6255,16 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45950.67708333334</v>
+        <v>45950.66666666666</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Stjarnan</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.51</v>
+        <v>3.07</v>
       </c>
       <c r="M46" t="n">
-        <v>3.09</v>
+        <v>3.9</v>
       </c>
       <c r="N46" t="n">
-        <v>2.51</v>
+        <v>1.86</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.25</v>
+        <v>1.4</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.65</v>
+        <v>2.75</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45950.79166666666</v>
+        <v>45950.67708333334</v>
       </c>
     </row>
     <row r="47">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.01</v>
+        <v>2.51</v>
       </c>
       <c r="M47" t="n">
-        <v>2.94</v>
+        <v>3.09</v>
       </c>
       <c r="N47" t="n">
-        <v>3.53</v>
+        <v>2.51</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6516,7 +6516,7 @@
         <v>2.25</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6562,126 +6562,255 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Ferroviária</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Paysandu</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M48" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" s="3" t="n">
+        <v>45950.79166666666</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Santos</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Vitória</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="inlineStr">
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L48" t="n">
+      <c r="L49" t="n">
         <v>1.67</v>
       </c>
-      <c r="M48" t="n">
+      <c r="M49" t="n">
         <v>3.53</v>
       </c>
-      <c r="N48" t="n">
+      <c r="N49" t="n">
         <v>4.2</v>
       </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="n">
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
         <v>2.17</v>
       </c>
-      <c r="Z48" t="n">
+      <c r="Z49" t="n">
         <v>1.7</v>
       </c>
-      <c r="AA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK48" s="3" t="n">
+      <c r="AA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK49" s="3" t="n">
         <v>45950.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.7</v>
+        <v>2.5</v>
       </c>
       <c r="M14" t="n">
-        <v>4.05</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
-        <v>1.43</v>
+        <v>2.4</v>
       </c>
       <c r="O14" t="n">
-        <v>6.71</v>
+        <v>3.14</v>
       </c>
       <c r="P14" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.93</v>
+        <v>2.93</v>
       </c>
       <c r="R14" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>2.69</v>
+        <v>2.49</v>
       </c>
       <c r="U14" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="V14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X14" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.08</v>
+        <v>2.81</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.03</v>
+        <v>1.56</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>2.68</v>
+        <v>1.46</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.09</v>
+        <v>1.41</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.7</v>
+        <v>5.7</v>
       </c>
       <c r="M15" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="O15" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X15" t="n">
         <v>3.5</v>
       </c>
-      <c r="N15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3.2</v>
-      </c>
       <c r="Y15" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.35</v>
+        <v>3.08</v>
       </c>
       <c r="AB15" t="n">
         <v>1.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.86</v>
+        <v>2.03</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>2.68</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.15</v>
+        <v>1.09</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="M16" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5.49</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="Z16" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,37 +2991,37 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
         <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="O20" t="n">
-        <v>2.5</v>
+        <v>2.99</v>
       </c>
       <c r="P20" t="n">
-        <v>2.09</v>
+        <v>1.72</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="S20" t="n">
-        <v>2.39</v>
+        <v>2.05</v>
       </c>
       <c r="T20" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="U20" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="V20" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="W20" t="n">
         <v>1.55</v>
@@ -3030,22 +3030,22 @@
         <v>2.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.33</v>
+        <v>2.97</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.15</v>
+        <v>2.46</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,37 +3120,37 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M21" t="n">
         <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>4.05</v>
+        <v>3.35</v>
       </c>
       <c r="O21" t="n">
-        <v>2.99</v>
+        <v>2.5</v>
       </c>
       <c r="P21" t="n">
-        <v>1.72</v>
+        <v>2.09</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.15</v>
+        <v>5.2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="S21" t="n">
-        <v>2.05</v>
+        <v>2.39</v>
       </c>
       <c r="T21" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="U21" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="V21" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
         <v>1.55</v>
@@ -3159,22 +3159,22 @@
         <v>2.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.97</v>
+        <v>2.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AA21" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.46</v>
+        <v>2.15</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.82</v>
+        <v>2.57</v>
       </c>
       <c r="M22" t="n">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>3.67</v>
+        <v>2.5</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="M23" t="n">
-        <v>3.69</v>
+        <v>3.36</v>
       </c>
       <c r="N23" t="n">
-        <v>3.89</v>
+        <v>3.67</v>
       </c>
       <c r="O23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.57</v>
+        <v>1.94</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,58 +3765,58 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="M26" t="n">
-        <v>3.42</v>
+        <v>3.33</v>
       </c>
       <c r="N26" t="n">
-        <v>3.19</v>
+        <v>3.63</v>
       </c>
       <c r="O26" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="S26" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V26" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="X26" t="n">
-        <v>3.12</v>
+        <v>3.45</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Z26" t="n">
         <v>1.85</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.52</v>
+        <v>3.04</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AD26" t="n">
         <v>2</v>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="M28" t="n">
-        <v>3.33</v>
+        <v>3.69</v>
       </c>
       <c r="N28" t="n">
-        <v>3.63</v>
+        <v>3.89</v>
       </c>
       <c r="O28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P28" t="n">
         <v>2.5</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.14</v>
       </c>
       <c r="Q28" t="n">
         <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="S28" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="T28" t="n">
-        <v>2.73</v>
+        <v>2.34</v>
       </c>
       <c r="U28" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W28" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X28" t="n">
-        <v>3.45</v>
+        <v>4.55</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.04</v>
+        <v>2.35</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.13</v>
+        <v>4.7</v>
       </c>
       <c r="M37" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>3.77</v>
+        <v>1.78</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W37" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="X37" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y37" t="n">
         <v>2.25</v>
       </c>
-      <c r="Y37" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Z37" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.7</v>
+        <v>2.13</v>
       </c>
       <c r="M38" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="N38" t="n">
-        <v>1.78</v>
+        <v>3.77</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5346,16 +5346,16 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5451,34 +5451,34 @@
         <v>2.25</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y39" t="n">
         <v>2.2</v>
@@ -5487,16 +5487,16 @@
         <v>1.6</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6354,34 +6354,34 @@
         <v>1.86</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>5.86</v>
       </c>
       <c r="Y46" t="n">
         <v>1.4</v>
@@ -6396,10 +6396,10 @@
         <v>1.8</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -628,12 +628,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -678,52 +678,52 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45950</v>
+        <v>45950.22916666666</v>
       </c>
     </row>
     <row r="3">
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45950</v>
+        <v>45950.29166666666</v>
       </c>
     </row>
     <row r="4">
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -936,52 +936,52 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45950.22916666666</v>
+        <v>45950.29166666666</v>
       </c>
     </row>
     <row r="5">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45950.375</v>
+        <v>45950.29166666666</v>
       </c>
     </row>
     <row r="7">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Da Nang</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45950.38541666666</v>
+        <v>45950.33333333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45950.41666666666</v>
+        <v>45950.375</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Da Nang</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45950.41666666666</v>
+        <v>45950.38541666666</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45950.45833333334</v>
+        <v>45950.41666666666</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45950.45833333334</v>
+        <v>45950.41666666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45950.47916666666</v>
+        <v>45950.41666666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.48</v>
+        <v>2.17</v>
       </c>
       <c r="M13" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N13" t="n">
-        <v>2.4</v>
+        <v>3.28</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45950.47916666666</v>
+        <v>45950.45833333334</v>
       </c>
     </row>
     <row r="14">
@@ -2176,27 +2176,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45950.5</v>
+        <v>45950.45833333334</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.7</v>
+        <v>1.36</v>
       </c>
       <c r="M15" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>1.43</v>
+        <v>7</v>
       </c>
       <c r="O15" t="n">
-        <v>6.71</v>
+        <v>1.85</v>
       </c>
       <c r="P15" t="n">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.93</v>
+        <v>6.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S15" t="n">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="T15" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W15" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X15" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="Y15" t="n">
         <v>1.83</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AA15" t="n">
         <v>3.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>2.68</v>
+        <v>1.12</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.09</v>
+        <v>2.75</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45950.5</v>
+        <v>45950.47916666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.7</v>
+        <v>2.48</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="O16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.49</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45950.5</v>
+        <v>45950.47916666666</v>
       </c>
     </row>
     <row r="17">
@@ -2563,27 +2563,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,62 +2604,62 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AD17" t="n">
         <v>2.25</v>
       </c>
-      <c r="M17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AE17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45950.52083333334</v>
+        <v>45950.5</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45950.54166666666</v>
+        <v>45950.5</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45950.54166666666</v>
+        <v>45950.5</v>
       </c>
     </row>
     <row r="20">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="N20" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="O20" t="n">
-        <v>2.99</v>
+        <v>2.72</v>
       </c>
       <c r="P20" t="n">
-        <v>1.72</v>
+        <v>2.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.15</v>
+        <v>4.55</v>
       </c>
       <c r="R20" t="n">
-        <v>1.74</v>
+        <v>1.52</v>
       </c>
       <c r="S20" t="n">
-        <v>2.05</v>
+        <v>2.34</v>
       </c>
       <c r="T20" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="V20" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="W20" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="X20" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.97</v>
+        <v>2.51</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AA20" t="n">
-        <v>6.2</v>
+        <v>4.44</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.46</v>
+        <v>2.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.41</v>
+        <v>1.66</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45950.5625</v>
+        <v>45950.52083333334</v>
       </c>
     </row>
     <row r="21">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q21" t="n">
         <v>2.5</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5.2</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>2.39</v>
+        <v>2.93</v>
       </c>
       <c r="T21" t="n">
-        <v>3.6</v>
+        <v>2.62</v>
       </c>
       <c r="U21" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="X21" t="n">
-        <v>2.3</v>
+        <v>3.48</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.33</v>
+        <v>1.79</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.55</v>
+        <v>1.92</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.15</v>
+        <v>1.66</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.63</v>
+        <v>2.07</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,11 +3187,11 @@
         </is>
       </c>
       <c r="AG21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.32</v>
       </c>
-      <c r="AH21" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AI21" t="n">
         <v>0</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45950.5625</v>
+        <v>45950.54166666666</v>
       </c>
     </row>
     <row r="22">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,78 +3249,78 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.57</v>
+        <v>2.09</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="N22" t="n">
-        <v>2.5</v>
+        <v>3.92</v>
       </c>
       <c r="O22" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="P22" t="n">
-        <v>2.11</v>
+        <v>1.72</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.18</v>
+        <v>5.15</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>1.74</v>
       </c>
       <c r="S22" t="n">
-        <v>2.91</v>
+        <v>2.03</v>
       </c>
       <c r="T22" t="n">
-        <v>2.74</v>
+        <v>4.25</v>
       </c>
       <c r="U22" t="n">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="V22" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="W22" t="n">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="X22" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.83</v>
+        <v>2.97</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.14</v>
+        <v>6.25</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.32</v>
+        <v>1.06</v>
       </c>
       <c r="AC22" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.67</v>
       </c>
-      <c r="AD22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AI22" t="n">
         <v>0</v>
       </c>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>45950.58333333334</v>
+        <v>45950.5625</v>
       </c>
     </row>
     <row r="23">
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="M23" t="n">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>3.67</v>
+        <v>4.4</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.94</v>
+        <v>2.46</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.76</v>
+        <v>1.56</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45950.58333333334</v>
+        <v>45950.5625</v>
       </c>
     </row>
     <row r="24">
@@ -3507,34 +3507,34 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N24" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="O24" t="n">
         <v>2.5</v>
       </c>
       <c r="P24" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.9</v>
+        <v>4.37</v>
       </c>
       <c r="R24" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
         <v>2.47</v>
       </c>
       <c r="T24" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="U24" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V24" t="n">
         <v>1.04</v>
@@ -3546,19 +3546,19 @@
         <v>2.62</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AA24" t="n">
         <v>4.15</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AD24" t="n">
         <v>1.71</v>
@@ -3574,7 +3574,7 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AH24" t="n">
         <v>1.85</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>5.4</v>
+        <v>1.73</v>
       </c>
       <c r="M25" t="n">
-        <v>3.99</v>
+        <v>3.75</v>
       </c>
       <c r="N25" t="n">
-        <v>1.46</v>
+        <v>3.85</v>
       </c>
       <c r="O25" t="n">
-        <v>5.73</v>
+        <v>2.25</v>
       </c>
       <c r="P25" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="S25" t="n">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="U25" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="V25" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W25" t="n">
         <v>1.18</v>
       </c>
       <c r="X25" t="n">
-        <v>3.94</v>
+        <v>4.55</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.84</v>
+        <v>5.4</v>
       </c>
       <c r="M26" t="n">
-        <v>3.33</v>
+        <v>3.99</v>
       </c>
       <c r="N26" t="n">
-        <v>3.63</v>
+        <v>1.46</v>
       </c>
       <c r="O26" t="n">
-        <v>2.5</v>
+        <v>5.73</v>
       </c>
       <c r="P26" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S26" t="n">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="T26" t="n">
-        <v>2.73</v>
+        <v>2.2</v>
       </c>
       <c r="U26" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X26" t="n">
-        <v>3.45</v>
+        <v>3.94</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.04</v>
+        <v>2.59</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AD26" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.75</v>
+        <v>1.1</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P27" t="n">
         <v>2.25</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.05</v>
-      </c>
       <c r="Q27" t="n">
-        <v>3.82</v>
+        <v>4.48</v>
       </c>
       <c r="R27" t="n">
         <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="T27" t="n">
         <v>2.8</v>
       </c>
       <c r="U27" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="X27" t="n">
         <v>3.12</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="AB27" t="n">
         <v>1.25</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.69</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>3.89</v>
+        <v>3.63</v>
       </c>
       <c r="O28" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="Q28" t="n">
         <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="T28" t="n">
-        <v>2.34</v>
+        <v>2.65</v>
       </c>
       <c r="U28" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="V28" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X28" t="n">
-        <v>4.55</v>
+        <v>3.65</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.35</v>
+        <v>3.04</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
         <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4240,27 +4240,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="M30" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>2.54</v>
+        <v>3.09</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.78</v>
+        <v>2.06</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45950.59027777778</v>
+        <v>45950.58333333334</v>
       </c>
     </row>
     <row r="31">
@@ -4369,27 +4369,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.72</v>
+        <v>2.54</v>
       </c>
       <c r="M31" t="n">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>1.9</v>
+        <v>2.57</v>
       </c>
       <c r="O31" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="P31" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q31" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T31" t="n">
         <v>2.62</v>
       </c>
-      <c r="R31" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.95</v>
-      </c>
       <c r="U31" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W31" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="X31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA31" t="n">
         <v>3</v>
       </c>
-      <c r="Y31" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AB31" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45950.60416666666</v>
+        <v>45950.59027777778</v>
       </c>
     </row>
     <row r="32">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45950.625</v>
+        <v>45950.60416666666</v>
       </c>
     </row>
     <row r="33">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45950.64583333334</v>
+        <v>45950.625</v>
       </c>
     </row>
     <row r="38">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.13</v>
+        <v>4.7</v>
       </c>
       <c r="M38" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="N38" t="n">
-        <v>3.77</v>
+        <v>1.78</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W38" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="X38" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y38" t="n">
         <v>2.25</v>
       </c>
-      <c r="Y38" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Z38" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.67</v>
+        <v>2.13</v>
       </c>
       <c r="M40" t="n">
-        <v>3.45</v>
+        <v>2.98</v>
       </c>
       <c r="N40" t="n">
-        <v>4.33</v>
+        <v>3.77</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45950.65625</v>
+        <v>45950.64583333334</v>
       </c>
     </row>
     <row r="41">
@@ -5709,34 +5709,34 @@
         <v>2.49</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y41" t="n">
         <v>2.15</v>
@@ -5745,16 +5745,16 @@
         <v>1.7</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45950.66666666666</v>
+        <v>45950.65625</v>
       </c>
     </row>
     <row r="44">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="M44" t="n">
-        <v>3.01</v>
+        <v>3.2</v>
       </c>
       <c r="N44" t="n">
-        <v>3.26</v>
+        <v>2.78</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="Z44" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC44" t="n">
         <v>1.66</v>
       </c>
-      <c r="AA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0</v>
-      </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="M45" t="n">
-        <v>3.5</v>
+        <v>3.01</v>
       </c>
       <c r="N45" t="n">
-        <v>2.85</v>
+        <v>3.26</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Z45" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.51</v>
+        <v>2.01</v>
       </c>
       <c r="M47" t="n">
-        <v>3.09</v>
+        <v>2.94</v>
       </c>
       <c r="N47" t="n">
-        <v>2.51</v>
+        <v>3.53</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6516,7 +6516,7 @@
         <v>2.25</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.01</v>
+        <v>2.51</v>
       </c>
       <c r="M48" t="n">
-        <v>2.94</v>
+        <v>3.09</v>
       </c>
       <c r="N48" t="n">
-        <v>3.53</v>
+        <v>2.51</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6645,7 +6645,7 @@
         <v>2.25</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -628,12 +628,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -678,52 +678,52 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45950.22916666666</v>
+        <v>45950</v>
       </c>
     </row>
     <row r="3">
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45950.29166666666</v>
+        <v>45950</v>
       </c>
     </row>
     <row r="4">
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -936,52 +936,52 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45950.29166666666</v>
+        <v>45950.22916666666</v>
       </c>
     </row>
     <row r="5">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="O8" t="n">
         <v>3.1</v>
@@ -1458,31 +1458,31 @@
         <v>2.04</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="R8" t="n">
         <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="T8" t="n">
         <v>2.89</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="X8" t="n">
         <v>3.22</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Z8" t="n">
         <v>1.78</v>
@@ -1491,7 +1491,7 @@
         <v>3.31</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AC8" t="n">
         <v>1.71</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AH8" t="n">
         <v>1.26</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.37</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1704,55 +1704,55 @@
         <v>4.35</v>
       </c>
       <c r="M10" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
         <v>1.7</v>
       </c>
       <c r="O10" t="n">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="P10" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>3.26</v>
+        <v>3.16</v>
       </c>
       <c r="T10" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="U10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="V10" t="n">
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>3.88</v>
+        <v>3.74</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="Z10" t="n">
         <v>2.02</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.74</v>
+        <v>2.81</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AD10" t="n">
         <v>1.97</v>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.17</v>
+        <v>2.35</v>
       </c>
       <c r="M13" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="O13" t="n">
         <v>2.88</v>
@@ -2127,10 +2127,10 @@
         <v>2.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AA13" t="n">
         <v>4.05</v>
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="N15" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="O15" t="n">
         <v>1.85</v>
@@ -2385,10 +2385,10 @@
         <v>3.42</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AA15" t="n">
         <v>3.08</v>
@@ -2604,22 +2604,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="O17" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="P17" t="n">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.93</v>
+        <v>2.98</v>
       </c>
       <c r="R17" t="n">
         <v>1.3</v>
@@ -2643,22 +2643,22 @@
         <v>3.88</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="Z17" t="n">
         <v>2</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.81</v>
+        <v>2.69</v>
       </c>
       <c r="AB17" t="n">
         <v>1.36</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.46</v>
+        <v>1.23</v>
       </c>
       <c r="AH17" t="n">
         <v>1.41</v>
@@ -2751,7 +2751,7 @@
         <v>5.25</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
         <v>2.95</v>
@@ -2766,10 +2766,10 @@
         <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="X18" t="n">
-        <v>3.22</v>
+        <v>3.36</v>
       </c>
       <c r="Y18" t="n">
         <v>1.85</v>
@@ -2778,7 +2778,7 @@
         <v>1.85</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AB18" t="n">
         <v>1.3</v>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="M19" t="n">
-        <v>4.05</v>
+        <v>4.7</v>
       </c>
       <c r="N19" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="O19" t="n">
         <v>6.55</v>
@@ -2901,10 +2901,10 @@
         <v>3.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="AA19" t="n">
         <v>2.97</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="N20" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O20" t="n">
         <v>2.72</v>
@@ -3024,10 +3024,10 @@
         <v>1.05</v>
       </c>
       <c r="W20" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="X20" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="Y20" t="n">
         <v>2.51</v>
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>3.92</v>
+        <v>4.05</v>
       </c>
       <c r="O22" t="n">
         <v>2.99</v>
@@ -3282,10 +3282,10 @@
         <v>1.16</v>
       </c>
       <c r="W22" t="n">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="X22" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Y22" t="n">
         <v>2.97</v>
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.72</v>
+        <v>2.25</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="O23" t="n">
         <v>2.35</v>
@@ -3411,10 +3411,10 @@
         <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="X23" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="Y23" t="n">
         <v>2.46</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,62 +3507,62 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y24" t="n">
         <v>1.9</v>
       </c>
-      <c r="M24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P24" t="n">
+      <c r="Z24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD24" t="n">
         <v>2</v>
       </c>
-      <c r="Q24" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.71</v>
-      </c>
       <c r="AE24" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="M25" t="n">
-        <v>3.75</v>
+        <v>3.36</v>
       </c>
       <c r="N25" t="n">
-        <v>3.85</v>
+        <v>3.67</v>
       </c>
       <c r="O25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P25" t="n">
         <v>2.25</v>
       </c>
-      <c r="P25" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>4.48</v>
       </c>
       <c r="R25" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="T25" t="n">
-        <v>2.34</v>
+        <v>2.8</v>
       </c>
       <c r="U25" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="V25" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="X25" t="n">
-        <v>4.55</v>
+        <v>3.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.54</v>
+        <v>1.94</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,77 +3765,77 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5.4</v>
+        <v>1.84</v>
       </c>
       <c r="M26" t="n">
-        <v>3.99</v>
+        <v>3.33</v>
       </c>
       <c r="N26" t="n">
-        <v>1.46</v>
+        <v>3.63</v>
       </c>
       <c r="O26" t="n">
-        <v>5.73</v>
+        <v>2.5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="Q26" t="n">
+        <v>4</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD26" t="n">
         <v>2</v>
       </c>
-      <c r="R26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC26" t="n">
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.1</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.01</v>
+        <v>1.69</v>
       </c>
       <c r="M27" t="n">
-        <v>3.2</v>
+        <v>3.69</v>
       </c>
       <c r="N27" t="n">
-        <v>3.5</v>
+        <v>3.89</v>
       </c>
       <c r="O27" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="P27" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.48</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="S27" t="n">
-        <v>2.69</v>
+        <v>3.4</v>
       </c>
       <c r="T27" t="n">
-        <v>2.8</v>
+        <v>2.34</v>
       </c>
       <c r="U27" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W27" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="X27" t="n">
-        <v>3.12</v>
+        <v>4.33</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.6</v>
+        <v>2.35</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,58 +4023,58 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>3.63</v>
+        <v>3.09</v>
       </c>
       <c r="O28" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="P28" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="R28" t="n">
         <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="T28" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="U28" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.25</v>
       </c>
-      <c r="X28" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AC28" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AD28" t="n">
         <v>2</v>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,77 +4152,77 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.57</v>
+        <v>1.73</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O29" t="n">
         <v>2.5</v>
       </c>
-      <c r="O29" t="n">
-        <v>3.05</v>
-      </c>
       <c r="P29" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.18</v>
+        <v>4.37</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S29" t="n">
-        <v>2.91</v>
+        <v>2.47</v>
       </c>
       <c r="T29" t="n">
-        <v>2.74</v>
+        <v>3.22</v>
       </c>
       <c r="U29" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="V29" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="X29" t="n">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="Z29" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.5</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.34</v>
+        <v>5.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>3.99</v>
       </c>
       <c r="N30" t="n">
-        <v>3.09</v>
+        <v>1.46</v>
       </c>
       <c r="O30" t="n">
-        <v>2.75</v>
+        <v>5.73</v>
       </c>
       <c r="P30" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.82</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="T30" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="U30" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V30" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="X30" t="n">
-        <v>3.33</v>
+        <v>3.94</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.06</v>
+        <v>1.65</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.52</v>
+        <v>2.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AC30" t="n">
         <v>1.75</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.62</v>
+        <v>1.1</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4410,19 +4410,19 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="N31" t="n">
         <v>2.54</v>
-      </c>
-      <c r="M31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.57</v>
       </c>
       <c r="O31" t="n">
         <v>3.1</v>
       </c>
       <c r="P31" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q31" t="n">
         <v>3.18</v>
@@ -4434,31 +4434,31 @@
         <v>3.1</v>
       </c>
       <c r="T31" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="U31" t="n">
         <v>1.44</v>
       </c>
       <c r="V31" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W31" t="n">
         <v>1.22</v>
       </c>
       <c r="X31" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AA31" t="n">
         <v>3</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AC31" t="n">
         <v>1.65</v>
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
         <v>1.5</v>
@@ -4548,25 +4548,25 @@
         <v>1.9</v>
       </c>
       <c r="O32" t="n">
-        <v>4.72</v>
+        <v>4.56</v>
       </c>
       <c r="P32" t="n">
         <v>2.09</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="R32" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S32" t="n">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="T32" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="U32" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="V32" t="n">
         <v>1.02</v>
@@ -4575,7 +4575,7 @@
         <v>1.33</v>
       </c>
       <c r="X32" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="Y32" t="n">
         <v>1.94</v>
@@ -4584,7 +4584,7 @@
         <v>1.76</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.1</v>
+        <v>4.19</v>
       </c>
       <c r="AB32" t="n">
         <v>1.21</v>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4797,22 +4797,22 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4821,37 +4821,37 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,22 +5055,22 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.85</v>
+        <v>2.03</v>
       </c>
       <c r="M36" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N36" t="n">
-        <v>2.3</v>
+        <v>3.01</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -5079,37 +5079,37 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.83</v>
+        <v>1.48</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5184,22 +5184,22 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -5208,37 +5208,37 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.7</v>
+        <v>2.13</v>
       </c>
       <c r="M38" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="N38" t="n">
-        <v>1.78</v>
+        <v>3.77</v>
       </c>
       <c r="O38" t="n">
-        <v>5.15</v>
+        <v>3</v>
       </c>
       <c r="P38" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.48</v>
+        <v>4.25</v>
       </c>
       <c r="R38" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="S38" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="T38" t="n">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="U38" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="V38" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W38" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="X38" t="n">
-        <v>2.56</v>
+        <v>2.25</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AA38" t="n">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.07</v>
+        <v>2.36</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.15</v>
+        <v>1.65</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M39" t="n">
         <v>3.25</v>
       </c>
-      <c r="M39" t="n">
-        <v>3.05</v>
-      </c>
       <c r="N39" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O39" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y39" t="n">
         <v>2.25</v>
       </c>
-      <c r="O39" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X39" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Z39" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.13</v>
+        <v>3.25</v>
       </c>
       <c r="M40" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="N40" t="n">
-        <v>3.77</v>
+        <v>2.25</v>
       </c>
       <c r="O40" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="P40" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.25</v>
+        <v>2.78</v>
       </c>
       <c r="R40" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="S40" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="T40" t="n">
-        <v>3.75</v>
+        <v>3.16</v>
       </c>
       <c r="U40" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="V40" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="W40" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="X40" t="n">
-        <v>2.25</v>
+        <v>2.69</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AA40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.36</v>
+        <v>1.54</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.65</v>
+        <v>1.27</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5970,7 +5970,7 @@
         <v>2.19</v>
       </c>
       <c r="P43" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="Q43" t="n">
         <v>5.42</v>
@@ -5979,22 +5979,22 @@
         <v>1.4</v>
       </c>
       <c r="S43" t="n">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="T43" t="n">
-        <v>2.94</v>
+        <v>3.03</v>
       </c>
       <c r="U43" t="n">
         <v>1.35</v>
       </c>
       <c r="V43" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W43" t="n">
         <v>1.28</v>
       </c>
       <c r="X43" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="Y43" t="n">
         <v>2.05</v>
@@ -6006,7 +6006,7 @@
         <v>3.44</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AC43" t="n">
         <v>1.89</v>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="M44" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N44" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="O44" t="n">
         <v>2.78</v>
@@ -6126,10 +6126,10 @@
         <v>3.52</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AA44" t="n">
         <v>3.06</v>
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.41</v>
+        <v>2.26</v>
       </c>
       <c r="M45" t="n">
-        <v>3.01</v>
+        <v>3.11</v>
       </c>
       <c r="N45" t="n">
-        <v>3.26</v>
+        <v>3.53</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6372,16 +6372,16 @@
         <v>2.05</v>
       </c>
       <c r="U46" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V46" t="n">
         <v>1.01</v>
       </c>
       <c r="W46" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X46" t="n">
-        <v>5.86</v>
+        <v>5.95</v>
       </c>
       <c r="Y46" t="n">
         <v>1.4</v>
@@ -6396,10 +6396,10 @@
         <v>1.8</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>1.25</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.01</v>
+        <v>2.51</v>
       </c>
       <c r="M47" t="n">
-        <v>2.94</v>
+        <v>3.09</v>
       </c>
       <c r="N47" t="n">
-        <v>3.53</v>
+        <v>2.51</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Y47" t="n">
         <v>2.25</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.51</v>
+        <v>2.01</v>
       </c>
       <c r="M48" t="n">
-        <v>3.09</v>
+        <v>2.94</v>
       </c>
       <c r="N48" t="n">
-        <v>2.51</v>
+        <v>3.53</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y48" t="n">
         <v>2.25</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6741,34 +6741,34 @@
         <v>4.2</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Y49" t="n">
         <v>2.17</v>
@@ -6777,16 +6777,16 @@
         <v>1.7</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK49"/>
+  <dimension ref="A1:AK52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.33</v>
+        <v>2.48</v>
       </c>
       <c r="M15" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="N15" t="n">
-        <v>7.5</v>
+        <v>2.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.48</v>
+        <v>1.33</v>
       </c>
       <c r="M16" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.4</v>
+        <v>7.5</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -3135,46 +3135,46 @@
         <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S21" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="T21" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="U21" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W21" t="n">
         <v>1.22</v>
       </c>
       <c r="X21" t="n">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AA21" t="n">
         <v>2.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.75</v>
+        <v>1.23</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,37 +3249,37 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M22" t="n">
         <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>4.05</v>
+        <v>3.35</v>
       </c>
       <c r="O22" t="n">
-        <v>2.99</v>
+        <v>2.35</v>
       </c>
       <c r="P22" t="n">
-        <v>1.72</v>
+        <v>2.01</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.15</v>
+        <v>5.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="S22" t="n">
-        <v>2.03</v>
+        <v>2.57</v>
       </c>
       <c r="T22" t="n">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="V22" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
         <v>1.55</v>
@@ -3288,22 +3288,22 @@
         <v>2.3</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.97</v>
+        <v>2.46</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="AA22" t="n">
-        <v>6.25</v>
+        <v>4.65</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.46</v>
+        <v>2.15</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,37 +3378,37 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
         <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="O23" t="n">
-        <v>2.35</v>
+        <v>2.99</v>
       </c>
       <c r="P23" t="n">
-        <v>2.01</v>
+        <v>1.72</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="R23" t="n">
-        <v>1.48</v>
+        <v>1.74</v>
       </c>
       <c r="S23" t="n">
-        <v>2.57</v>
+        <v>2.03</v>
       </c>
       <c r="T23" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="U23" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="W23" t="n">
         <v>1.55</v>
@@ -3417,22 +3417,22 @@
         <v>2.3</v>
       </c>
       <c r="Y23" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC23" t="n">
         <v>2.46</v>
       </c>
-      <c r="Z23" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AD23" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,58 +3507,58 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.45</v>
+        <v>1.84</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N24" t="n">
-        <v>2.6</v>
+        <v>3.63</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
         <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>2.91</v>
+        <v>2.85</v>
       </c>
       <c r="T24" t="n">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="U24" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="V24" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
         <v>1.25</v>
       </c>
       <c r="X24" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="Z24" t="n">
         <v>1.85</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AD24" t="n">
         <v>2</v>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.82</v>
+        <v>2.34</v>
       </c>
       <c r="M25" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>3.67</v>
+        <v>3.09</v>
       </c>
       <c r="O25" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.48</v>
+        <v>3.82</v>
       </c>
       <c r="R25" t="n">
         <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="T25" t="n">
         <v>2.8</v>
       </c>
       <c r="U25" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="X25" t="n">
-        <v>3.1</v>
+        <v>3.33</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="Z25" t="n">
         <v>1.76</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="AB25" t="n">
         <v>1.25</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="M26" t="n">
-        <v>3.33</v>
+        <v>3.36</v>
       </c>
       <c r="N26" t="n">
-        <v>3.63</v>
+        <v>3.67</v>
       </c>
       <c r="O26" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="P26" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>4.48</v>
       </c>
       <c r="R26" t="n">
         <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="T26" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="V26" t="n">
         <v>1.01</v>
       </c>
       <c r="W26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB26" t="n">
         <v>1.25</v>
       </c>
-      <c r="X26" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Y26" t="n">
+      <c r="AC26" t="n">
         <v>1.85</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AD26" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,58 +4023,58 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>3.09</v>
+        <v>2.6</v>
       </c>
       <c r="O28" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="P28" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.82</v>
+        <v>3.15</v>
       </c>
       <c r="R28" t="n">
         <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="T28" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="V28" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.32</v>
       </c>
-      <c r="X28" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AC28" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AD28" t="n">
         <v>2</v>
@@ -4093,7 +4093,7 @@
         <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.73</v>
+        <v>5.4</v>
       </c>
       <c r="M29" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="O29" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S29" t="n">
         <v>3.25</v>
       </c>
-      <c r="N29" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.47</v>
-      </c>
       <c r="T29" t="n">
-        <v>3.22</v>
+        <v>2.38</v>
       </c>
       <c r="U29" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="V29" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W29" t="n">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="X29" t="n">
-        <v>2.62</v>
+        <v>3.94</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>4.15</v>
+        <v>2.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.71</v>
+        <v>1.95</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.85</v>
+        <v>1.1</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5.4</v>
+        <v>1.73</v>
       </c>
       <c r="M30" t="n">
-        <v>3.99</v>
+        <v>3.25</v>
       </c>
       <c r="N30" t="n">
-        <v>1.46</v>
+        <v>4.3</v>
       </c>
       <c r="O30" t="n">
-        <v>5.73</v>
+        <v>2.5</v>
       </c>
       <c r="P30" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>4.37</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="S30" t="n">
-        <v>3.25</v>
+        <v>2.47</v>
       </c>
       <c r="T30" t="n">
-        <v>2.38</v>
+        <v>3.22</v>
       </c>
       <c r="U30" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="V30" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W30" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="X30" t="n">
-        <v>3.94</v>
+        <v>2.62</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.7</v>
+        <v>4.15</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.1</v>
+        <v>1.85</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,22 +4668,22 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5.3</v>
+        <v>2.09</v>
       </c>
       <c r="M33" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="N33" t="n">
-        <v>1.47</v>
+        <v>2.97</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4692,37 +4692,37 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,22 +4797,22 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.09</v>
+        <v>2.85</v>
       </c>
       <c r="M34" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>2.97</v>
+        <v>2.3</v>
       </c>
       <c r="O34" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4821,37 +4821,37 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,22 +4926,22 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.85</v>
+        <v>2.03</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N35" t="n">
-        <v>2.3</v>
+        <v>3.01</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4950,37 +4950,37 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.83</v>
+        <v>1.48</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,22 +5055,22 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.03</v>
+        <v>5.3</v>
       </c>
       <c r="M36" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="N36" t="n">
-        <v>3.01</v>
+        <v>1.47</v>
       </c>
       <c r="O36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -5079,37 +5079,37 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,77 +5442,77 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="M39" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="N39" t="n">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="O39" t="n">
-        <v>5.4</v>
+        <v>3.65</v>
       </c>
       <c r="P39" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="R39" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="S39" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="T39" t="n">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="U39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AH39" t="n">
         <v>1.27</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.16</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M40" t="n">
         <v>3.25</v>
       </c>
-      <c r="M40" t="n">
-        <v>3.05</v>
-      </c>
       <c r="N40" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O40" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X40" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y40" t="n">
         <v>2.25</v>
       </c>
-      <c r="O40" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P40" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T40" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X40" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Z40" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AA40" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>5.42</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6691,126 +6691,513 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Portmore United</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Harbour View</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK49" s="3" t="n">
+        <v>45950.79166666666</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="M50" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3" t="n">
+        <v>45950.8125</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Santos</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Vitória</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="inlineStr">
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L49" t="n">
+      <c r="L51" t="n">
         <v>1.67</v>
       </c>
-      <c r="M49" t="n">
+      <c r="M51" t="n">
         <v>3.53</v>
       </c>
-      <c r="N49" t="n">
+      <c r="N51" t="n">
         <v>4.2</v>
       </c>
-      <c r="O49" t="n">
+      <c r="O51" t="n">
         <v>2.23</v>
       </c>
-      <c r="P49" t="n">
+      <c r="P51" t="n">
         <v>2.08</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="Q51" t="n">
         <v>5.7</v>
       </c>
-      <c r="R49" t="n">
+      <c r="R51" t="n">
         <v>1.43</v>
       </c>
-      <c r="S49" t="n">
+      <c r="S51" t="n">
         <v>2.65</v>
       </c>
-      <c r="T49" t="n">
+      <c r="T51" t="n">
         <v>3.1</v>
       </c>
-      <c r="U49" t="n">
+      <c r="U51" t="n">
         <v>1.33</v>
       </c>
-      <c r="V49" t="n">
+      <c r="V51" t="n">
         <v>1.01</v>
       </c>
-      <c r="W49" t="n">
+      <c r="W51" t="n">
         <v>1.32</v>
       </c>
-      <c r="X49" t="n">
+      <c r="X51" t="n">
         <v>2.89</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="Y51" t="n">
         <v>2.17</v>
       </c>
-      <c r="Z49" t="n">
+      <c r="Z51" t="n">
         <v>1.7</v>
       </c>
-      <c r="AA49" t="n">
+      <c r="AA51" t="n">
         <v>3.8</v>
       </c>
-      <c r="AB49" t="n">
+      <c r="AB51" t="n">
         <v>1.19</v>
       </c>
-      <c r="AC49" t="n">
+      <c r="AC51" t="n">
         <v>2.06</v>
       </c>
-      <c r="AD49" t="n">
+      <c r="AD51" t="n">
         <v>1.68</v>
       </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG49" t="n">
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
         <v>1.28</v>
       </c>
-      <c r="AH49" t="n">
+      <c r="AH51" t="n">
         <v>2.2</v>
       </c>
-      <c r="AI49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK49" s="3" t="n">
+      <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3" t="n">
+        <v>45950.89583333334</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Arnett Gardens</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tivoli Gardens</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N52" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK52" s="3" t="n">
         <v>45950.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.48</v>
+        <v>1.36</v>
       </c>
       <c r="M15" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>2.4</v>
+        <v>7.9</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.08</v>
+        <v>1.86</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.33</v>
+        <v>2.48</v>
       </c>
       <c r="M16" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="N16" t="n">
-        <v>7.5</v>
+        <v>2.4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.2</v>
+        <v>1.55</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="O17" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.98</v>
+        <v>5.25</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="T17" t="n">
-        <v>2.49</v>
+        <v>2.77</v>
       </c>
       <c r="U17" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="V17" t="n">
         <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="X17" t="n">
-        <v>3.88</v>
+        <v>3.36</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="Z17" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.69</v>
+        <v>3.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.22</v>
+        <v>1.84</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>1.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.41</v>
+        <v>2.14</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="O18" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.25</v>
+        <v>2.98</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>2.77</v>
+        <v>2.49</v>
       </c>
       <c r="U18" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="V18" t="n">
         <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="X18" t="n">
-        <v>3.36</v>
+        <v>3.88</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.25</v>
+        <v>2.69</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.84</v>
+        <v>2.22</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>1.23</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.14</v>
+        <v>1.41</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="M24" t="n">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="N24" t="n">
-        <v>3.63</v>
+        <v>3.85</v>
       </c>
       <c r="O24" t="n">
         <v>2.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>5.15</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="T24" t="n">
-        <v>2.65</v>
+        <v>3.22</v>
       </c>
       <c r="U24" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="X24" t="n">
-        <v>3.65</v>
+        <v>2.95</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.04</v>
+        <v>3.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,77 +3636,77 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.34</v>
+        <v>1.82</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="N25" t="n">
-        <v>3.09</v>
+        <v>3.67</v>
       </c>
       <c r="O25" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="P25" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.82</v>
+        <v>4.48</v>
       </c>
       <c r="R25" t="n">
         <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="T25" t="n">
         <v>2.8</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="X25" t="n">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="Z25" t="n">
         <v>1.76</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="AB25" t="n">
         <v>1.25</v>
       </c>
       <c r="AC25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.62</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="M26" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="N26" t="n">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
       <c r="O26" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.48</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
         <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="U26" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V26" t="n">
         <v>1.01</v>
       </c>
       <c r="W26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB26" t="n">
         <v>1.29</v>
       </c>
-      <c r="X26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AC26" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.69</v>
+        <v>2.45</v>
       </c>
       <c r="M27" t="n">
-        <v>3.69</v>
+        <v>3.25</v>
       </c>
       <c r="N27" t="n">
-        <v>3.89</v>
+        <v>2.6</v>
       </c>
       <c r="O27" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.33</v>
+        <v>2.11</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="R27" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X27" t="n">
         <v>3.4</v>
       </c>
-      <c r="T27" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X27" t="n">
-        <v>4.33</v>
-      </c>
       <c r="Y27" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.35</v>
+        <v>3.14</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,58 +4023,58 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="M28" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N28" t="n">
-        <v>2.6</v>
+        <v>3.09</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="P28" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.15</v>
+        <v>3.82</v>
       </c>
       <c r="R28" t="n">
         <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="T28" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="U28" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.25</v>
       </c>
-      <c r="X28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AC28" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AD28" t="n">
         <v>2</v>
@@ -4093,7 +4093,7 @@
         <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5.4</v>
+        <v>1.69</v>
       </c>
       <c r="M29" t="n">
-        <v>3.99</v>
+        <v>3.69</v>
       </c>
       <c r="N29" t="n">
-        <v>1.46</v>
+        <v>3.89</v>
       </c>
       <c r="O29" t="n">
-        <v>5.73</v>
+        <v>2.25</v>
       </c>
       <c r="P29" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="S29" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T29" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="U29" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V29" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
         <v>1.18</v>
       </c>
       <c r="X29" t="n">
-        <v>3.94</v>
+        <v>4.33</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.1</v>
+        <v>1.91</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="O30" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X30" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC30" t="n">
         <v>1.73</v>
       </c>
-      <c r="M30" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N30" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X30" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AD30" t="n">
-        <v>1.71</v>
+        <v>1.94</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.13</v>
+        <v>2.4</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.85</v>
+        <v>1.1</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,22 +4668,22 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.09</v>
+        <v>2.85</v>
       </c>
       <c r="M33" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>2.97</v>
+        <v>2.3</v>
       </c>
       <c r="O33" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4692,37 +4692,37 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.85</v>
+        <v>5.3</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="N34" t="n">
-        <v>2.3</v>
+        <v>1.47</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,22 +4926,22 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="M35" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="N35" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="O35" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="P35" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4950,37 +4950,37 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="U35" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="X35" t="n">
-        <v>5.6</v>
+        <v>4.75</v>
       </c>
       <c r="Y35" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB35" t="n">
         <v>1.48</v>
       </c>
-      <c r="Z35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AC35" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,22 +5055,22 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>5.3</v>
+        <v>2.03</v>
       </c>
       <c r="M36" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="N36" t="n">
-        <v>1.47</v>
+        <v>3.01</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -5079,37 +5079,37 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="M38" t="n">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="N38" t="n">
-        <v>3.77</v>
+        <v>2.23</v>
       </c>
       <c r="O38" t="n">
-        <v>3</v>
+        <v>4.21</v>
       </c>
       <c r="P38" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.25</v>
+        <v>2.83</v>
       </c>
       <c r="R38" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="S38" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="T38" t="n">
-        <v>3.75</v>
+        <v>3.16</v>
       </c>
       <c r="U38" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V38" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="W38" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="X38" t="n">
-        <v>2.25</v>
+        <v>2.69</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AA38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.65</v>
+        <v>1.27</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M39" t="n">
         <v>3.25</v>
       </c>
-      <c r="M39" t="n">
-        <v>3.05</v>
-      </c>
       <c r="N39" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="O39" t="n">
-        <v>3.65</v>
+        <v>4.65</v>
       </c>
       <c r="P39" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="R39" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="S39" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="T39" t="n">
-        <v>3.16</v>
+        <v>3.28</v>
       </c>
       <c r="U39" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V39" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W39" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="X39" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AA39" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.54</v>
+        <v>1.29</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.7</v>
+        <v>2.15</v>
       </c>
       <c r="M40" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="N40" t="n">
-        <v>1.78</v>
+        <v>3.4</v>
       </c>
       <c r="O40" t="n">
-        <v>5.4</v>
+        <v>2.64</v>
       </c>
       <c r="P40" t="n">
-        <v>2.06</v>
+        <v>1.79</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.48</v>
+        <v>4.25</v>
       </c>
       <c r="R40" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="S40" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="T40" t="n">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="U40" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="V40" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W40" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X40" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Z40" t="n">
         <v>1.44</v>
       </c>
-      <c r="X40" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AA40" t="n">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.16</v>
+        <v>1.71</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.67</v>
+        <v>2.88</v>
       </c>
       <c r="M41" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N41" t="n">
-        <v>4.33</v>
+        <v>2.49</v>
       </c>
       <c r="O41" t="n">
-        <v>2.19</v>
+        <v>3.74</v>
       </c>
       <c r="P41" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.42</v>
+        <v>3</v>
       </c>
       <c r="R41" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S41" t="n">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="T41" t="n">
-        <v>3.03</v>
+        <v>2.88</v>
       </c>
       <c r="U41" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V41" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="W41" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="X41" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.44</v>
+        <v>4</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.06</v>
+        <v>1.37</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6354,7 +6354,7 @@
         <v>1.86</v>
       </c>
       <c r="O46" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="P46" t="n">
         <v>2.41</v>
@@ -6363,22 +6363,22 @@
         <v>2.35</v>
       </c>
       <c r="R46" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S46" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="T46" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="U46" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V46" t="n">
         <v>1.01</v>
       </c>
       <c r="W46" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X46" t="n">
         <v>5.95</v>
@@ -6399,7 +6399,7 @@
         <v>1.36</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>1.25</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.01</v>
+        <v>1.81</v>
       </c>
       <c r="M48" t="n">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="N48" t="n">
-        <v>3.53</v>
+        <v>3.9</v>
       </c>
       <c r="O48" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.81</v>
+        <v>2.01</v>
       </c>
       <c r="M49" t="n">
-        <v>3.35</v>
+        <v>2.94</v>
       </c>
       <c r="N49" t="n">
-        <v>3.9</v>
+        <v>3.53</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="M50" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="N50" t="n">
-        <v>2.27</v>
+        <v>2.67</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="M51" t="n">
-        <v>3.53</v>
+        <v>3.45</v>
       </c>
       <c r="N51" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="O51" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.17</v>
+        <v>1.73</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AA51" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="M52" t="n">
-        <v>3.45</v>
+        <v>3.53</v>
       </c>
       <c r="N52" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -936,52 +936,52 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="P4" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.34</v>
+        <v>3.85</v>
       </c>
       <c r="R4" t="n">
         <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="T4" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="U4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X4" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Z4" t="n">
         <v>1.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
         <v>2.37</v>
@@ -1455,10 +1455,10 @@
         <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>2.04</v>
+        <v>2.19</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="R8" t="n">
         <v>1.38</v>
@@ -1467,25 +1467,25 @@
         <v>2.73</v>
       </c>
       <c r="T8" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="U8" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="V8" t="n">
         <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="X8" t="n">
         <v>3.22</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AA8" t="n">
         <v>3.31</v>
@@ -1494,7 +1494,7 @@
         <v>1.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AD8" t="n">
         <v>2</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.46</v>
+        <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1839,52 +1839,52 @@
         <v>1.7</v>
       </c>
       <c r="O11" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="U11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="X11" t="n">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Z11" t="n">
         <v>2.02</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="AB11" t="n">
         <v>1.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2604,34 +2604,34 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="M17" t="n">
         <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>5.3</v>
+        <v>4.75</v>
       </c>
       <c r="O17" t="n">
         <v>2.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Q17" t="n">
         <v>5.25</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="T17" t="n">
         <v>2.77</v>
       </c>
       <c r="U17" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="V17" t="n">
         <v>1.01</v>
@@ -2640,26 +2640,26 @@
         <v>1.35</v>
       </c>
       <c r="X17" t="n">
-        <v>3.36</v>
+        <v>3.22</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.85</v>
       </c>
-      <c r="Z17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AE17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="N18" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>6.55</v>
       </c>
       <c r="P18" t="n">
-        <v>2.04</v>
+        <v>2.27</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.98</v>
+        <v>1.93</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="T18" t="n">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="U18" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
         <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X18" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="Z18" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.69</v>
+        <v>2.97</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.61</v>
+        <v>1.98</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.22</v>
+        <v>1.74</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="M19" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="O19" t="n">
-        <v>6.55</v>
+        <v>3.14</v>
       </c>
       <c r="P19" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.93</v>
+        <v>2.94</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>2.98</v>
+        <v>3.14</v>
       </c>
       <c r="T19" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X19" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z19" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z19" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AA19" t="n">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.03</v>
+        <v>1.61</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.74</v>
+        <v>2.22</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.21</v>
+        <v>1.45</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.09</v>
+        <v>1.41</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N20" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="O20" t="n">
         <v>2.72</v>
@@ -3012,7 +3012,7 @@
         <v>1.52</v>
       </c>
       <c r="S20" t="n">
-        <v>2.34</v>
+        <v>2.49</v>
       </c>
       <c r="T20" t="n">
         <v>3.5</v>
@@ -3024,10 +3024,10 @@
         <v>1.05</v>
       </c>
       <c r="W20" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="X20" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="Y20" t="n">
         <v>2.51</v>
@@ -3061,7 +3061,7 @@
         <v>1.34</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3129,7 +3129,7 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4.13</v>
+        <v>4.19</v>
       </c>
       <c r="P21" t="n">
         <v>2.2</v>
@@ -3138,43 +3138,43 @@
         <v>2.51</v>
       </c>
       <c r="R21" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="S21" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="T21" t="n">
         <v>2.38</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="X21" t="n">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AH21" t="n">
         <v>1.24</v>
@@ -3249,16 +3249,16 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.25</v>
+        <v>1.72</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="O22" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="P22" t="n">
         <v>2.01</v>
@@ -3267,7 +3267,7 @@
         <v>5.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S22" t="n">
         <v>2.57</v>
@@ -3282,10 +3282,10 @@
         <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="X22" t="n">
-        <v>2.3</v>
+        <v>2.77</v>
       </c>
       <c r="Y22" t="n">
         <v>2.46</v>
@@ -3300,10 +3300,10 @@
         <v>1.12</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3378,25 +3378,25 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="N23" t="n">
-        <v>4.05</v>
+        <v>3.92</v>
       </c>
       <c r="O23" t="n">
         <v>2.99</v>
       </c>
       <c r="P23" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Q23" t="n">
         <v>5.15</v>
       </c>
       <c r="R23" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="S23" t="n">
         <v>2.03</v>
@@ -3411,10 +3411,10 @@
         <v>1.16</v>
       </c>
       <c r="W23" t="n">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="X23" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="Y23" t="n">
         <v>2.97</v>
@@ -3429,10 +3429,10 @@
         <v>1.06</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.46</v>
+        <v>2.78</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="O24" t="n">
         <v>2.5</v>
       </c>
       <c r="P24" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.15</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="T24" t="n">
-        <v>3.22</v>
+        <v>2.55</v>
       </c>
       <c r="U24" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="X24" t="n">
-        <v>2.95</v>
+        <v>3.65</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.82</v>
+        <v>2.45</v>
       </c>
       <c r="M25" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="N25" t="n">
-        <v>3.67</v>
+        <v>2.51</v>
       </c>
       <c r="O25" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.48</v>
+        <v>3.18</v>
       </c>
       <c r="R25" t="n">
         <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="U25" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W25" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X25" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.75</v>
+        <v>1.49</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,58 +3765,58 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="M26" t="n">
-        <v>3.33</v>
+        <v>3.38</v>
       </c>
       <c r="N26" t="n">
-        <v>3.63</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="P26" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="R26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U26" t="n">
         <v>1.36</v>
       </c>
-      <c r="S26" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.42</v>
-      </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AB26" t="n">
         <v>1.25</v>
       </c>
-      <c r="X26" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AC26" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AD26" t="n">
         <v>2</v>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.45</v>
+        <v>1.82</v>
       </c>
       <c r="M27" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="N27" t="n">
-        <v>2.6</v>
+        <v>3.67</v>
       </c>
       <c r="O27" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="P27" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.15</v>
+        <v>4.48</v>
       </c>
       <c r="R27" t="n">
         <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="T27" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="U27" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB27" t="n">
         <v>1.25</v>
       </c>
-      <c r="X27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z27" t="n">
+      <c r="AC27" t="n">
         <v>1.85</v>
       </c>
-      <c r="AA27" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.34</v>
+        <v>5.4</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>3.99</v>
       </c>
       <c r="N28" t="n">
-        <v>3.09</v>
+        <v>1.46</v>
       </c>
       <c r="O28" t="n">
-        <v>2.75</v>
+        <v>5.68</v>
       </c>
       <c r="P28" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.82</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="S28" t="n">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="T28" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="V28" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W28" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="X28" t="n">
-        <v>3.33</v>
+        <v>4.07</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.06</v>
+        <v>1.67</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.76</v>
+        <v>2.09</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.52</v>
+        <v>2.69</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.62</v>
+        <v>1.1</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="M29" t="n">
-        <v>3.69</v>
+        <v>3.1</v>
       </c>
       <c r="N29" t="n">
-        <v>3.89</v>
+        <v>3.85</v>
       </c>
       <c r="O29" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="P29" t="n">
-        <v>2.33</v>
+        <v>1.96</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>5.15</v>
       </c>
       <c r="R29" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="S29" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="T29" t="n">
-        <v>2.34</v>
+        <v>3.22</v>
       </c>
       <c r="U29" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="V29" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W29" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="X29" t="n">
-        <v>4.33</v>
+        <v>2.95</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.35</v>
+        <v>3.9</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5.4</v>
+        <v>1.73</v>
       </c>
       <c r="M30" t="n">
-        <v>3.99</v>
+        <v>3.8</v>
       </c>
       <c r="N30" t="n">
-        <v>1.46</v>
+        <v>3.85</v>
       </c>
       <c r="O30" t="n">
-        <v>5.68</v>
+        <v>2.25</v>
       </c>
       <c r="P30" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S30" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="T30" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="U30" t="n">
         <v>1.53</v>
       </c>
       <c r="V30" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W30" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X30" t="n">
-        <v>4.07</v>
+        <v>4.55</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>2.4</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.1</v>
+        <v>1.91</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4539,34 +4539,34 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.72</v>
+        <v>3.85</v>
       </c>
       <c r="M32" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="N32" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>4.56</v>
+        <v>4.4</v>
       </c>
       <c r="P32" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="Q32" t="n">
         <v>2.55</v>
       </c>
       <c r="R32" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S32" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="T32" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U32" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="V32" t="n">
         <v>1.02</v>
@@ -4575,25 +4575,25 @@
         <v>1.33</v>
       </c>
       <c r="X32" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.19</v>
+        <v>3.78</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q33" t="n">
         <v>2.85</v>
       </c>
-      <c r="M33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N33" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="M34" t="n">
-        <v>4.9</v>
+        <v>4.75</v>
       </c>
       <c r="N34" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4926,46 +4926,46 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="M35" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N35" t="n">
-        <v>2.97</v>
+        <v>2.87</v>
       </c>
       <c r="O35" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="P35" t="n">
-        <v>2.43</v>
+        <v>2.31</v>
       </c>
       <c r="Q35" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S35" t="n">
         <v>3.35</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
       </c>
       <c r="T35" t="n">
         <v>2.23</v>
       </c>
       <c r="U35" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W35" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X35" t="n">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="Z35" t="n">
         <v>2.25</v>
@@ -4974,10 +4974,10 @@
         <v>2.5</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AD35" t="n">
         <v>2.35</v>
@@ -4996,7 +4996,7 @@
         <v>1.22</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,22 +5055,22 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.03</v>
+        <v>2.85</v>
       </c>
       <c r="M36" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>3.01</v>
+        <v>2.3</v>
       </c>
       <c r="O36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -5079,37 +5079,37 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.42</v>
+        <v>2</v>
       </c>
       <c r="M37" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="N37" t="n">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="O37" t="n">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="P37" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T37" t="n">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="U37" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X37" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.46</v>
+        <v>1.2</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,77 +5313,77 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="M38" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="N38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S38" t="n">
         <v>2.23</v>
       </c>
-      <c r="O38" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.43</v>
-      </c>
       <c r="T38" t="n">
-        <v>3.16</v>
+        <v>3.75</v>
       </c>
       <c r="U38" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V38" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="W38" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
         <v>1.4</v>
       </c>
-      <c r="X38" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD38" t="n">
+      <c r="AH38" t="n">
         <v>1.71</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.27</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="M40" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="N40" t="n">
-        <v>3.4</v>
+        <v>2.23</v>
       </c>
       <c r="O40" t="n">
-        <v>2.64</v>
+        <v>4.21</v>
       </c>
       <c r="P40" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.25</v>
+        <v>2.83</v>
       </c>
       <c r="R40" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="S40" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="T40" t="n">
-        <v>3.75</v>
+        <v>3.16</v>
       </c>
       <c r="U40" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V40" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="W40" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="X40" t="n">
-        <v>2.38</v>
+        <v>2.69</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.82</v>
+        <v>2.2</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AA40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.71</v>
+        <v>1.27</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5700,22 +5700,22 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="M41" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N41" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="O41" t="n">
-        <v>3.74</v>
+        <v>3.79</v>
       </c>
       <c r="P41" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="Q41" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="R41" t="n">
         <v>1.5</v>
@@ -5724,37 +5724,37 @@
         <v>2.63</v>
       </c>
       <c r="T41" t="n">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="U41" t="n">
         <v>1.33</v>
       </c>
       <c r="V41" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W41" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="X41" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AA41" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AB41" t="n">
         <v>1.21</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.67</v>
+        <v>2.32</v>
       </c>
       <c r="M43" t="n">
-        <v>3.45</v>
+        <v>3.29</v>
       </c>
       <c r="N43" t="n">
-        <v>4.33</v>
+        <v>3.02</v>
       </c>
       <c r="O43" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>5.42</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6087,31 +6087,31 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="M44" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="N44" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="O44" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="P44" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q44" t="n">
         <v>3.4</v>
       </c>
       <c r="R44" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S44" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="T44" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="U44" t="n">
         <v>1.44</v>
@@ -6120,28 +6120,28 @@
         <v>1.02</v>
       </c>
       <c r="W44" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="X44" t="n">
-        <v>3.52</v>
+        <v>3.44</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="Z44" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="AB44" t="n">
         <v>1.33</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6216,28 +6216,28 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="M45" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="N45" t="n">
-        <v>3.53</v>
+        <v>3.25</v>
       </c>
       <c r="O45" t="n">
         <v>2.9</v>
       </c>
       <c r="P45" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="R45" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="S45" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="T45" t="n">
         <v>3.3</v>
@@ -6246,31 +6246,31 @@
         <v>1.3</v>
       </c>
       <c r="V45" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W45" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="X45" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AA45" t="n">
-        <v>4.7</v>
+        <v>4.33</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6474,28 +6474,28 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="M47" t="n">
-        <v>3.09</v>
+        <v>3.28</v>
       </c>
       <c r="N47" t="n">
-        <v>2.51</v>
+        <v>2.66</v>
       </c>
       <c r="O47" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="P47" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="R47" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S47" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="T47" t="n">
         <v>3.1</v>
@@ -6504,22 +6504,22 @@
         <v>1.32</v>
       </c>
       <c r="V47" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W47" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="X47" t="n">
-        <v>3.09</v>
+        <v>3.13</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="AB47" t="n">
         <v>1.18</v>
@@ -6528,7 +6528,7 @@
         <v>1.85</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="M48" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N48" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.01</v>
+        <v>1.81</v>
       </c>
       <c r="M49" t="n">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="N49" t="n">
-        <v>3.53</v>
+        <v>3.9</v>
       </c>
       <c r="O49" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AA49" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M50" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O50" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X50" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Y50" t="n">
         <v>2.4</v>
       </c>
-      <c r="M50" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N50" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Z50" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -7119,31 +7119,31 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="M52" t="n">
-        <v>3.53</v>
+        <v>3.75</v>
       </c>
       <c r="N52" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="O52" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="P52" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="R52" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S52" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="T52" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="U52" t="n">
         <v>1.33</v>
@@ -7152,29 +7152,29 @@
         <v>1.01</v>
       </c>
       <c r="W52" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X52" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="Z52" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD52" t="n">
         <v>1.7</v>
       </c>
-      <c r="AA52" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AE52" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH52" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -1839,19 +1839,19 @@
         <v>1.7</v>
       </c>
       <c r="O11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="R11" t="n">
         <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="T11" t="n">
         <v>2.59</v>
@@ -1863,22 +1863,22 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AA11" t="n">
         <v>2.83</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC11" t="n">
         <v>1.78</v>
@@ -1900,7 +1900,7 @@
         <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.17</v>
+        <v>2.36</v>
       </c>
       <c r="M14" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N14" t="n">
         <v>3.15</v>
       </c>
-      <c r="N14" t="n">
-        <v>3.28</v>
-      </c>
       <c r="O14" t="n">
-        <v>2.81</v>
+        <v>2.69</v>
       </c>
       <c r="P14" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.92</v>
+        <v>3.58</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S14" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="T14" t="n">
-        <v>3.16</v>
+        <v>3.35</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V14" t="n">
         <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="X14" t="n">
-        <v>2.74</v>
+        <v>2.59</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.21</v>
+        <v>2.49</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.98</v>
+        <v>4.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.36</v>
+        <v>2.48</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="N15" t="n">
-        <v>7.9</v>
+        <v>2.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.48</v>
+        <v>1.36</v>
       </c>
       <c r="M16" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>2.4</v>
+        <v>7</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>4.75</v>
+        <v>2.4</v>
       </c>
       <c r="O17" t="n">
-        <v>2.2</v>
+        <v>3.14</v>
       </c>
       <c r="P17" t="n">
         <v>2.18</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.25</v>
+        <v>2.94</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="T17" t="n">
-        <v>2.77</v>
+        <v>2.52</v>
       </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V17" t="n">
         <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
-        <v>3.22</v>
+        <v>4.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.91</v>
+        <v>1.61</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.85</v>
+        <v>2.22</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.1</v>
+        <v>1.41</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5.7</v>
+        <v>1.7</v>
       </c>
       <c r="M18" t="n">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>1.43</v>
+        <v>4.5</v>
       </c>
       <c r="O18" t="n">
-        <v>6.55</v>
+        <v>2.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.93</v>
+        <v>5.25</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="U18" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V18" t="n">
         <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="X18" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.97</v>
+        <v>3.32</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.6</v>
+        <v>5.7</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>4.05</v>
       </c>
       <c r="N19" t="n">
-        <v>2.4</v>
+        <v>1.43</v>
       </c>
       <c r="O19" t="n">
-        <v>3.14</v>
+        <v>6.71</v>
       </c>
       <c r="P19" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.94</v>
+        <v>1.95</v>
       </c>
       <c r="R19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB19" t="n">
         <v>1.3</v>
       </c>
-      <c r="S19" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AC19" t="n">
-        <v>1.61</v>
+        <v>1.98</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.22</v>
+        <v>1.74</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.41</v>
+        <v>1.07</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="N20" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="O20" t="n">
         <v>2.72</v>
@@ -3061,7 +3061,7 @@
         <v>1.34</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3135,10 +3135,10 @@
         <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
         <v>3.15</v>
@@ -3147,7 +3147,7 @@
         <v>2.38</v>
       </c>
       <c r="U21" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="V21" t="n">
         <v>1.01</v>
@@ -3171,7 +3171,7 @@
         <v>1.28</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AD21" t="n">
         <v>2</v>
@@ -3249,77 +3249,77 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N22" t="n">
         <v>4.4</v>
       </c>
       <c r="O22" t="n">
-        <v>2.32</v>
+        <v>2.56</v>
       </c>
       <c r="P22" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.2</v>
+        <v>4.42</v>
       </c>
       <c r="R22" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="S22" t="n">
-        <v>2.57</v>
+        <v>2.36</v>
       </c>
       <c r="T22" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U22" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W22" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="X22" t="n">
-        <v>2.77</v>
+        <v>2.49</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="AB22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
         <v>1.12</v>
       </c>
-      <c r="AC22" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3387,19 +3387,19 @@
         <v>3.92</v>
       </c>
       <c r="O23" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
         <v>1.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.15</v>
+        <v>4.72</v>
       </c>
       <c r="R23" t="n">
         <v>1.68</v>
       </c>
       <c r="S23" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="T23" t="n">
         <v>4.25</v>
@@ -3411,7 +3411,7 @@
         <v>1.16</v>
       </c>
       <c r="W23" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="X23" t="n">
         <v>2.03</v>
@@ -3420,13 +3420,13 @@
         <v>2.97</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AA23" t="n">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AC23" t="n">
         <v>2.78</v>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,58 +3507,58 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="N24" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="O24" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="P24" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="T24" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="U24" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AB24" t="n">
         <v>1.25</v>
       </c>
-      <c r="X24" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AC24" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="AD24" t="n">
         <v>2</v>
@@ -3577,7 +3577,7 @@
         <v>1.26</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,58 +3636,58 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="M25" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>2.51</v>
+        <v>3.7</v>
       </c>
       <c r="O25" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="P25" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.18</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="T25" t="n">
-        <v>2.74</v>
+        <v>2.55</v>
       </c>
       <c r="U25" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
         <v>1.25</v>
       </c>
       <c r="X25" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.14</v>
+        <v>2.87</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AD25" t="n">
         <v>2</v>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.15</v>
+        <v>5.4</v>
       </c>
       <c r="M26" t="n">
-        <v>3.38</v>
+        <v>3.99</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>1.46</v>
       </c>
       <c r="O26" t="n">
-        <v>2.75</v>
+        <v>5.74</v>
       </c>
       <c r="P26" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.82</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S26" t="n">
-        <v>2.7</v>
+        <v>3.12</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="U26" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V26" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="X26" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.06</v>
+        <v>1.58</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.72</v>
+        <v>2.07</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.54</v>
+        <v>2.62</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AD26" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>2.39</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.62</v>
+        <v>1.1</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.82</v>
+        <v>2.47</v>
       </c>
       <c r="M27" t="n">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="N27" t="n">
-        <v>3.67</v>
+        <v>2.5</v>
       </c>
       <c r="O27" t="n">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="P27" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.48</v>
+        <v>3.2</v>
       </c>
       <c r="R27" t="n">
         <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>2.8</v>
+        <v>3.06</v>
       </c>
       <c r="T27" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W27" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X27" t="n">
-        <v>3.1</v>
+        <v>3.68</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>5.4</v>
+        <v>1.82</v>
       </c>
       <c r="M28" t="n">
-        <v>3.99</v>
+        <v>3.36</v>
       </c>
       <c r="N28" t="n">
-        <v>1.46</v>
+        <v>3.67</v>
       </c>
       <c r="O28" t="n">
-        <v>5.68</v>
+        <v>2.4</v>
       </c>
       <c r="P28" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>4.48</v>
       </c>
       <c r="R28" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="T28" t="n">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="U28" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="X28" t="n">
-        <v>4.07</v>
+        <v>3.1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.09</v>
+        <v>1.76</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.69</v>
+        <v>3.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>2.4</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.1</v>
+        <v>1.75</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,62 +4152,62 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="M29" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="N29" t="n">
         <v>3.85</v>
       </c>
       <c r="O29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X29" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA29" t="n">
         <v>2.5</v>
       </c>
-      <c r="P29" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y29" t="n">
+      <c r="AB29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD29" t="n">
         <v>2.3</v>
       </c>
-      <c r="Z29" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AE29" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q30" t="n">
         <v>3.85</v>
       </c>
-      <c r="O30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>4</v>
-      </c>
       <c r="R30" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="S30" t="n">
-        <v>3.4</v>
+        <v>2.66</v>
       </c>
       <c r="T30" t="n">
-        <v>2.34</v>
+        <v>3.16</v>
       </c>
       <c r="U30" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="V30" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="X30" t="n">
-        <v>4.55</v>
+        <v>2.95</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.54</v>
+        <v>2.27</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.3</v>
+        <v>1.61</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4542,25 +4542,25 @@
         <v>3.85</v>
       </c>
       <c r="M32" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
         <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="P32" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.55</v>
+        <v>2.71</v>
       </c>
       <c r="R32" t="n">
         <v>1.42</v>
       </c>
       <c r="S32" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="T32" t="n">
         <v>2.88</v>
@@ -4569,22 +4569,22 @@
         <v>1.36</v>
       </c>
       <c r="V32" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W32" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="X32" t="n">
         <v>2.85</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="Z32" t="n">
         <v>1.65</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.78</v>
+        <v>4</v>
       </c>
       <c r="AB32" t="n">
         <v>1.22</v>
@@ -4593,7 +4593,7 @@
         <v>1.96</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>1.28</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.48</v>
+        <v>2.85</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5.5</v>
+        <v>2.48</v>
       </c>
       <c r="M34" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>1.42</v>
+        <v>2.5</v>
       </c>
       <c r="O34" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="P34" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.9</v>
+        <v>2.85</v>
       </c>
       <c r="R34" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="S34" t="n">
-        <v>4.25</v>
+        <v>3.36</v>
       </c>
       <c r="T34" t="n">
-        <v>1.9</v>
+        <v>2.29</v>
       </c>
       <c r="U34" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W34" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X34" t="n">
-        <v>6.45</v>
+        <v>5</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.97</v>
+        <v>2.35</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.87</v>
+        <v>1.49</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.13</v>
+        <v>1.46</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,74 +4926,74 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N35" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="O35" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="P35" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="R35" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="S35" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="T35" t="n">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="U35" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="V35" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X35" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
         <v>1.2</v>
-      </c>
-      <c r="X35" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.22</v>
       </c>
       <c r="AH35" t="n">
         <v>1.67</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.85</v>
+        <v>2.14</v>
       </c>
       <c r="M36" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N36" t="n">
-        <v>2.3</v>
+        <v>2.87</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Y36" t="n">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,77 +5184,77 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="M37" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="N37" t="n">
-        <v>2.9</v>
+        <v>1.42</v>
       </c>
       <c r="O37" t="n">
-        <v>2.56</v>
+        <v>4.8</v>
       </c>
       <c r="P37" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="R37" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="S37" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="T37" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="U37" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X37" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
         <v>1.15</v>
       </c>
-      <c r="X37" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AH37" t="n">
-        <v>1.67</v>
+        <v>1.13</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5331,7 +5331,7 @@
         <v>4.25</v>
       </c>
       <c r="R38" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="S38" t="n">
         <v>2.23</v>
@@ -5340,7 +5340,7 @@
         <v>3.75</v>
       </c>
       <c r="U38" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="V38" t="n">
         <v>1.08</v>
@@ -5352,10 +5352,10 @@
         <v>2.38</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AA38" t="n">
         <v>5</v>
@@ -5367,7 +5367,7 @@
         <v>2.2</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="M39" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="N39" t="n">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="O39" t="n">
-        <v>4.65</v>
+        <v>4.26</v>
       </c>
       <c r="P39" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="R39" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="S39" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="T39" t="n">
-        <v>3.28</v>
+        <v>3.17</v>
       </c>
       <c r="U39" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="V39" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W39" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="X39" t="n">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AA39" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="M40" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="N40" t="n">
-        <v>2.23</v>
+        <v>1.78</v>
       </c>
       <c r="O40" t="n">
-        <v>4.21</v>
+        <v>4.76</v>
       </c>
       <c r="P40" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.83</v>
+        <v>2.67</v>
       </c>
       <c r="R40" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S40" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="T40" t="n">
-        <v>3.16</v>
+        <v>3.28</v>
       </c>
       <c r="U40" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="V40" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W40" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="X40" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AA40" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AC40" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.81</v>
+        <v>1.7</v>
       </c>
       <c r="M41" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>2.47</v>
+        <v>4.5</v>
       </c>
       <c r="O41" t="n">
-        <v>3.79</v>
+        <v>2.2</v>
       </c>
       <c r="P41" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.35</v>
+        <v>5.47</v>
       </c>
       <c r="R41" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="S41" t="n">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="T41" t="n">
-        <v>3.28</v>
+        <v>3.01</v>
       </c>
       <c r="U41" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V41" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W41" t="n">
         <v>1.33</v>
       </c>
       <c r="X41" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.9</v>
+        <v>3.44</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.55</v>
+        <v>1.18</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.41</v>
+        <v>1.97</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.7</v>
+        <v>3.09</v>
       </c>
       <c r="M42" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N42" t="n">
-        <v>4.6</v>
+        <v>2.14</v>
       </c>
       <c r="O42" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="P42" t="n">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="R42" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S42" t="n">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
       <c r="T42" t="n">
-        <v>3.03</v>
+        <v>2.88</v>
       </c>
       <c r="U42" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V42" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="W42" t="n">
         <v>1.33</v>
       </c>
       <c r="X42" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Y42" t="n">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.18</v>
+        <v>1.55</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.97</v>
+        <v>1.4</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="M43" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="N43" t="n">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6087,19 +6087,19 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="M44" t="n">
-        <v>3.15</v>
+        <v>3.38</v>
       </c>
       <c r="N44" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O44" t="n">
         <v>2.9</v>
       </c>
       <c r="P44" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="Q44" t="n">
         <v>3.4</v>
@@ -6111,37 +6111,37 @@
         <v>3</v>
       </c>
       <c r="T44" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="U44" t="n">
         <v>1.44</v>
       </c>
       <c r="V44" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W44" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X44" t="n">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="Y44" t="n">
         <v>1.9</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC44" t="n">
         <v>1.7</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.62</v>
+        <v>2.11</v>
       </c>
       <c r="M47" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="N47" t="n">
-        <v>2.66</v>
+        <v>3.5</v>
       </c>
       <c r="O47" t="n">
-        <v>3.34</v>
+        <v>2.7</v>
       </c>
       <c r="P47" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="R47" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S47" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T47" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="U47" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V47" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W47" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="X47" t="n">
-        <v>3.13</v>
+        <v>2.9</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AA47" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M48" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
         <v>2.05</v>
       </c>
-      <c r="M48" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N48" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O48" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P48" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>4</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X48" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>2.12</v>
-      </c>
       <c r="Z48" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.81</v>
+        <v>2.7</v>
       </c>
       <c r="M49" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="N49" t="n">
-        <v>3.9</v>
+        <v>2.63</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6861,22 +6861,22 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="M50" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="N50" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O50" t="n">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="P50" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="R50" t="n">
         <v>1.53</v>
@@ -6900,10 +6900,10 @@
         <v>2.57</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AA50" t="n">
         <v>4.33</v>
@@ -6912,10 +6912,10 @@
         <v>1.15</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>1.34</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -7122,31 +7122,31 @@
         <v>1.65</v>
       </c>
       <c r="M52" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N52" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="O52" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="P52" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.75</v>
+        <v>5.9</v>
       </c>
       <c r="R52" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S52" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="T52" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="U52" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V52" t="n">
         <v>1.01</v>
@@ -7155,13 +7155,13 @@
         <v>1.31</v>
       </c>
       <c r="X52" t="n">
-        <v>2.94</v>
+        <v>3.17</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AA52" t="n">
         <v>3.83</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -936,25 +936,25 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.95</v>
+        <v>2.78</v>
       </c>
       <c r="P4" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.85</v>
+        <v>3.78</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="T4" t="n">
         <v>2.5</v>
       </c>
       <c r="U4" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
@@ -972,16 +972,16 @@
         <v>1.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1446,19 +1446,19 @@
         <v>2.47</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="O8" t="n">
         <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>2.19</v>
+        <v>2.02</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="R8" t="n">
         <v>1.38</v>
@@ -1467,31 +1467,31 @@
         <v>2.73</v>
       </c>
       <c r="T8" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
         <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="X8" t="n">
         <v>3.22</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AA8" t="n">
         <v>3.31</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AC8" t="n">
         <v>1.7</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1854,7 +1854,7 @@
         <v>3.02</v>
       </c>
       <c r="T11" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="U11" t="n">
         <v>1.42</v>
@@ -1878,10 +1878,10 @@
         <v>2.83</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AD11" t="n">
         <v>2</v>
@@ -1900,7 +1900,7 @@
         <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2481,7 +2481,7 @@
         <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="O16" t="n">
         <v>1.85</v>
@@ -2496,7 +2496,7 @@
         <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
         <v>2.65</v>
@@ -2514,10 +2514,10 @@
         <v>3.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AA16" t="n">
         <v>3.08</v>
@@ -2526,7 +2526,7 @@
         <v>1.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="AD16" t="n">
         <v>1.67</v>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2733,16 +2733,16 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="M18" t="n">
         <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="O18" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="P18" t="n">
         <v>2.28</v>
@@ -2769,25 +2769,25 @@
         <v>1.35</v>
       </c>
       <c r="X18" t="n">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="Z18" t="n">
         <v>1.85</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="AB18" t="n">
         <v>1.27</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="M19" t="n">
-        <v>4.05</v>
+        <v>4.7</v>
       </c>
       <c r="N19" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="O19" t="n">
         <v>6.71</v>
@@ -2883,13 +2883,13 @@
         <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="T19" t="n">
         <v>2.75</v>
       </c>
       <c r="U19" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
         <v>1.04</v>
@@ -2901,13 +2901,13 @@
         <v>3.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="AB19" t="n">
         <v>1.3</v>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="N20" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O20" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="P20" t="n">
         <v>2.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="R20" t="n">
         <v>1.52</v>
@@ -3024,10 +3024,10 @@
         <v>1.05</v>
       </c>
       <c r="W20" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="X20" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="Y20" t="n">
         <v>2.51</v>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AH20" t="n">
         <v>1.71</v>
@@ -3249,16 +3249,16 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.74</v>
+        <v>2.25</v>
       </c>
       <c r="M22" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="O22" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="P22" t="n">
         <v>1.96</v>
@@ -3267,10 +3267,10 @@
         <v>4.42</v>
       </c>
       <c r="R22" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="S22" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T22" t="n">
         <v>3.6</v>
@@ -3282,16 +3282,16 @@
         <v>1.04</v>
       </c>
       <c r="W22" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="X22" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="Y22" t="n">
         <v>2.43</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AA22" t="n">
         <v>4.9</v>
@@ -3300,10 +3300,10 @@
         <v>1.11</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>1.12</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3378,16 +3378,16 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>2.69</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>3.92</v>
+        <v>4.05</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="P23" t="n">
         <v>1.75</v>
@@ -3396,10 +3396,10 @@
         <v>4.72</v>
       </c>
       <c r="R23" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="S23" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="T23" t="n">
         <v>4.25</v>
@@ -3408,31 +3408,31 @@
         <v>1.16</v>
       </c>
       <c r="V23" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="W23" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="X23" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="Y23" t="n">
         <v>2.97</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.78</v>
+        <v>2.46</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="M24" t="n">
-        <v>3.38</v>
+        <v>3.05</v>
       </c>
       <c r="N24" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.82</v>
+        <v>4.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="T24" t="n">
-        <v>2.8</v>
+        <v>3.16</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="X24" t="n">
-        <v>3.15</v>
+        <v>2.95</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.54</v>
+        <v>3.9</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3642,7 +3642,7 @@
         <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>3.7</v>
+        <v>3.56</v>
       </c>
       <c r="O25" t="n">
         <v>2.5</v>
@@ -3678,7 +3678,7 @@
         <v>1.92</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AA25" t="n">
         <v>2.87</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5.4</v>
+        <v>1.82</v>
       </c>
       <c r="M26" t="n">
-        <v>3.99</v>
+        <v>3.36</v>
       </c>
       <c r="N26" t="n">
-        <v>1.46</v>
+        <v>3.67</v>
       </c>
       <c r="O26" t="n">
-        <v>5.74</v>
+        <v>2.4</v>
       </c>
       <c r="P26" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>4.48</v>
       </c>
       <c r="R26" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>3.12</v>
+        <v>2.69</v>
       </c>
       <c r="T26" t="n">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="V26" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W26" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="X26" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.58</v>
+        <v>1.94</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.07</v>
+        <v>1.76</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>2.39</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.1</v>
+        <v>1.77</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,77 +3894,77 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.47</v>
+        <v>1.81</v>
       </c>
       <c r="M27" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P27" t="n">
         <v>2.5</v>
       </c>
-      <c r="O27" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.11</v>
-      </c>
       <c r="Q27" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S27" t="n">
-        <v>3.06</v>
+        <v>3.4</v>
       </c>
       <c r="T27" t="n">
-        <v>2.74</v>
+        <v>2.34</v>
       </c>
       <c r="U27" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="V27" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W27" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X27" t="n">
-        <v>3.68</v>
+        <v>4.55</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.9</v>
+        <v>1.54</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.14</v>
+        <v>2.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AD27" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH27" t="n">
         <v>2</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.82</v>
+        <v>5.4</v>
       </c>
       <c r="M28" t="n">
-        <v>3.36</v>
+        <v>3.99</v>
       </c>
       <c r="N28" t="n">
-        <v>3.67</v>
+        <v>1.46</v>
       </c>
       <c r="O28" t="n">
-        <v>2.4</v>
+        <v>5.74</v>
       </c>
       <c r="P28" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.48</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="T28" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W28" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="X28" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.94</v>
+        <v>1.58</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.76</v>
+        <v>2.07</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.6</v>
+        <v>2.59</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.75</v>
+        <v>1.1</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.73</v>
+        <v>2.55</v>
       </c>
       <c r="M29" t="n">
-        <v>3.8</v>
+        <v>3.38</v>
       </c>
       <c r="N29" t="n">
-        <v>3.85</v>
+        <v>2.5</v>
       </c>
       <c r="O29" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="P29" t="n">
-        <v>2.36</v>
+        <v>2.11</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>3.08</v>
       </c>
       <c r="R29" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>3.4</v>
+        <v>3.06</v>
       </c>
       <c r="T29" t="n">
-        <v>2.34</v>
+        <v>2.74</v>
       </c>
       <c r="U29" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="V29" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W29" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X29" t="n">
-        <v>4.55</v>
+        <v>3.42</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.54</v>
+        <v>1.96</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.5</v>
+        <v>3.08</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,62 +4281,62 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD30" t="n">
         <v>2</v>
       </c>
-      <c r="M30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X30" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AE30" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.89</v>
+        <v>1.59</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4422,31 +4422,31 @@
         <v>3.1</v>
       </c>
       <c r="P31" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q31" t="n">
         <v>3.18</v>
       </c>
       <c r="R31" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S31" t="n">
         <v>3.1</v>
       </c>
       <c r="T31" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="U31" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="V31" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W31" t="n">
         <v>1.22</v>
       </c>
       <c r="X31" t="n">
-        <v>4.1</v>
+        <v>3.54</v>
       </c>
       <c r="Y31" t="n">
         <v>1.78</v>
@@ -4458,10 +4458,10 @@
         <v>3</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AD31" t="n">
         <v>2.15</v>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4539,22 +4539,22 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.85</v>
+        <v>3.72</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="N32" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="O32" t="n">
-        <v>4</v>
+        <v>4.62</v>
       </c>
       <c r="P32" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="R32" t="n">
         <v>1.42</v>
@@ -4578,10 +4578,10 @@
         <v>2.85</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.24</v>
+        <v>1.94</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AA32" t="n">
         <v>4</v>
@@ -4593,7 +4593,7 @@
         <v>1.96</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.85</v>
+        <v>2</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N33" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="Y33" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.8</v>
+        <v>2.46</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.48</v>
+        <v>5.5</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="N34" t="n">
-        <v>2.5</v>
+        <v>1.42</v>
       </c>
       <c r="O34" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="P34" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.85</v>
+        <v>1.9</v>
       </c>
       <c r="R34" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="S34" t="n">
-        <v>3.36</v>
+        <v>4.25</v>
       </c>
       <c r="T34" t="n">
-        <v>2.29</v>
+        <v>1.9</v>
       </c>
       <c r="U34" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="V34" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>5</v>
+        <v>6.45</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.35</v>
+        <v>2.97</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.4</v>
+        <v>1.88</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.49</v>
+        <v>1.87</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.46</v>
+        <v>1.13</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,77 +4926,77 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>2.48</v>
       </c>
       <c r="M35" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="O35" t="n">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="P35" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="R35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X35" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
         <v>1.22</v>
       </c>
-      <c r="S35" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X35" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AH35" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.14</v>
+        <v>2.85</v>
       </c>
       <c r="M36" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>2.87</v>
+        <v>2.3</v>
       </c>
       <c r="O36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>5.5</v>
+        <v>2.14</v>
       </c>
       <c r="M37" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="N37" t="n">
-        <v>1.42</v>
+        <v>2.87</v>
       </c>
       <c r="O37" t="n">
-        <v>4.8</v>
+        <v>2.55</v>
       </c>
       <c r="P37" t="n">
-        <v>2.65</v>
+        <v>2.31</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.9</v>
+        <v>3.54</v>
       </c>
       <c r="R37" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="S37" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X37" t="n">
         <v>4.25</v>
       </c>
-      <c r="T37" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X37" t="n">
-        <v>6.45</v>
-      </c>
       <c r="Y37" t="n">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.97</v>
+        <v>2.25</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.88</v>
+        <v>2.5</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.87</v>
+        <v>1.45</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.13</v>
+        <v>1.67</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.15</v>
+        <v>4.7</v>
       </c>
       <c r="M38" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="N38" t="n">
-        <v>3.4</v>
+        <v>1.78</v>
       </c>
       <c r="O38" t="n">
-        <v>2.64</v>
+        <v>4.76</v>
       </c>
       <c r="P38" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.25</v>
+        <v>2.69</v>
       </c>
       <c r="R38" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="S38" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="T38" t="n">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="U38" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="V38" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W38" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="X38" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="AA38" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.65</v>
+        <v>1.16</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5460,16 +5460,16 @@
         <v>2.8</v>
       </c>
       <c r="R39" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S39" t="n">
         <v>2.57</v>
       </c>
       <c r="T39" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="U39" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="V39" t="n">
         <v>1.04</v>
@@ -5493,7 +5493,7 @@
         <v>1.19</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AD39" t="n">
         <v>1.71</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.7</v>
+        <v>2.15</v>
       </c>
       <c r="M40" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="N40" t="n">
-        <v>1.78</v>
+        <v>3.4</v>
       </c>
       <c r="O40" t="n">
-        <v>4.76</v>
+        <v>2.64</v>
       </c>
       <c r="P40" t="n">
-        <v>2.01</v>
+        <v>1.79</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.67</v>
+        <v>4.25</v>
       </c>
       <c r="R40" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S40" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="T40" t="n">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="U40" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="V40" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W40" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="X40" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="AA40" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.16</v>
+        <v>1.65</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5829,28 +5829,28 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="M42" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="N42" t="n">
         <v>2.14</v>
       </c>
       <c r="O42" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="P42" t="n">
         <v>1.97</v>
       </c>
       <c r="Q42" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="R42" t="n">
         <v>1.5</v>
       </c>
       <c r="S42" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="T42" t="n">
         <v>2.88</v>
@@ -5877,7 +5877,7 @@
         <v>3.9</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AC42" t="n">
         <v>1.93</v>
@@ -5899,7 +5899,7 @@
         <v>1.55</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5961,58 +5961,58 @@
         <v>2.3</v>
       </c>
       <c r="M43" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="N43" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="M44" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="N44" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O44" t="n">
         <v>2.9</v>
@@ -6129,16 +6129,16 @@
         <v>1.9</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AA44" t="n">
         <v>3.18</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AD44" t="n">
         <v>2.05</v>
@@ -6219,7 +6219,7 @@
         <v>2.25</v>
       </c>
       <c r="M45" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="N45" t="n">
         <v>3.25</v>
@@ -6234,10 +6234,10 @@
         <v>3.72</v>
       </c>
       <c r="R45" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S45" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="T45" t="n">
         <v>3.3</v>
@@ -6249,7 +6249,7 @@
         <v>1.06</v>
       </c>
       <c r="W45" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X45" t="n">
         <v>2.6</v>
@@ -6258,19 +6258,19 @@
         <v>2.45</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AA45" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AC45" t="n">
         <v>2</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.11</v>
+        <v>1.81</v>
       </c>
       <c r="M47" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N47" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="O47" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.81</v>
+        <v>2.6</v>
       </c>
       <c r="M48" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="N48" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,58 +6732,58 @@
         </is>
       </c>
       <c r="L49" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N49" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O49" t="n">
         <v>2.7</v>
       </c>
-      <c r="M49" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="N49" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="O49" t="n">
-        <v>3.3</v>
-      </c>
       <c r="P49" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="R49" t="n">
         <v>1.44</v>
       </c>
       <c r="S49" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T49" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="U49" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W49" t="n">
         <v>1.32</v>
       </c>
-      <c r="V49" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.38</v>
-      </c>
       <c r="X49" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AA49" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AD49" t="n">
         <v>1.85</v>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.49</v>
+        <v>1.31</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6864,28 +6864,28 @@
         <v>2.82</v>
       </c>
       <c r="M50" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="N50" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O50" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="P50" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="R50" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S50" t="n">
         <v>2.42</v>
       </c>
       <c r="T50" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="U50" t="n">
         <v>1.28</v>
@@ -6903,7 +6903,7 @@
         <v>2.42</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AA50" t="n">
         <v>4.33</v>
@@ -6912,10 +6912,10 @@
         <v>1.15</v>
       </c>
       <c r="AC50" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>1.34</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="M51" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N51" t="n">
-        <v>3.35</v>
+        <v>5.5</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y51" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z51" t="n">
         <v>1.73</v>
       </c>
-      <c r="Z51" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="M52" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N52" t="n">
-        <v>5.5</v>
+        <v>3.35</v>
       </c>
       <c r="O52" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="AA52" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -936,22 +936,22 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="P4" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="T4" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="U4" t="n">
         <v>1.35</v>
@@ -966,16 +966,16 @@
         <v>3.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="Z4" t="n">
         <v>1.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AC4" t="n">
         <v>1.7</v>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1443,49 +1443,49 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="N8" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="O8" t="n">
         <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.08</v>
+        <v>3.29</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S8" t="n">
-        <v>2.73</v>
+        <v>2.95</v>
       </c>
       <c r="T8" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="U8" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V8" t="n">
         <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X8" t="n">
-        <v>3.22</v>
+        <v>3.43</v>
       </c>
       <c r="Y8" t="n">
         <v>1.96</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AA8" t="n">
         <v>3.31</v>
@@ -1513,7 +1513,7 @@
         <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="N16" t="n">
-        <v>7.25</v>
+        <v>7.5</v>
       </c>
       <c r="O16" t="n">
         <v>1.85</v>
@@ -2514,7 +2514,7 @@
         <v>3.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="Z16" t="n">
         <v>1.89</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>1.55</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>2.4</v>
+        <v>5.3</v>
       </c>
       <c r="O17" t="n">
-        <v>3.14</v>
+        <v>2.28</v>
       </c>
       <c r="P17" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.94</v>
+        <v>5.25</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="T17" t="n">
-        <v>2.52</v>
+        <v>2.77</v>
       </c>
       <c r="U17" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="V17" t="n">
         <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="X17" t="n">
-        <v>4.1</v>
+        <v>3.14</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.7</v>
+        <v>3.35</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.22</v>
+        <v>1.84</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.45</v>
+        <v>1.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.41</v>
+        <v>2.14</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.55</v>
+        <v>5</v>
       </c>
       <c r="M18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X18" t="n">
         <v>3.5</v>
       </c>
-      <c r="N18" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.14</v>
-      </c>
       <c r="Y18" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.35</v>
+        <v>2.97</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.14</v>
+        <v>1.09</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="M19" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="N19" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="O19" t="n">
-        <v>6.71</v>
+        <v>3.05</v>
       </c>
       <c r="P19" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S19" t="n">
-        <v>2.98</v>
+        <v>3.14</v>
       </c>
       <c r="T19" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="V19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X19" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.74</v>
+        <v>2.19</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.09</v>
+        <v>1.41</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -3120,16 +3120,16 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O21" t="n">
-        <v>4.19</v>
+        <v>4.22</v>
       </c>
       <c r="P21" t="n">
         <v>2.2</v>
@@ -3150,31 +3150,31 @@
         <v>1.49</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X21" t="n">
-        <v>3.28</v>
+        <v>2.97</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.05</v>
+        <v>3.42</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AD21" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
         <v>1.24</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,37 +3249,37 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="M22" t="n">
         <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="O22" t="n">
-        <v>2.54</v>
+        <v>2.99</v>
       </c>
       <c r="P22" t="n">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.42</v>
+        <v>4.72</v>
       </c>
       <c r="R22" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="S22" t="n">
-        <v>2.38</v>
+        <v>2.03</v>
       </c>
       <c r="T22" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="U22" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="V22" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="W22" t="n">
         <v>1.55</v>
@@ -3288,22 +3288,22 @@
         <v>2.3</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.43</v>
+        <v>2.97</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.9</v>
+        <v>6.25</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,37 +3378,37 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M23" t="n">
         <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>4.05</v>
+        <v>3.35</v>
       </c>
       <c r="O23" t="n">
-        <v>2.99</v>
+        <v>2.54</v>
       </c>
       <c r="P23" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.72</v>
+        <v>4.42</v>
       </c>
       <c r="R23" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="S23" t="n">
-        <v>2.03</v>
+        <v>2.38</v>
       </c>
       <c r="T23" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="U23" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="V23" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="W23" t="n">
         <v>1.55</v>
@@ -3417,22 +3417,22 @@
         <v>2.3</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.97</v>
+        <v>2.43</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AA23" t="n">
-        <v>6.25</v>
+        <v>4.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.43</v>
+        <v>1.12</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,62 +3507,62 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="M24" t="n">
-        <v>3.05</v>
+        <v>3.22</v>
       </c>
       <c r="N24" t="n">
+        <v>3</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA24" t="n">
         <v>3.5</v>
       </c>
-      <c r="O24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P24" t="n">
+      <c r="AB24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD24" t="n">
         <v>2</v>
       </c>
-      <c r="Q24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AE24" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.89</v>
+        <v>1.59</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="M25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N25" t="n">
         <v>3.5</v>
       </c>
-      <c r="N25" t="n">
-        <v>3.56</v>
-      </c>
       <c r="O25" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="P25" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>4.48</v>
       </c>
       <c r="R25" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="S25" t="n">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="T25" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="U25" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="V25" t="n">
         <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X25" t="n">
-        <v>3.42</v>
+        <v>3.12</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.87</v>
+        <v>3.6</v>
       </c>
       <c r="AB25" t="n">
         <v>1.3</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="M26" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="N26" t="n">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
       <c r="O26" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.48</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="S26" t="n">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="U26" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="V26" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X26" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.6</v>
+        <v>2.87</v>
       </c>
       <c r="AB26" t="n">
         <v>1.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="M27" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="N27" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="O27" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="P27" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="S27" t="n">
-        <v>3.4</v>
+        <v>2.47</v>
       </c>
       <c r="T27" t="n">
-        <v>2.34</v>
+        <v>3.16</v>
       </c>
       <c r="U27" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="V27" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W27" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="X27" t="n">
-        <v>4.55</v>
+        <v>2.95</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.54</v>
+        <v>2.05</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.21</v>
+        <v>1.77</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.5</v>
+        <v>1.16</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.23</v>
+        <v>1.76</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AH27" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>5.4</v>
+        <v>1.69</v>
       </c>
       <c r="M28" t="n">
-        <v>3.99</v>
+        <v>3.69</v>
       </c>
       <c r="N28" t="n">
-        <v>1.46</v>
+        <v>3.89</v>
       </c>
       <c r="O28" t="n">
-        <v>5.74</v>
+        <v>2.25</v>
       </c>
       <c r="P28" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S28" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="T28" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="U28" t="n">
         <v>1.53</v>
       </c>
       <c r="V28" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W28" t="n">
         <v>1.18</v>
       </c>
       <c r="X28" t="n">
-        <v>4.2</v>
+        <v>4.55</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.59</v>
+        <v>2.35</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.93</v>
+        <v>2.23</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.37</v>
+        <v>5.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.22</v>
+        <v>3.99</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>1.46</v>
       </c>
       <c r="O30" t="n">
-        <v>2.75</v>
+        <v>5.74</v>
       </c>
       <c r="P30" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.82</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S30" t="n">
-        <v>2.7</v>
+        <v>3.12</v>
       </c>
       <c r="T30" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="U30" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V30" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="X30" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.06</v>
+        <v>1.65</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.5</v>
+        <v>2.59</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.59</v>
+        <v>1.1</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4410,25 +4410,25 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="M31" t="n">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
       <c r="O31" t="n">
         <v>3.1</v>
       </c>
       <c r="P31" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="R31" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S31" t="n">
         <v>3.1</v>
@@ -4437,7 +4437,7 @@
         <v>2.62</v>
       </c>
       <c r="U31" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="V31" t="n">
         <v>1.04</v>
@@ -4446,13 +4446,13 @@
         <v>1.22</v>
       </c>
       <c r="X31" t="n">
-        <v>3.54</v>
+        <v>4.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AA31" t="n">
         <v>3</v>
@@ -4461,7 +4461,7 @@
         <v>1.33</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.62</v>
+        <v>1.69</v>
       </c>
       <c r="AD31" t="n">
         <v>2.15</v>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4668,19 +4668,19 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="M33" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="N33" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="O33" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="P33" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="Q33" t="n">
         <v>3.3</v>
@@ -4710,10 +4710,10 @@
         <v>1.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AB33" t="n">
         <v>1.62</v>
@@ -4738,7 +4738,7 @@
         <v>1.2</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,58 +4797,58 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5.5</v>
+        <v>2.41</v>
       </c>
       <c r="M34" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="N34" t="n">
-        <v>1.42</v>
+        <v>2.53</v>
       </c>
       <c r="O34" t="n">
-        <v>4.8</v>
+        <v>2.85</v>
       </c>
       <c r="P34" t="n">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.9</v>
+        <v>2.85</v>
       </c>
       <c r="R34" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="S34" t="n">
-        <v>4.25</v>
+        <v>3.52</v>
       </c>
       <c r="T34" t="n">
-        <v>1.9</v>
+        <v>2.24</v>
       </c>
       <c r="U34" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W34" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X34" t="n">
-        <v>6.45</v>
+        <v>5</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.97</v>
+        <v>2.38</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="AD34" t="n">
         <v>2.6</v>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.13</v>
+        <v>1.56</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,77 +4926,77 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="M35" t="n">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="N35" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X35" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AA35" t="n">
         <v>2.5</v>
       </c>
-      <c r="O35" t="n">
-        <v>3</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="R35" t="n">
+      <c r="AB35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
         <v>1.25</v>
       </c>
-      <c r="S35" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X35" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH35" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.14</v>
+        <v>5</v>
       </c>
       <c r="M37" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="N37" t="n">
-        <v>2.87</v>
+        <v>1.45</v>
       </c>
       <c r="O37" t="n">
-        <v>2.55</v>
+        <v>4.75</v>
       </c>
       <c r="P37" t="n">
-        <v>2.31</v>
+        <v>2.65</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.54</v>
+        <v>1.9</v>
       </c>
       <c r="R37" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="S37" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="T37" t="n">
-        <v>2.23</v>
+        <v>1.9</v>
       </c>
       <c r="U37" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="V37" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="X37" t="n">
-        <v>4.25</v>
+        <v>6.55</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.25</v>
+        <v>3.04</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.45</v>
+        <v>1.87</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.67</v>
+        <v>1.13</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="M38" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="N38" t="n">
-        <v>1.78</v>
+        <v>2.25</v>
       </c>
       <c r="O38" t="n">
-        <v>4.76</v>
+        <v>4.26</v>
       </c>
       <c r="P38" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC38" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q38" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.01</v>
-      </c>
       <c r="AD38" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>1.28</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M39" t="n">
         <v>3.25</v>
       </c>
-      <c r="M39" t="n">
-        <v>3.05</v>
-      </c>
       <c r="N39" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O39" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y39" t="n">
         <v>2.25</v>
       </c>
-      <c r="O39" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X39" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Z39" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AA39" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
         <v>1.28</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5700,19 +5700,19 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="M41" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N41" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="O41" t="n">
         <v>2.2</v>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="Q41" t="n">
         <v>5.47</v>
@@ -5721,7 +5721,7 @@
         <v>1.39</v>
       </c>
       <c r="S41" t="n">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
       <c r="T41" t="n">
         <v>3.01</v>
@@ -5739,22 +5739,22 @@
         <v>3.25</v>
       </c>
       <c r="Y41" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AA41" t="n">
         <v>3.44</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AH41" t="n">
         <v>1.97</v>
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="M42" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="N42" t="n">
-        <v>2.14</v>
+        <v>2.49</v>
       </c>
       <c r="O42" t="n">
         <v>3.78</v>
@@ -5868,10 +5868,10 @@
         <v>3.2</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AA42" t="n">
         <v>3.9</v>
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="M43" t="n">
-        <v>3.18</v>
+        <v>3.35</v>
       </c>
       <c r="N43" t="n">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="O43" t="n">
         <v>3.02</v>
@@ -5997,10 +5997,10 @@
         <v>3.18</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AA43" t="n">
         <v>3.24</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="M44" t="n">
-        <v>3.3</v>
+        <v>3.11</v>
       </c>
       <c r="N44" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="O44" t="n">
         <v>2.9</v>
       </c>
       <c r="P44" t="n">
-        <v>2.14</v>
+        <v>1.91</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="R44" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>2.39</v>
       </c>
       <c r="T44" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="U44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W44" t="n">
         <v>1.44</v>
       </c>
-      <c r="V44" t="n">
-        <v>1</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.27</v>
-      </c>
       <c r="X44" t="n">
-        <v>3.38</v>
+        <v>2.6</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.18</v>
+        <v>4.4</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="M45" t="n">
-        <v>3.11</v>
+        <v>3.5</v>
       </c>
       <c r="N45" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="O45" t="n">
         <v>2.9</v>
       </c>
       <c r="P45" t="n">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="R45" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="S45" t="n">
-        <v>2.39</v>
+        <v>3</v>
       </c>
       <c r="T45" t="n">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="U45" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="V45" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="W45" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="X45" t="n">
-        <v>2.6</v>
+        <v>3.38</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AA45" t="n">
-        <v>4.4</v>
+        <v>3.18</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="AC45" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6354,7 +6354,7 @@
         <v>1.86</v>
       </c>
       <c r="O46" t="n">
-        <v>3.35</v>
+        <v>3.51</v>
       </c>
       <c r="P46" t="n">
         <v>2.41</v>
@@ -6363,16 +6363,16 @@
         <v>2.35</v>
       </c>
       <c r="R46" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="T46" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="U46" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V46" t="n">
         <v>1.01</v>
@@ -6399,7 +6399,7 @@
         <v>1.36</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,58 +6603,58 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.6</v>
+        <v>2.01</v>
       </c>
       <c r="M48" t="n">
-        <v>3.28</v>
+        <v>2.94</v>
       </c>
       <c r="N48" t="n">
-        <v>2.6</v>
+        <v>3.53</v>
       </c>
       <c r="O48" t="n">
-        <v>3.34</v>
+        <v>2.7</v>
       </c>
       <c r="P48" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S48" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="T48" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="U48" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W48" t="n">
         <v>1.32</v>
       </c>
-      <c r="V48" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.38</v>
-      </c>
       <c r="X48" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AA48" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AD48" t="n">
         <v>1.85</v>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,58 +6732,58 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.09</v>
+        <v>2.6</v>
       </c>
       <c r="M49" t="n">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="N49" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="O49" t="n">
-        <v>2.7</v>
+        <v>3.34</v>
       </c>
       <c r="P49" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="Q49" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X49" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA49" t="n">
         <v>4</v>
       </c>
-      <c r="R49" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S49" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X49" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AB49" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AD49" t="n">
         <v>1.85</v>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="M16" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>7.5</v>
+        <v>8.08</v>
       </c>
       <c r="O16" t="n">
         <v>1.85</v>
@@ -2493,10 +2493,10 @@
         <v>6.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T16" t="n">
         <v>2.65</v>
@@ -2514,10 +2514,10 @@
         <v>3.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="AA16" t="n">
         <v>3.08</v>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.55</v>
+        <v>5</v>
       </c>
       <c r="M17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X17" t="n">
         <v>3.5</v>
       </c>
-      <c r="N17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.14</v>
-      </c>
       <c r="Y17" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.35</v>
+        <v>2.97</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.14</v>
+        <v>1.09</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1.5</v>
       </c>
-      <c r="O18" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.74</v>
+        <v>2.22</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.09</v>
+        <v>1.41</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>1.6</v>
+        <v>5.57</v>
       </c>
       <c r="O19" t="n">
-        <v>3.05</v>
+        <v>2.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="Q19" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S19" t="n">
         <v>2.75</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.14</v>
-      </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="U19" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="X19" t="n">
-        <v>4.1</v>
+        <v>3.14</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="Z19" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.7</v>
+        <v>3.35</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.19</v>
+        <v>1.84</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>1.23</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.41</v>
+        <v>2.14</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,37 +3249,37 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M22" t="n">
         <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>4.05</v>
+        <v>3.35</v>
       </c>
       <c r="O22" t="n">
-        <v>2.99</v>
+        <v>2.54</v>
       </c>
       <c r="P22" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.72</v>
+        <v>4.42</v>
       </c>
       <c r="R22" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="S22" t="n">
-        <v>2.03</v>
+        <v>2.38</v>
       </c>
       <c r="T22" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="U22" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="V22" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="W22" t="n">
         <v>1.55</v>
@@ -3288,22 +3288,22 @@
         <v>2.3</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.97</v>
+        <v>2.43</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AA22" t="n">
-        <v>6.25</v>
+        <v>4.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.43</v>
+        <v>1.12</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,37 +3378,37 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
         <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="O23" t="n">
-        <v>2.54</v>
+        <v>2.99</v>
       </c>
       <c r="P23" t="n">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.42</v>
+        <v>4.72</v>
       </c>
       <c r="R23" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="S23" t="n">
-        <v>2.38</v>
+        <v>2.03</v>
       </c>
       <c r="T23" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="U23" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="V23" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="W23" t="n">
         <v>1.55</v>
@@ -3417,22 +3417,22 @@
         <v>2.3</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.43</v>
+        <v>2.97</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.9</v>
+        <v>6.25</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,58 +3507,58 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="M24" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S24" t="n">
         <v>3</v>
       </c>
-      <c r="O24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.7</v>
-      </c>
       <c r="T24" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="V24" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="W24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AB24" t="n">
         <v>1.32</v>
       </c>
-      <c r="X24" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AC24" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AD24" t="n">
         <v>2</v>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O25" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.48</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="T25" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="U25" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
         <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X25" t="n">
-        <v>3.12</v>
+        <v>3.42</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.6</v>
+        <v>2.87</v>
       </c>
       <c r="AB25" t="n">
         <v>1.3</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="M26" t="n">
-        <v>3.33</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="O26" t="n">
         <v>2.5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="R26" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S26" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="T26" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="X26" t="n">
-        <v>3.42</v>
+        <v>2.95</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.87</v>
+        <v>3.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="AD26" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,77 +3894,77 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="M27" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N27" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="O27" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
       <c r="R27" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S27" t="n">
-        <v>2.47</v>
+        <v>2.69</v>
       </c>
       <c r="T27" t="n">
-        <v>3.16</v>
+        <v>2.8</v>
       </c>
       <c r="U27" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="X27" t="n">
-        <v>2.95</v>
+        <v>3.32</v>
       </c>
       <c r="Y27" t="n">
         <v>2.05</v>
       </c>
       <c r="Z27" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.77</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.89</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.69</v>
+        <v>2.25</v>
       </c>
       <c r="M28" t="n">
-        <v>3.69</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>3.89</v>
+        <v>3.1</v>
       </c>
       <c r="O28" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="P28" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="R28" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="T28" t="n">
-        <v>2.34</v>
+        <v>2.8</v>
       </c>
       <c r="U28" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W28" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="X28" t="n">
-        <v>4.55</v>
+        <v>3.15</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.57</v>
+        <v>2.06</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.35</v>
+        <v>3.54</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AH28" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.55</v>
+        <v>5.3</v>
       </c>
       <c r="M29" t="n">
-        <v>3.38</v>
+        <v>4.05</v>
       </c>
       <c r="N29" t="n">
-        <v>2.5</v>
+        <v>1.47</v>
       </c>
       <c r="O29" t="n">
-        <v>2.95</v>
+        <v>5.74</v>
       </c>
       <c r="P29" t="n">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.08</v>
+        <v>2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="S29" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="T29" t="n">
-        <v>2.74</v>
+        <v>2.38</v>
       </c>
       <c r="U29" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="V29" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W29" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X29" t="n">
-        <v>3.42</v>
+        <v>4.2</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.96</v>
+        <v>1.58</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.08</v>
+        <v>2.62</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5.4</v>
+        <v>1.69</v>
       </c>
       <c r="M30" t="n">
-        <v>3.99</v>
+        <v>3.69</v>
       </c>
       <c r="N30" t="n">
-        <v>1.46</v>
+        <v>3.89</v>
       </c>
       <c r="O30" t="n">
-        <v>5.74</v>
+        <v>2.25</v>
       </c>
       <c r="P30" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S30" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="T30" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="U30" t="n">
         <v>1.53</v>
       </c>
       <c r="V30" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W30" t="n">
         <v>1.18</v>
       </c>
       <c r="X30" t="n">
-        <v>4.2</v>
+        <v>4.55</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.59</v>
+        <v>2.35</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.93</v>
+        <v>2.23</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="M31" t="n">
         <v>3.5</v>
@@ -4437,7 +4437,7 @@
         <v>2.62</v>
       </c>
       <c r="U31" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V31" t="n">
         <v>1.04</v>
@@ -4452,7 +4452,7 @@
         <v>1.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AA31" t="n">
         <v>3</v>
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="M32" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="O32" t="n">
         <v>4.62</v>
@@ -4578,10 +4578,10 @@
         <v>2.85</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.94</v>
+        <v>2.24</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AA32" t="n">
         <v>4</v>
@@ -4609,7 +4609,7 @@
         <v>1.28</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.09</v>
+        <v>2.82</v>
       </c>
       <c r="M33" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>3.15</v>
+        <v>2.27</v>
       </c>
       <c r="O33" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="M34" t="n">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="N34" t="n">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="O34" t="n">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="P34" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.85</v>
+        <v>3.12</v>
       </c>
       <c r="R34" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="S34" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="T34" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="U34" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="V34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X34" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="M35" t="n">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="N35" t="n">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="O35" t="n">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="P35" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.12</v>
+        <v>2.85</v>
       </c>
       <c r="R35" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="S35" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="T35" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="U35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X35" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y35" t="n">
         <v>1.55</v>
       </c>
-      <c r="V35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X35" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.61</v>
-      </c>
       <c r="Z35" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.85</v>
+        <v>5</v>
       </c>
       <c r="M36" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="N36" t="n">
-        <v>2.3</v>
+        <v>1.45</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.83</v>
+        <v>1.29</v>
       </c>
       <c r="Z36" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AA36" t="n">
         <v>1.87</v>
       </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>5</v>
+        <v>2.09</v>
       </c>
       <c r="M37" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="N37" t="n">
-        <v>1.45</v>
+        <v>3.15</v>
       </c>
       <c r="O37" t="n">
-        <v>4.75</v>
+        <v>2.55</v>
       </c>
       <c r="P37" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="R37" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="S37" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="T37" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="U37" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="X37" t="n">
-        <v>6.55</v>
+        <v>5.6</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.04</v>
+        <v>2.55</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.87</v>
+        <v>2.19</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.13</v>
+        <v>1.68</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.25</v>
+        <v>4.02</v>
       </c>
       <c r="M38" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="N38" t="n">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="O38" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="P38" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="R38" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S38" t="n">
-        <v>2.57</v>
+        <v>2.35</v>
       </c>
       <c r="T38" t="n">
-        <v>3.16</v>
+        <v>3.28</v>
       </c>
       <c r="U38" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="V38" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W38" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="X38" t="n">
-        <v>2.89</v>
+        <v>2.55</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.7</v>
+        <v>2.15</v>
       </c>
       <c r="M39" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="N39" t="n">
-        <v>1.78</v>
+        <v>3.4</v>
       </c>
       <c r="O39" t="n">
-        <v>4.76</v>
+        <v>2.64</v>
       </c>
       <c r="P39" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.69</v>
+        <v>4.25</v>
       </c>
       <c r="R39" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="S39" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="T39" t="n">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="U39" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="V39" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W39" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="X39" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AA39" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.16</v>
+        <v>1.65</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.15</v>
+        <v>3.44</v>
       </c>
       <c r="M40" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="O40" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q40" t="n">
         <v>2.8</v>
       </c>
-      <c r="N40" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O40" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="P40" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>4.25</v>
-      </c>
       <c r="R40" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="S40" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X40" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Y40" t="n">
         <v>2.23</v>
       </c>
-      <c r="T40" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="X40" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>2.8</v>
-      </c>
       <c r="Z40" t="n">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="AA40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,49 +5700,49 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.67</v>
+        <v>2.35</v>
       </c>
       <c r="M41" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N41" t="n">
-        <v>4.33</v>
+        <v>3.05</v>
       </c>
       <c r="O41" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="P41" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.47</v>
+        <v>3.77</v>
       </c>
       <c r="R41" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S41" t="n">
-        <v>2.85</v>
+        <v>2.58</v>
       </c>
       <c r="T41" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="U41" t="n">
         <v>1.35</v>
       </c>
       <c r="V41" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W41" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X41" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AA41" t="n">
         <v>3.44</v>
@@ -5751,10 +5751,10 @@
         <v>1.23</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.97</v>
+        <v>1.52</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.88</v>
+        <v>1.7</v>
       </c>
       <c r="M42" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>2.49</v>
+        <v>4.8</v>
       </c>
       <c r="O42" t="n">
-        <v>3.78</v>
+        <v>2.2</v>
       </c>
       <c r="P42" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.18</v>
+        <v>4.7</v>
       </c>
       <c r="R42" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="S42" t="n">
-        <v>2.65</v>
+        <v>2.85</v>
       </c>
       <c r="T42" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U42" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V42" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="W42" t="n">
         <v>1.33</v>
       </c>
       <c r="X42" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.9</v>
+        <v>3.44</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.55</v>
+        <v>1.16</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.41</v>
+        <v>2.05</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="M43" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="N43" t="n">
-        <v>3.05</v>
+        <v>2.49</v>
       </c>
       <c r="O43" t="n">
-        <v>3.02</v>
+        <v>3.78</v>
       </c>
       <c r="P43" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.65</v>
+        <v>3.18</v>
       </c>
       <c r="R43" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S43" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="T43" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="U43" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="V43" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W43" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="X43" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="Y43" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC43" t="n">
         <v>1.93</v>
       </c>
-      <c r="Z43" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AD43" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="M44" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="N44" t="n">
-        <v>3.25</v>
+        <v>2.93</v>
       </c>
       <c r="O44" t="n">
         <v>2.9</v>
       </c>
       <c r="P44" t="n">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="R44" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="S44" t="n">
-        <v>2.39</v>
+        <v>3</v>
       </c>
       <c r="T44" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="U44" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="V44" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="W44" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="X44" t="n">
-        <v>2.6</v>
+        <v>3.38</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AA44" t="n">
-        <v>4.4</v>
+        <v>3.24</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AC44" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.73</v>
+        <v>2.22</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="M45" t="n">
-        <v>3.5</v>
+        <v>3.11</v>
       </c>
       <c r="N45" t="n">
-        <v>2.85</v>
+        <v>3.54</v>
       </c>
       <c r="O45" t="n">
         <v>2.9</v>
       </c>
       <c r="P45" t="n">
-        <v>2.14</v>
+        <v>1.91</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="R45" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="T45" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="U45" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W45" t="n">
         <v>1.44</v>
       </c>
-      <c r="V45" t="n">
-        <v>1</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.27</v>
-      </c>
       <c r="X45" t="n">
-        <v>3.38</v>
+        <v>2.6</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="Z45" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC45" t="n">
         <v>2</v>
       </c>
-      <c r="AA45" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1.71</v>
-      </c>
       <c r="AD45" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>1.33</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.81</v>
+        <v>2.6</v>
       </c>
       <c r="M47" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="N47" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.6</v>
+        <v>1.81</v>
       </c>
       <c r="M49" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="N49" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="O49" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AA49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="M51" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N51" t="n">
-        <v>5.5</v>
+        <v>3.35</v>
       </c>
       <c r="O51" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="AA51" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="M52" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N52" t="n">
-        <v>3.35</v>
+        <v>5.5</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y52" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z52" t="n">
         <v>1.73</v>
       </c>
-      <c r="Z52" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -939,10 +939,10 @@
         <v>2.9</v>
       </c>
       <c r="P4" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="R4" t="n">
         <v>1.4</v>
@@ -997,7 +997,7 @@
         <v>1.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="M8" t="n">
         <v>3.18</v>
       </c>
       <c r="N8" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="O8" t="n">
         <v>3.1</v>
@@ -1458,7 +1458,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.29</v>
+        <v>3.18</v>
       </c>
       <c r="R8" t="n">
         <v>1.39</v>
@@ -1470,7 +1470,7 @@
         <v>2.8</v>
       </c>
       <c r="U8" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
         <v>1.01</v>
@@ -1479,25 +1479,25 @@
         <v>1.25</v>
       </c>
       <c r="X8" t="n">
-        <v>3.43</v>
+        <v>3.28</v>
       </c>
       <c r="Y8" t="n">
         <v>1.96</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AC8" t="n">
         <v>1.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1851,22 +1851,22 @@
         <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="U11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="V11" t="n">
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
       <c r="Y11" t="n">
         <v>1.76</v>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>2.08</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
         <v>1.12</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2481,7 +2481,7 @@
         <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>8.08</v>
+        <v>8</v>
       </c>
       <c r="O16" t="n">
         <v>1.85</v>
@@ -2496,7 +2496,7 @@
         <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T16" t="n">
         <v>2.65</v>
@@ -2514,10 +2514,10 @@
         <v>3.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="AA16" t="n">
         <v>3.08</v>
@@ -2526,10 +2526,10 @@
         <v>1.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="M17" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>1.5</v>
+        <v>4.75</v>
       </c>
       <c r="O17" t="n">
-        <v>6.71</v>
+        <v>2.25</v>
       </c>
       <c r="P17" t="n">
-        <v>2.13</v>
+        <v>2.28</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.95</v>
+        <v>5.25</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="T17" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="X17" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.97</v>
+        <v>3.35</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.09</v>
+        <v>2.14</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>5.7</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>4.05</v>
       </c>
       <c r="N18" t="n">
-        <v>2.43</v>
+        <v>1.43</v>
       </c>
       <c r="O18" t="n">
-        <v>3.05</v>
+        <v>5.13</v>
       </c>
       <c r="P18" t="n">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="Q18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T18" t="n">
         <v>2.75</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.5</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="V18" t="n">
         <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X18" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.5</v>
+        <v>1.98</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.22</v>
+        <v>1.74</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.41</v>
+        <v>1.07</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N19" t="n">
-        <v>5.57</v>
+        <v>1.6</v>
       </c>
       <c r="O19" t="n">
-        <v>2.2</v>
+        <v>3.05</v>
       </c>
       <c r="P19" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.25</v>
+        <v>2.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="X19" t="n">
-        <v>3.14</v>
+        <v>4.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.35</v>
+        <v>2.55</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.84</v>
+        <v>2.23</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>1.23</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.14</v>
+        <v>1.41</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2991,16 +2991,16 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="N20" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="O20" t="n">
-        <v>2.71</v>
+        <v>2.59</v>
       </c>
       <c r="P20" t="n">
         <v>2.04</v>
@@ -3024,19 +3024,19 @@
         <v>1.05</v>
       </c>
       <c r="W20" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="X20" t="n">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.44</v>
+        <v>4.65</v>
       </c>
       <c r="AB20" t="n">
         <v>1.12</v>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="X21" t="n">
         <v>2.97</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="N22" t="n">
-        <v>3.35</v>
+        <v>3.92</v>
       </c>
       <c r="O22" t="n">
-        <v>2.54</v>
+        <v>2.99</v>
       </c>
       <c r="P22" t="n">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.42</v>
+        <v>4.72</v>
       </c>
       <c r="R22" t="n">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="S22" t="n">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="T22" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="U22" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="V22" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="W22" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="X22" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.43</v>
+        <v>2.97</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.9</v>
+        <v>6.25</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>4.05</v>
+        <v>4.83</v>
       </c>
       <c r="O23" t="n">
-        <v>2.99</v>
+        <v>2.5</v>
       </c>
       <c r="P23" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.72</v>
+        <v>4.42</v>
       </c>
       <c r="R23" t="n">
-        <v>1.72</v>
+        <v>1.54</v>
       </c>
       <c r="S23" t="n">
-        <v>2.03</v>
+        <v>2.36</v>
       </c>
       <c r="T23" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="U23" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="V23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AB23" t="n">
         <v>1.11</v>
       </c>
-      <c r="W23" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AC23" t="n">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.43</v>
+        <v>1.12</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,58 +3507,58 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.55</v>
+        <v>2.27</v>
       </c>
       <c r="M24" t="n">
         <v>3.3</v>
       </c>
       <c r="N24" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="O24" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="P24" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.08</v>
+        <v>3.82</v>
       </c>
       <c r="R24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U24" t="n">
         <v>1.36</v>
       </c>
-      <c r="S24" t="n">
-        <v>3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.43</v>
-      </c>
       <c r="V24" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="W24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AB24" t="n">
         <v>1.25</v>
       </c>
-      <c r="X24" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AC24" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AD24" t="n">
         <v>2</v>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="M25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N25" t="n">
         <v>3.5</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.55</v>
       </c>
       <c r="O25" t="n">
         <v>2.5</v>
       </c>
       <c r="P25" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="T25" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="X25" t="n">
-        <v>3.42</v>
+        <v>2.95</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.92</v>
+        <v>2.23</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.9</v>
+        <v>1.63</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.87</v>
+        <v>3.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,77 +3765,77 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>3.92</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="O26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P26" t="n">
         <v>2.5</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
+        <v>4</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH26" t="n">
         <v>2</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.89</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Z27" t="n">
         <v>1.85</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X27" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AA27" t="n">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.77</v>
+        <v>1.44</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.25</v>
+        <v>5.62</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>4.28</v>
       </c>
       <c r="N28" t="n">
-        <v>3.1</v>
+        <v>1.47</v>
       </c>
       <c r="O28" t="n">
-        <v>2.75</v>
+        <v>5.74</v>
       </c>
       <c r="P28" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.82</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S28" t="n">
-        <v>2.7</v>
+        <v>3.12</v>
       </c>
       <c r="T28" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V28" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W28" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="X28" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.06</v>
+        <v>1.58</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.72</v>
+        <v>2.09</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.54</v>
+        <v>2.59</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.62</v>
+        <v>1.08</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>5.3</v>
+        <v>1.85</v>
       </c>
       <c r="M29" t="n">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>1.47</v>
+        <v>3.55</v>
       </c>
       <c r="O29" t="n">
-        <v>5.74</v>
+        <v>2.4</v>
       </c>
       <c r="P29" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>4.48</v>
       </c>
       <c r="R29" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="S29" t="n">
-        <v>3.12</v>
+        <v>2.69</v>
       </c>
       <c r="T29" t="n">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="U29" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="V29" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="X29" t="n">
-        <v>4.2</v>
+        <v>3.32</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.58</v>
+        <v>2.05</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.07</v>
+        <v>1.82</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.08</v>
+        <v>1.77</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="M30" t="n">
-        <v>3.69</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>3.89</v>
+        <v>3.7</v>
       </c>
       <c r="O30" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="P30" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q30" t="n">
         <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="T30" t="n">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="U30" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="V30" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="X30" t="n">
-        <v>4.55</v>
+        <v>3.42</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.35</v>
+        <v>2.87</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AH30" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4545,16 +4545,16 @@
         <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O32" t="n">
-        <v>4.62</v>
+        <v>4</v>
       </c>
       <c r="P32" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="R32" t="n">
         <v>1.42</v>
@@ -4572,19 +4572,19 @@
         <v>1.03</v>
       </c>
       <c r="W32" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="X32" t="n">
         <v>2.85</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.24</v>
+        <v>2.33</v>
       </c>
       <c r="Z32" t="n">
         <v>1.65</v>
       </c>
       <c r="AA32" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="AB32" t="n">
         <v>1.22</v>
@@ -4593,7 +4593,7 @@
         <v>1.96</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>1.28</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N33" t="n">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="Y33" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.3</v>
+        <v>2.82</v>
       </c>
       <c r="M34" t="n">
-        <v>3.78</v>
+        <v>3.25</v>
       </c>
       <c r="N34" t="n">
-        <v>2.49</v>
+        <v>2.27</v>
       </c>
       <c r="O34" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.31</v>
+        <v>1.8</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="M35" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="N35" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="O35" t="n">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="P35" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="R35" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="S35" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="T35" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="U35" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X35" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Y35" t="n">
         <v>1.62</v>
       </c>
-      <c r="V35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X35" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.55</v>
-      </c>
       <c r="Z35" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5058,10 +5058,10 @@
         <v>5</v>
       </c>
       <c r="M36" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="N36" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="O36" t="n">
         <v>4.75</v>
@@ -5076,7 +5076,7 @@
         <v>1.16</v>
       </c>
       <c r="S36" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="T36" t="n">
         <v>1.9</v>
@@ -5085,22 +5085,22 @@
         <v>1.8</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
         <v>1.05</v>
       </c>
       <c r="X36" t="n">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.04</v>
+        <v>3.19</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AB36" t="n">
         <v>1.87</v>
@@ -5190,7 +5190,7 @@
         <v>3.7</v>
       </c>
       <c r="N37" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="O37" t="n">
         <v>2.55</v>
@@ -5229,7 +5229,7 @@
         <v>2.55</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AB37" t="n">
         <v>1.62</v>
@@ -5238,7 +5238,7 @@
         <v>1.42</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.02</v>
+        <v>2.95</v>
       </c>
       <c r="M38" t="n">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="N38" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="O38" t="n">
-        <v>4.25</v>
+        <v>4.16</v>
       </c>
       <c r="P38" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC38" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q38" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AD38" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.15</v>
+        <v>3.75</v>
       </c>
       <c r="M39" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="N39" t="n">
-        <v>3.4</v>
+        <v>1.97</v>
       </c>
       <c r="O39" t="n">
-        <v>2.64</v>
+        <v>4.4</v>
       </c>
       <c r="P39" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.25</v>
+        <v>2.71</v>
       </c>
       <c r="R39" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="S39" t="n">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="T39" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="U39" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="V39" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W39" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="X39" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.8</v>
+        <v>2.41</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AA39" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.65</v>
+        <v>1.16</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,77 +5571,77 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.44</v>
+        <v>2.15</v>
       </c>
       <c r="M40" t="n">
-        <v>3.06</v>
+        <v>2.8</v>
       </c>
       <c r="N40" t="n">
-        <v>2.06</v>
+        <v>3.4</v>
       </c>
       <c r="O40" t="n">
-        <v>4.26</v>
+        <v>2.64</v>
       </c>
       <c r="P40" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="Q40" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X40" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y40" t="n">
         <v>2.8</v>
       </c>
-      <c r="R40" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T40" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W40" t="n">
+      <c r="Z40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
         <v>1.36</v>
       </c>
-      <c r="X40" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH40" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="M41" t="n">
-        <v>3.35</v>
+        <v>3.01</v>
       </c>
       <c r="N41" t="n">
-        <v>3.05</v>
+        <v>2.83</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -5832,16 +5832,16 @@
         <v>1.7</v>
       </c>
       <c r="M42" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N42" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="O42" t="n">
         <v>2.2</v>
       </c>
       <c r="P42" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Q42" t="n">
         <v>4.7</v>
@@ -5850,13 +5850,13 @@
         <v>1.39</v>
       </c>
       <c r="S42" t="n">
-        <v>2.85</v>
+        <v>2.69</v>
       </c>
       <c r="T42" t="n">
         <v>2.8</v>
       </c>
       <c r="U42" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V42" t="n">
         <v>1</v>
@@ -5880,10 +5880,10 @@
         <v>1.28</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         <v>1.16</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5958,28 +5958,28 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="M43" t="n">
         <v>3.1</v>
       </c>
       <c r="N43" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="O43" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="P43" t="n">
         <v>1.97</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.18</v>
+        <v>3.32</v>
       </c>
       <c r="R43" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S43" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="T43" t="n">
         <v>2.88</v>
@@ -5988,7 +5988,7 @@
         <v>1.33</v>
       </c>
       <c r="V43" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="W43" t="n">
         <v>1.33</v>
@@ -5997,16 +5997,16 @@
         <v>3.2</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AA43" t="n">
         <v>3.9</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AC43" t="n">
         <v>1.93</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="M44" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N44" t="n">
-        <v>2.93</v>
+        <v>3.57</v>
       </c>
       <c r="O44" t="n">
         <v>2.9</v>
       </c>
       <c r="P44" t="n">
-        <v>2.14</v>
+        <v>1.91</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="R44" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>2.39</v>
       </c>
       <c r="T44" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="U44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W44" t="n">
         <v>1.44</v>
       </c>
-      <c r="V44" t="n">
-        <v>1</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.26</v>
-      </c>
       <c r="X44" t="n">
-        <v>3.38</v>
+        <v>2.6</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.24</v>
+        <v>4.4</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.22</v>
+        <v>1.73</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>1.33</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="M45" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="N45" t="n">
-        <v>3.54</v>
+        <v>2.7</v>
       </c>
       <c r="O45" t="n">
         <v>2.9</v>
       </c>
       <c r="P45" t="n">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="R45" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="S45" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="T45" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="U45" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="V45" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="W45" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="X45" t="n">
-        <v>2.6</v>
+        <v>3.38</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.62</v>
+        <v>1.92</v>
       </c>
       <c r="AA45" t="n">
-        <v>4.4</v>
+        <v>3.24</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AC45" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>1.33</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6345,16 +6345,16 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="M46" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="N46" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="O46" t="n">
-        <v>3.51</v>
+        <v>3.4</v>
       </c>
       <c r="P46" t="n">
         <v>2.41</v>
@@ -6363,10 +6363,10 @@
         <v>2.35</v>
       </c>
       <c r="R46" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S46" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="T46" t="n">
         <v>1.94</v>
@@ -6378,28 +6378,28 @@
         <v>1.01</v>
       </c>
       <c r="W46" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X46" t="n">
-        <v>5.95</v>
+        <v>5.4</v>
       </c>
       <c r="Y46" t="n">
         <v>1.4</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AC46" t="n">
         <v>1.36</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="M47" t="n">
         <v>3.28</v>
       </c>
       <c r="N47" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="O47" t="n">
         <v>3.34</v>
@@ -6489,7 +6489,7 @@
         <v>2.01</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R47" t="n">
         <v>1.42</v>
@@ -6541,7 +6541,7 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="AH47" t="n">
         <v>1.47</v>
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.01</v>
+        <v>1.82</v>
       </c>
       <c r="M48" t="n">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="N48" t="n">
-        <v>3.53</v>
+        <v>3.9</v>
       </c>
       <c r="O48" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AA48" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.81</v>
+        <v>2.01</v>
       </c>
       <c r="M49" t="n">
-        <v>3.35</v>
+        <v>2.94</v>
       </c>
       <c r="N49" t="n">
-        <v>3.9</v>
+        <v>3.53</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6861,31 +6861,31 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="M50" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="O50" t="n">
         <v>3.72</v>
       </c>
       <c r="P50" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="Q50" t="n">
         <v>3.18</v>
       </c>
       <c r="R50" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S50" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="T50" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="U50" t="n">
         <v>1.28</v>
@@ -6909,13 +6909,13 @@
         <v>4.33</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>1.34</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.92</v>
+        <v>1.59</v>
       </c>
       <c r="M51" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="N51" t="n">
-        <v>3.35</v>
+        <v>5.5</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="M52" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N52" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="O52" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="AA52" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.7</v>
+        <v>5.7</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4.75</v>
+        <v>1.43</v>
       </c>
       <c r="O17" t="n">
-        <v>2.25</v>
+        <v>5.13</v>
       </c>
       <c r="P17" t="n">
-        <v>2.28</v>
+        <v>2.13</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.25</v>
+        <v>1.98</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T17" t="n">
         <v>2.75</v>
       </c>
-      <c r="T17" t="n">
-        <v>2.81</v>
-      </c>
       <c r="U17" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="V17" t="n">
         <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="X17" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.35</v>
+        <v>2.97</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.14</v>
+        <v>1.07</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="M18" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="O18" t="n">
-        <v>5.13</v>
+        <v>3.05</v>
       </c>
       <c r="P18" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.98</v>
+        <v>2.75</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U18" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="V18" t="n">
         <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X18" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.97</v>
+        <v>2.55</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.98</v>
+        <v>1.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.74</v>
+        <v>2.23</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.07</v>
+        <v>1.41</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>1.6</v>
+        <v>4.75</v>
       </c>
       <c r="O19" t="n">
-        <v>3.05</v>
+        <v>2.25</v>
       </c>
       <c r="P19" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="Q19" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S19" t="n">
         <v>2.75</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.1</v>
-      </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="U19" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="X19" t="n">
-        <v>4.1</v>
+        <v>3.14</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="Z19" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.55</v>
+        <v>3.35</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.23</v>
+        <v>1.83</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>1.23</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.41</v>
+        <v>2.14</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,77 +3507,77 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.27</v>
+        <v>1.7</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>3.92</v>
       </c>
       <c r="N24" t="n">
-        <v>3</v>
+        <v>3.85</v>
       </c>
       <c r="O24" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="P24" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="S24" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="T24" t="n">
-        <v>2.8</v>
+        <v>2.34</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="V24" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W24" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="X24" t="n">
-        <v>3.15</v>
+        <v>4.7</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.06</v>
+        <v>1.54</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.72</v>
+        <v>2.28</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.54</v>
+        <v>2.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AD24" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH24" t="n">
         <v>2</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.62</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O25" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.33</v>
+        <v>4.48</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S25" t="n">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="T25" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="U25" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="X25" t="n">
-        <v>2.95</v>
+        <v>3.32</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="M26" t="n">
-        <v>3.92</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="O26" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="R26" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="S26" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="T26" t="n">
-        <v>2.34</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="V26" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="X26" t="n">
-        <v>4.7</v>
+        <v>2.95</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.54</v>
+        <v>2.23</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.28</v>
+        <v>1.63</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.55</v>
+        <v>1.96</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.23</v>
+        <v>1.76</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AH26" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.64</v>
+        <v>5.25</v>
       </c>
       <c r="M27" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="N27" t="n">
-        <v>2.5</v>
+        <v>1.51</v>
       </c>
       <c r="O27" t="n">
-        <v>2.95</v>
+        <v>5.74</v>
       </c>
       <c r="P27" t="n">
-        <v>2.11</v>
+        <v>2.29</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.08</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="S27" t="n">
-        <v>2.91</v>
+        <v>3.12</v>
       </c>
       <c r="T27" t="n">
-        <v>2.74</v>
+        <v>2.38</v>
       </c>
       <c r="U27" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="V27" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W27" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="X27" t="n">
-        <v>3.68</v>
+        <v>4.2</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.96</v>
+        <v>1.58</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.85</v>
+        <v>2.17</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.14</v>
+        <v>2.59</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,62 +4023,62 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>5.62</v>
+        <v>1.95</v>
       </c>
       <c r="M28" t="n">
-        <v>4.28</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>1.47</v>
+        <v>3.5</v>
       </c>
       <c r="O28" t="n">
-        <v>5.74</v>
+        <v>2.5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="Q28" t="n">
+        <v>4</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD28" t="n">
         <v>2</v>
       </c>
-      <c r="R28" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AE28" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.08</v>
+        <v>1.75</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Z29" t="n">
         <v>1.85</v>
       </c>
-      <c r="M29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AA29" t="n">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.77</v>
+        <v>1.44</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,58 +4281,58 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.95</v>
+        <v>2.27</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="O30" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="P30" t="n">
         <v>2.15</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="R30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U30" t="n">
         <v>1.36</v>
       </c>
-      <c r="S30" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W30" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.25</v>
       </c>
-      <c r="X30" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AC30" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AD30" t="n">
         <v>2</v>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.5</v>
+        <v>2.09</v>
       </c>
       <c r="M33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S33" t="n">
         <v>3.6</v>
       </c>
-      <c r="N33" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="O33" t="n">
-        <v>3</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.52</v>
-      </c>
       <c r="T33" t="n">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="U33" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="V33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X33" t="n">
-        <v>5.15</v>
+        <v>5.6</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.82</v>
+        <v>2.3</v>
       </c>
       <c r="M34" t="n">
         <v>3.25</v>
       </c>
       <c r="N34" t="n">
-        <v>2.27</v>
+        <v>2.7</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Y34" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.8</v>
+        <v>2.29</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,77 +4926,77 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="M35" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="N35" t="n">
-        <v>2.7</v>
+        <v>1.44</v>
       </c>
       <c r="O35" t="n">
-        <v>2.55</v>
+        <v>4.75</v>
       </c>
       <c r="P35" t="n">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="R35" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="S35" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="T35" t="n">
-        <v>2.23</v>
+        <v>1.9</v>
       </c>
       <c r="U35" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="V35" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X35" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
         <v>1.15</v>
       </c>
-      <c r="X35" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH35" t="n">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M36" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="N36" t="n">
-        <v>1.44</v>
+        <v>2.45</v>
       </c>
       <c r="O36" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="P36" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.9</v>
+        <v>2.85</v>
       </c>
       <c r="R36" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="S36" t="n">
-        <v>4.6</v>
+        <v>3.52</v>
       </c>
       <c r="T36" t="n">
-        <v>1.9</v>
+        <v>2.23</v>
       </c>
       <c r="U36" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W36" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X36" t="n">
-        <v>6.5</v>
+        <v>5.15</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.19</v>
+        <v>2.38</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.88</v>
+        <v>2.31</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.13</v>
+        <v>1.46</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.09</v>
+        <v>2.82</v>
       </c>
       <c r="M37" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>3</v>
+        <v>2.27</v>
       </c>
       <c r="O37" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,58 +5313,58 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="M38" t="n">
         <v>2.95</v>
       </c>
-      <c r="M38" t="n">
-        <v>3.06</v>
-      </c>
       <c r="N38" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="O38" t="n">
-        <v>4.16</v>
+        <v>4.55</v>
       </c>
       <c r="P38" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="R38" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="S38" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="T38" t="n">
-        <v>3.16</v>
+        <v>3.28</v>
       </c>
       <c r="U38" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="V38" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W38" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="X38" t="n">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AA38" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AD38" t="n">
         <v>1.71</v>
@@ -5383,7 +5383,7 @@
         <v>1.28</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="T39" t="n">
         <v>3.75</v>
       </c>
-      <c r="M39" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="N39" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="O39" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3.35</v>
-      </c>
       <c r="U39" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="V39" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W39" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="X39" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.41</v>
+        <v>2.8</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AA39" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.16</v>
+        <v>1.65</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.15</v>
+        <v>3.27</v>
       </c>
       <c r="M40" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="O40" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q40" t="n">
         <v>2.8</v>
       </c>
-      <c r="N40" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O40" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="P40" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>4.25</v>
-      </c>
       <c r="R40" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="S40" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="T40" t="n">
-        <v>3.75</v>
+        <v>3.18</v>
       </c>
       <c r="U40" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="V40" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="W40" t="n">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="X40" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AA40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,77 +5700,77 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.3</v>
+        <v>2.83</v>
       </c>
       <c r="M41" t="n">
-        <v>3.01</v>
+        <v>3.1</v>
       </c>
       <c r="N41" t="n">
-        <v>2.83</v>
+        <v>2.47</v>
       </c>
       <c r="O41" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="P41" t="n">
         <v>1.97</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.77</v>
+        <v>3.32</v>
       </c>
       <c r="R41" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH41" t="n">
         <v>1.41</v>
-      </c>
-      <c r="S41" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X41" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.52</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,77 +5958,77 @@
         </is>
       </c>
       <c r="L43" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="N43" t="n">
         <v>2.83</v>
       </c>
-      <c r="M43" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N43" t="n">
-        <v>2.47</v>
-      </c>
       <c r="O43" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="P43" t="n">
         <v>1.97</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.32</v>
+        <v>3.77</v>
       </c>
       <c r="R43" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="S43" t="n">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="T43" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="U43" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X43" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
         <v>1.33</v>
       </c>
-      <c r="V43" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X43" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AH43" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="M44" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N44" t="n">
-        <v>3.57</v>
+        <v>2.7</v>
       </c>
       <c r="O44" t="n">
         <v>2.9</v>
       </c>
       <c r="P44" t="n">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="R44" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="S44" t="n">
-        <v>2.39</v>
+        <v>3</v>
       </c>
       <c r="T44" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="U44" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="V44" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="W44" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="X44" t="n">
-        <v>2.6</v>
+        <v>3.38</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.62</v>
+        <v>1.92</v>
       </c>
       <c r="AA44" t="n">
-        <v>4.4</v>
+        <v>3.24</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AC44" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>1.33</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="M45" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N45" t="n">
-        <v>2.7</v>
+        <v>3.57</v>
       </c>
       <c r="O45" t="n">
         <v>2.9</v>
       </c>
       <c r="P45" t="n">
-        <v>2.14</v>
+        <v>1.91</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="R45" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
+        <v>2.39</v>
       </c>
       <c r="T45" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="U45" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W45" t="n">
         <v>1.44</v>
       </c>
-      <c r="V45" t="n">
-        <v>1</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.26</v>
-      </c>
       <c r="X45" t="n">
-        <v>3.38</v>
+        <v>2.6</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.9</v>
+        <v>2.45</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.92</v>
+        <v>1.62</v>
       </c>
       <c r="AA45" t="n">
-        <v>3.24</v>
+        <v>4.4</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.04</v>
+        <v>1.73</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>1.33</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6345,16 +6345,16 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="M46" t="n">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="N46" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O46" t="n">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="P46" t="n">
         <v>2.41</v>
@@ -6363,7 +6363,7 @@
         <v>2.35</v>
       </c>
       <c r="R46" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S46" t="n">
         <v>4.2</v>
@@ -6381,7 +6381,7 @@
         <v>1.12</v>
       </c>
       <c r="X46" t="n">
-        <v>5.4</v>
+        <v>5.86</v>
       </c>
       <c r="Y46" t="n">
         <v>1.4</v>
@@ -6399,7 +6399,7 @@
         <v>1.36</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M47" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O47" t="n">
         <v>2.7</v>
       </c>
-      <c r="M47" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="N47" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="O47" t="n">
-        <v>3.34</v>
-      </c>
       <c r="P47" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="R47" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S47" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="T47" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="U47" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V47" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W47" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="X47" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AA47" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.82</v>
+        <v>2.7</v>
       </c>
       <c r="M48" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N48" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O48" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q48" t="n">
         <v>3.35</v>
       </c>
-      <c r="N48" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.01</v>
+        <v>1.82</v>
       </c>
       <c r="M49" t="n">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="N49" t="n">
-        <v>3.53</v>
+        <v>3.9</v>
       </c>
       <c r="O49" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AA49" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6861,28 +6861,28 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="M50" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N50" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="O50" t="n">
-        <v>3.72</v>
+        <v>3.65</v>
       </c>
       <c r="P50" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="R50" t="n">
         <v>1.5</v>
       </c>
       <c r="S50" t="n">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="T50" t="n">
         <v>3.34</v>
@@ -6906,16 +6906,16 @@
         <v>1.59</v>
       </c>
       <c r="AA50" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AC50" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>1.34</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.59</v>
+        <v>1.93</v>
       </c>
       <c r="M51" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N51" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="O51" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.12</v>
+        <v>1.73</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AA51" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.93</v>
+        <v>1.56</v>
       </c>
       <c r="M52" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N52" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.73</v>
+        <v>2.11</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O4" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="P4" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.85</v>
+        <v>3.01</v>
       </c>
       <c r="R4" t="n">
         <v>1.4</v>
@@ -954,7 +954,7 @@
         <v>2.9</v>
       </c>
       <c r="U4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
@@ -978,7 +978,7 @@
         <v>1.25</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AD4" t="n">
         <v>1.95</v>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45950.22916666666</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1258,10 +1258,10 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45950.29166666666</v>
@@ -1446,10 +1446,10 @@
         <v>2.6</v>
       </c>
       <c r="M8" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="O8" t="n">
         <v>3.1</v>
@@ -1458,7 +1458,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.18</v>
+        <v>3.29</v>
       </c>
       <c r="R8" t="n">
         <v>1.39</v>
@@ -1467,25 +1467,25 @@
         <v>2.95</v>
       </c>
       <c r="T8" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="U8" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X8" t="n">
         <v>3.28</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AA8" t="n">
         <v>3.2</v>
@@ -1497,7 +1497,7 @@
         <v>1.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="AH8" t="n">
         <v>1.39</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45950.375</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45950.41666666666</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.35</v>
+        <v>1.9</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="N12" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="O12" t="n">
-        <v>4.8</v>
+        <v>2.62</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.24</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.76</v>
+        <v>2.75</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.99</v>
+        <v>1.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2161,10 +2161,10 @@
         <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45950.45833333334</v>
@@ -2217,16 +2217,16 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="M14" t="n">
-        <v>3.01</v>
+        <v>2.9</v>
       </c>
       <c r="N14" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="P14" t="n">
         <v>1.93</v>
@@ -2238,10 +2238,10 @@
         <v>1.52</v>
       </c>
       <c r="S14" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="T14" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="U14" t="n">
         <v>1.27</v>
@@ -2250,16 +2250,16 @@
         <v>1.04</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="X14" t="n">
         <v>2.56</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AA14" t="n">
         <v>4.33</v>
@@ -2290,10 +2290,10 @@
         <v>1.62</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45950.45833333334</v>
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="N16" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="O16" t="n">
         <v>1.85</v>
@@ -2493,16 +2493,16 @@
         <v>6.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="T16" t="n">
         <v>2.65</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V16" t="n">
         <v>1</v>
@@ -2514,10 +2514,10 @@
         <v>3.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AA16" t="n">
         <v>3.08</v>
@@ -2526,10 +2526,10 @@
         <v>1.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2548,10 +2548,10 @@
         <v>2.75</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45950.47916666666</v>
@@ -2604,22 +2604,22 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="M17" t="n">
-        <v>4.05</v>
+        <v>4.7</v>
       </c>
       <c r="N17" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="O17" t="n">
-        <v>5.13</v>
+        <v>6.71</v>
       </c>
       <c r="P17" t="n">
         <v>2.13</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="R17" t="n">
         <v>1.33</v>
@@ -2631,10 +2631,10 @@
         <v>2.75</v>
       </c>
       <c r="U17" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W17" t="n">
         <v>1.22</v>
@@ -2643,13 +2643,13 @@
         <v>3.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AB17" t="n">
         <v>1.3</v>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45950.5</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.2</v>
+        <v>1.55</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="O18" t="n">
-        <v>3.05</v>
+        <v>2.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S18" t="n">
         <v>2.75</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.1</v>
-      </c>
       <c r="T18" t="n">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="U18" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="V18" t="n">
         <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="X18" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="Z18" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.55</v>
+        <v>3.35</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.23</v>
+        <v>1.83</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2803,13 +2803,13 @@
         <v>1.23</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.41</v>
+        <v>2.14</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45950.5</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N19" t="n">
-        <v>4.75</v>
+        <v>1.6</v>
       </c>
       <c r="O19" t="n">
-        <v>2.25</v>
+        <v>3.14</v>
       </c>
       <c r="P19" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.25</v>
+        <v>2.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S19" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="U19" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="X19" t="n">
-        <v>3.14</v>
+        <v>4.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.35</v>
+        <v>2.81</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.14</v>
+        <v>1.4</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45950.5</v>
@@ -2991,28 +2991,28 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="N20" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="O20" t="n">
-        <v>2.59</v>
+        <v>2.72</v>
       </c>
       <c r="P20" t="n">
         <v>2.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="R20" t="n">
         <v>1.52</v>
       </c>
       <c r="S20" t="n">
-        <v>2.49</v>
+        <v>2.34</v>
       </c>
       <c r="T20" t="n">
         <v>3.5</v>
@@ -3024,16 +3024,16 @@
         <v>1.05</v>
       </c>
       <c r="W20" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="X20" t="n">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AA20" t="n">
         <v>4.65</v>
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="O21" t="n">
         <v>4.22</v>
@@ -3138,7 +3138,7 @@
         <v>2.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
         <v>3.15</v>
@@ -3147,7 +3147,7 @@
         <v>2.38</v>
       </c>
       <c r="U21" t="n">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="V21" t="n">
         <v>1.02</v>
@@ -3156,25 +3156,25 @@
         <v>1.36</v>
       </c>
       <c r="X21" t="n">
-        <v>2.97</v>
+        <v>3.01</v>
       </c>
       <c r="Y21" t="n">
         <v>2.04</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AA21" t="n">
         <v>3.42</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.88</v>
+        <v>2.12</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3249,16 +3249,16 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="M22" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>3.92</v>
+        <v>4.05</v>
       </c>
       <c r="O22" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="P22" t="n">
         <v>1.75</v>
@@ -3267,7 +3267,7 @@
         <v>4.72</v>
       </c>
       <c r="R22" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="S22" t="n">
         <v>2.06</v>
@@ -3276,34 +3276,34 @@
         <v>4.25</v>
       </c>
       <c r="U22" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="V22" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="W22" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="X22" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.97</v>
+        <v>3.21</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AA22" t="n">
-        <v>6.25</v>
+        <v>5.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.21</v>
+        <v>1.43</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3378,28 +3378,28 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.74</v>
+        <v>2.25</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>4.83</v>
+        <v>3.35</v>
       </c>
       <c r="O23" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="P23" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.42</v>
+        <v>5.77</v>
       </c>
       <c r="R23" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S23" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T23" t="n">
         <v>3.6</v>
@@ -3411,28 +3411,28 @@
         <v>1.04</v>
       </c>
       <c r="W23" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="X23" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="AB23" t="n">
         <v>1.11</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
         <v>1.86</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="M24" t="n">
-        <v>3.92</v>
+        <v>3.34</v>
       </c>
       <c r="N24" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="P24" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>3.87</v>
       </c>
       <c r="R24" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="T24" t="n">
-        <v>2.34</v>
+        <v>2.8</v>
       </c>
       <c r="U24" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="V24" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W24" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="X24" t="n">
-        <v>4.7</v>
+        <v>3.15</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.54</v>
+        <v>2.11</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.28</v>
+        <v>1.72</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.5</v>
+        <v>3.81</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AH24" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.85</v>
+        <v>5.4</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>3.99</v>
       </c>
       <c r="N25" t="n">
-        <v>3.55</v>
+        <v>1.46</v>
       </c>
       <c r="O25" t="n">
-        <v>2.4</v>
+        <v>5.57</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.48</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="S25" t="n">
-        <v>2.69</v>
+        <v>3.25</v>
       </c>
       <c r="T25" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="X25" t="n">
-        <v>3.32</v>
+        <v>4.06</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.6</v>
+        <v>2.71</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>2.38</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.77</v>
+        <v>1.1</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,62 +3765,62 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>3.33</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>3.63</v>
       </c>
       <c r="O26" t="n">
         <v>2.5</v>
       </c>
       <c r="P26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD26" t="n">
         <v>2</v>
       </c>
-      <c r="Q26" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AE26" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.25</v>
+        <v>1.82</v>
       </c>
       <c r="M27" t="n">
-        <v>4.1</v>
+        <v>3.36</v>
       </c>
       <c r="N27" t="n">
-        <v>1.51</v>
+        <v>3.67</v>
       </c>
       <c r="O27" t="n">
-        <v>5.74</v>
+        <v>2.4</v>
       </c>
       <c r="P27" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>4.63</v>
       </c>
       <c r="R27" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="S27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X27" t="n">
         <v>3.12</v>
       </c>
-      <c r="T27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X27" t="n">
-        <v>4.2</v>
-      </c>
       <c r="Y27" t="n">
-        <v>1.58</v>
+        <v>1.94</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.17</v>
+        <v>1.76</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.59</v>
+        <v>3.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.13</v>
+        <v>1.77</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,77 +4023,77 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>3.69</v>
       </c>
       <c r="N28" t="n">
-        <v>3.5</v>
+        <v>3.89</v>
       </c>
       <c r="O28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P28" t="n">
         <v>2.5</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.15</v>
       </c>
       <c r="Q28" t="n">
         <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="S28" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="T28" t="n">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="U28" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W28" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="X28" t="n">
-        <v>3.42</v>
+        <v>4.74</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.87</v>
+        <v>2.35</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AD28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH28" t="n">
         <v>2</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.75</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.64</v>
+        <v>1.73</v>
       </c>
       <c r="M29" t="n">
         <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="O29" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X29" t="n">
         <v>2.95</v>
       </c>
-      <c r="P29" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.68</v>
-      </c>
       <c r="Y29" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.14</v>
+        <v>3.9</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.67</v>
+        <v>2.04</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,58 +4281,58 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="O30" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="P30" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.82</v>
+        <v>2.99</v>
       </c>
       <c r="R30" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="T30" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="U30" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="V30" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="W30" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.32</v>
       </c>
-      <c r="X30" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AC30" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AD30" t="n">
         <v>2</v>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.59</v>
+        <v>2.38</v>
       </c>
       <c r="M31" t="n">
-        <v>3.5</v>
+        <v>3.26</v>
       </c>
       <c r="N31" t="n">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
       <c r="O31" t="n">
         <v>3.1</v>
@@ -4428,16 +4428,16 @@
         <v>3.2</v>
       </c>
       <c r="R31" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S31" t="n">
         <v>3.1</v>
       </c>
       <c r="T31" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="U31" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V31" t="n">
         <v>1.04</v>
@@ -4449,10 +4449,10 @@
         <v>4.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="AA31" t="n">
         <v>3</v>
@@ -4461,7 +4461,7 @@
         <v>1.33</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AD31" t="n">
         <v>2.15</v>
@@ -4539,22 +4539,22 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="N32" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="O32" t="n">
         <v>4</v>
       </c>
       <c r="P32" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="R32" t="n">
         <v>1.42</v>
@@ -4578,10 +4578,10 @@
         <v>2.85</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.33</v>
+        <v>1.94</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AA32" t="n">
         <v>4.25</v>
@@ -4593,7 +4593,7 @@
         <v>1.96</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="M33" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N33" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="O33" t="n">
         <v>2.55</v>
       </c>
       <c r="P33" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="Q33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S33" t="n">
         <v>3.3</v>
       </c>
-      <c r="R33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.6</v>
-      </c>
       <c r="T33" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="U33" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="V33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W33" t="n">
         <v>1.15</v>
       </c>
       <c r="X33" t="n">
-        <v>5.6</v>
+        <v>4.25</v>
       </c>
       <c r="Y33" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC33" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z33" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AD33" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,77 +4797,77 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="M34" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N34" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="O34" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="P34" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="R34" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S34" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="T34" t="n">
         <v>2.23</v>
       </c>
       <c r="U34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X34" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB34" t="n">
         <v>1.55</v>
       </c>
-      <c r="V34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X34" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AA34" t="n">
+      <c r="AC34" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD34" t="n">
         <v>2.5</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH34" t="n">
         <v>1.46</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>5</v>
+        <v>2.09</v>
       </c>
       <c r="M35" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="N35" t="n">
-        <v>1.44</v>
+        <v>3</v>
       </c>
       <c r="O35" t="n">
-        <v>4.75</v>
+        <v>2.55</v>
       </c>
       <c r="P35" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="R35" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="S35" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="T35" t="n">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="U35" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="V35" t="n">
         <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="X35" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.19</v>
+        <v>2.55</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.13</v>
+        <v>1.68</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="M36" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="O36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.47</v>
+        <v>1.83</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.38</v>
+        <v>1.87</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.82</v>
+        <v>5</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="N37" t="n">
-        <v>2.27</v>
+        <v>1.44</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.8</v>
+        <v>3.19</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.82</v>
+        <v>2.13</v>
       </c>
       <c r="M38" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="N38" t="n">
-        <v>2</v>
+        <v>3.77</v>
       </c>
       <c r="O38" t="n">
-        <v>4.55</v>
+        <v>2.75</v>
       </c>
       <c r="P38" t="n">
-        <v>2.01</v>
+        <v>1.79</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.68</v>
+        <v>4.25</v>
       </c>
       <c r="R38" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="S38" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="T38" t="n">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="U38" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="V38" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W38" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="X38" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AA38" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.16</v>
+        <v>1.66</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.15</v>
+        <v>3.82</v>
       </c>
       <c r="M39" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="N39" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="O39" t="n">
-        <v>2.64</v>
+        <v>4.4</v>
       </c>
       <c r="P39" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.25</v>
+        <v>2.69</v>
       </c>
       <c r="R39" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="S39" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="T39" t="n">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="U39" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="V39" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W39" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="X39" t="n">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AA39" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.65</v>
+        <v>1.16</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5580,16 +5580,16 @@
         <v>2.13</v>
       </c>
       <c r="O40" t="n">
-        <v>3.65</v>
+        <v>4.05</v>
       </c>
       <c r="P40" t="n">
         <v>1.94</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="R40" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S40" t="n">
         <v>2.43</v>
@@ -5598,7 +5598,7 @@
         <v>3.18</v>
       </c>
       <c r="U40" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="V40" t="n">
         <v>1.04</v>
@@ -5622,10 +5622,10 @@
         <v>1.19</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>1.28</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.83</v>
+        <v>1.67</v>
       </c>
       <c r="M41" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="N41" t="n">
-        <v>2.47</v>
+        <v>4.33</v>
       </c>
       <c r="O41" t="n">
-        <v>3.75</v>
+        <v>2.2</v>
       </c>
       <c r="P41" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.32</v>
+        <v>4.55</v>
       </c>
       <c r="R41" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="S41" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T41" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U41" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V41" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W41" t="n">
         <v>1.33</v>
       </c>
       <c r="X41" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.9</v>
+        <v>3.44</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.55</v>
+        <v>1.27</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.41</v>
+        <v>2.17</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.7</v>
+        <v>2.88</v>
       </c>
       <c r="M42" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N42" t="n">
-        <v>4.75</v>
+        <v>2.49</v>
       </c>
       <c r="O42" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="P42" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="R42" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="S42" t="n">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
       <c r="T42" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U42" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V42" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W42" t="n">
         <v>1.33</v>
       </c>
       <c r="X42" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Y42" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.16</v>
+        <v>1.55</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.97</v>
+        <v>1.4</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5967,13 +5967,13 @@
         <v>2.83</v>
       </c>
       <c r="O43" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P43" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.77</v>
+        <v>3.67</v>
       </c>
       <c r="R43" t="n">
         <v>1.41</v>
@@ -5982,16 +5982,16 @@
         <v>2.58</v>
       </c>
       <c r="T43" t="n">
-        <v>2.99</v>
+        <v>3.08</v>
       </c>
       <c r="U43" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V43" t="n">
         <v>1.02</v>
       </c>
       <c r="W43" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="X43" t="n">
         <v>2.99</v>
@@ -6087,19 +6087,19 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="M44" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N44" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="O44" t="n">
         <v>2.9</v>
       </c>
       <c r="P44" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="Q44" t="n">
         <v>3.4</v>
@@ -6120,28 +6120,28 @@
         <v>1</v>
       </c>
       <c r="W44" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X44" t="n">
-        <v>3.38</v>
+        <v>3.85</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AA44" t="n">
         <v>3.24</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>3.1</v>
       </c>
       <c r="N45" t="n">
-        <v>3.57</v>
+        <v>3.3</v>
       </c>
       <c r="O45" t="n">
         <v>2.9</v>
@@ -6237,7 +6237,7 @@
         <v>1.57</v>
       </c>
       <c r="S45" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="T45" t="n">
         <v>3.3</v>
@@ -6255,10 +6255,10 @@
         <v>2.6</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AA45" t="n">
         <v>4.4</v>
@@ -6345,16 +6345,16 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.09</v>
+        <v>3.07</v>
       </c>
       <c r="M46" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="N46" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="O46" t="n">
-        <v>3.44</v>
+        <v>3.54</v>
       </c>
       <c r="P46" t="n">
         <v>2.41</v>
@@ -6363,10 +6363,10 @@
         <v>2.35</v>
       </c>
       <c r="R46" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S46" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="T46" t="n">
         <v>1.94</v>
@@ -6378,22 +6378,22 @@
         <v>1.01</v>
       </c>
       <c r="W46" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X46" t="n">
-        <v>5.86</v>
+        <v>5.95</v>
       </c>
       <c r="Y46" t="n">
         <v>1.4</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC46" t="n">
         <v>1.36</v>
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,77 +6474,77 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="M47" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N47" t="n">
-        <v>3.65</v>
+        <v>4.15</v>
       </c>
       <c r="O47" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="P47" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="Q47" t="n">
-        <v>4</v>
+        <v>4.85</v>
       </c>
       <c r="R47" t="n">
         <v>1.4</v>
       </c>
       <c r="S47" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="T47" t="n">
-        <v>3.13</v>
+        <v>2.99</v>
       </c>
       <c r="U47" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V47" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="W47" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="X47" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AA47" t="n">
-        <v>4.1</v>
+        <v>3.68</v>
       </c>
       <c r="AB47" t="n">
         <v>1.2</v>
       </c>
       <c r="AC47" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH47" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>1.69</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M48" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="O48" t="n">
         <v>2.7</v>
       </c>
-      <c r="M48" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="N48" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="O48" t="n">
-        <v>3.25</v>
-      </c>
       <c r="P48" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S48" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="T48" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="U48" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W48" t="n">
         <v>1.32</v>
       </c>
-      <c r="V48" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.38</v>
-      </c>
       <c r="X48" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AA48" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.43</v>
+        <v>1.7</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.82</v>
+        <v>2.51</v>
       </c>
       <c r="M49" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="O49" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q49" t="n">
         <v>3.35</v>
       </c>
-      <c r="N49" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="M50" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N50" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="O50" t="n">
         <v>3.65</v>
@@ -6879,7 +6879,7 @@
         <v>3.22</v>
       </c>
       <c r="R50" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S50" t="n">
         <v>2.42</v>
@@ -6900,10 +6900,10 @@
         <v>2.57</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AA50" t="n">
         <v>4.3</v>
@@ -6912,10 +6912,10 @@
         <v>1.15</v>
       </c>
       <c r="AC50" t="n">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6934,10 +6934,10 @@
         <v>1.41</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45950.8125</v>
@@ -6993,58 +6993,58 @@
         <v>1.93</v>
       </c>
       <c r="M51" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N51" t="n">
         <v>3.5</v>
       </c>
-      <c r="N51" t="n">
-        <v>3.4</v>
-      </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7119,19 +7119,19 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="M52" t="n">
-        <v>3.7</v>
+        <v>3.53</v>
       </c>
       <c r="N52" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="O52" t="n">
         <v>2.18</v>
       </c>
       <c r="P52" t="n">
-        <v>2.26</v>
+        <v>2.09</v>
       </c>
       <c r="Q52" t="n">
         <v>5.95</v>
@@ -7143,7 +7143,7 @@
         <v>2.65</v>
       </c>
       <c r="T52" t="n">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="U52" t="n">
         <v>1.33</v>
@@ -7158,13 +7158,13 @@
         <v>2.94</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AA52" t="n">
-        <v>4.2</v>
+        <v>3.82</v>
       </c>
       <c r="AB52" t="n">
         <v>1.2</v>
@@ -7173,7 +7173,7 @@
         <v>2.1</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AH52" t="n">
         <v>2.27</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45950.29166666666</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1258,10 +1258,10 @@
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45950.29166666666</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,22 +1701,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,22 +1959,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>3.49</v>
+        <v>3.2</v>
       </c>
       <c r="O13" t="n">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45950.45833333334</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>3.49</v>
       </c>
       <c r="O14" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="P14" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45950.45833333334</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5</v>
+        <v>1.55</v>
       </c>
       <c r="M17" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="O17" t="n">
-        <v>6.71</v>
+        <v>2.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.95</v>
+        <v>5.25</v>
       </c>
       <c r="R17" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="T17" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="X17" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.08</v>
+        <v>3.35</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.09</v>
+        <v>2.14</v>
       </c>
       <c r="AI17" t="n">
-        <v>3.5</v>
+        <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.34</v>
+        <v>2.95</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45950.5</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="O18" t="n">
-        <v>2.2</v>
+        <v>3.14</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.25</v>
+        <v>2.75</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="U18" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="V18" t="n">
         <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="X18" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.35</v>
+        <v>2.81</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.14</v>
+        <v>1.4</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.95</v>
+        <v>1.89</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45950.5</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="N19" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="O19" t="n">
-        <v>3.14</v>
+        <v>6.71</v>
       </c>
       <c r="P19" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="Q19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T19" t="n">
         <v>2.75</v>
       </c>
-      <c r="R19" t="n">
+      <c r="U19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB19" t="n">
         <v>1.3</v>
       </c>
-      <c r="S19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AC19" t="n">
-        <v>1.5</v>
+        <v>1.98</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.25</v>
+        <v>1.74</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.4</v>
+        <v>1.09</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.89</v>
+        <v>1.34</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45950.5</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,37 +3249,37 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M22" t="n">
         <v>3</v>
       </c>
       <c r="N22" t="n">
-        <v>4.05</v>
+        <v>3.35</v>
       </c>
       <c r="O22" t="n">
-        <v>2.98</v>
+        <v>2.54</v>
       </c>
       <c r="P22" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.72</v>
+        <v>5.77</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="S22" t="n">
-        <v>2.06</v>
+        <v>2.38</v>
       </c>
       <c r="T22" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="U22" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="V22" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="W22" t="n">
         <v>1.55</v>
@@ -3288,22 +3288,22 @@
         <v>2.3</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.21</v>
+        <v>2.45</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AA22" t="n">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.66</v>
+        <v>1.86</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,37 +3378,37 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
         <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="O23" t="n">
-        <v>2.54</v>
+        <v>2.98</v>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.77</v>
+        <v>4.72</v>
       </c>
       <c r="R23" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="S23" t="n">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="T23" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="U23" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="V23" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="W23" t="n">
         <v>1.55</v>
@@ -3417,22 +3417,22 @@
         <v>2.3</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.45</v>
+        <v>3.21</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,77 +3507,77 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="M24" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>3.63</v>
       </c>
       <c r="O24" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="P24" t="n">
         <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.87</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="T24" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="X24" t="n">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.81</v>
+        <v>2.87</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AC24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.62</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,61 +3636,61 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>5.4</v>
+        <v>2.25</v>
       </c>
       <c r="M25" t="n">
-        <v>3.99</v>
+        <v>3.34</v>
       </c>
       <c r="N25" t="n">
-        <v>1.46</v>
+        <v>3.1</v>
       </c>
       <c r="O25" t="n">
-        <v>5.57</v>
+        <v>2.75</v>
       </c>
       <c r="P25" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>3.87</v>
       </c>
       <c r="R25" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="T25" t="n">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="U25" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="V25" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W25" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="X25" t="n">
-        <v>4.06</v>
+        <v>3.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.65</v>
+        <v>2.11</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.71</v>
+        <v>3.81</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>2.38</v>
+        <v>1.26</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.1</v>
+        <v>1.62</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="M26" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="N26" t="n">
-        <v>3.63</v>
+        <v>4.3</v>
       </c>
       <c r="O26" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="P26" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S26" t="n">
-        <v>2.85</v>
+        <v>2.6</v>
       </c>
       <c r="T26" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="X26" t="n">
-        <v>3.42</v>
+        <v>2.95</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.87</v>
+        <v>3.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.73</v>
+        <v>2.04</v>
       </c>
       <c r="AD26" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.82</v>
+        <v>2.55</v>
       </c>
       <c r="M27" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="N27" t="n">
-        <v>3.67</v>
+        <v>2.5</v>
       </c>
       <c r="O27" t="n">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="P27" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.63</v>
+        <v>2.99</v>
       </c>
       <c r="R27" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="T27" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="U27" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W27" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="X27" t="n">
-        <v>3.12</v>
+        <v>3.66</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.6</v>
+        <v>3.08</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.77</v>
+        <v>1.49</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="M28" t="n">
-        <v>3.69</v>
+        <v>3.36</v>
       </c>
       <c r="N28" t="n">
-        <v>3.89</v>
+        <v>3.67</v>
       </c>
       <c r="O28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P28" t="n">
         <v>2.25</v>
       </c>
-      <c r="P28" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>4.63</v>
       </c>
       <c r="R28" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="S28" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="T28" t="n">
-        <v>2.34</v>
+        <v>2.8</v>
       </c>
       <c r="U28" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="X28" t="n">
-        <v>4.74</v>
+        <v>3.12</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.57</v>
+        <v>1.94</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.35</v>
+        <v>3.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.55</v>
+        <v>1.81</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>3.69</v>
       </c>
       <c r="N29" t="n">
-        <v>4.3</v>
+        <v>3.89</v>
       </c>
       <c r="O29" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="P29" t="n">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="S29" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="T29" t="n">
-        <v>3</v>
+        <v>2.34</v>
       </c>
       <c r="U29" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="V29" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="X29" t="n">
-        <v>2.95</v>
+        <v>4.74</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.05</v>
+        <v>1.57</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.9</v>
+        <v>2.35</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.04</v>
+        <v>1.55</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.55</v>
+        <v>5.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.38</v>
+        <v>3.99</v>
       </c>
       <c r="N30" t="n">
-        <v>2.5</v>
+        <v>1.46</v>
       </c>
       <c r="O30" t="n">
-        <v>2.95</v>
+        <v>5.57</v>
       </c>
       <c r="P30" t="n">
-        <v>2.11</v>
+        <v>2.45</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.99</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="S30" t="n">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="T30" t="n">
-        <v>2.74</v>
+        <v>2.38</v>
       </c>
       <c r="U30" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="V30" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="X30" t="n">
-        <v>3.66</v>
+        <v>4.06</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.08</v>
+        <v>2.71</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.49</v>
+        <v>1.1</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="M33" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N33" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="O33" t="n">
-        <v>2.55</v>
+        <v>2.99</v>
       </c>
       <c r="P33" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="R33" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="S33" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="T33" t="n">
         <v>2.23</v>
       </c>
       <c r="U33" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="V33" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X33" t="n">
-        <v>4.25</v>
+        <v>4.85</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="M34" t="n">
-        <v>3.6</v>
+        <v>4.85</v>
       </c>
       <c r="N34" t="n">
-        <v>2.45</v>
+        <v>1.44</v>
       </c>
       <c r="O34" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="P34" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.85</v>
+        <v>1.9</v>
       </c>
       <c r="R34" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="S34" t="n">
-        <v>3.52</v>
+        <v>4.2</v>
       </c>
       <c r="T34" t="n">
-        <v>2.23</v>
+        <v>1.9</v>
       </c>
       <c r="U34" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="V34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X34" t="n">
-        <v>5.15</v>
+        <v>6.55</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.38</v>
+        <v>3.04</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.31</v>
+        <v>1.86</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.55</v>
+        <v>1.94</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.46</v>
+        <v>1.13</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4926,16 +4926,16 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="M35" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N35" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O35" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="P35" t="n">
         <v>2.55</v>
@@ -4950,10 +4950,10 @@
         <v>3.6</v>
       </c>
       <c r="T35" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="U35" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="V35" t="n">
         <v>1.01</v>
@@ -4971,16 +4971,16 @@
         <v>2.55</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB35" t="n">
         <v>1.62</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AH35" t="n">
         <v>1.68</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="M36" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N36" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>5</v>
+        <v>2.85</v>
       </c>
       <c r="M37" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="O37" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.3</v>
+        <v>1.83</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.19</v>
+        <v>1.87</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,77 +5442,77 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.82</v>
+        <v>3.27</v>
       </c>
       <c r="M39" t="n">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="N39" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="O39" t="n">
-        <v>4.4</v>
+        <v>4.05</v>
       </c>
       <c r="P39" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.69</v>
+        <v>2.82</v>
       </c>
       <c r="R39" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="S39" t="n">
         <v>2.43</v>
       </c>
       <c r="T39" t="n">
-        <v>3.28</v>
+        <v>3.18</v>
       </c>
       <c r="U39" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH39" t="n">
         <v>1.27</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X39" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.16</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.27</v>
+        <v>3.82</v>
       </c>
       <c r="M40" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="N40" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="O40" t="n">
-        <v>4.05</v>
+        <v>4.4</v>
       </c>
       <c r="P40" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.82</v>
+        <v>2.69</v>
       </c>
       <c r="R40" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="S40" t="n">
         <v>2.43</v>
       </c>
       <c r="T40" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="U40" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="V40" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W40" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="X40" t="n">
-        <v>2.85</v>
+        <v>2.52</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AA40" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AC40" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.67</v>
+        <v>2.88</v>
       </c>
       <c r="M41" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N41" t="n">
-        <v>4.33</v>
+        <v>2.49</v>
       </c>
       <c r="O41" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="P41" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.55</v>
+        <v>3</v>
       </c>
       <c r="R41" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="S41" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T41" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U41" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V41" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W41" t="n">
         <v>1.33</v>
       </c>
       <c r="X41" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.27</v>
+        <v>1.55</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.17</v>
+        <v>1.4</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,77 +5829,77 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="M42" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="O42" t="n">
         <v>3.1</v>
       </c>
-      <c r="N42" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="O42" t="n">
-        <v>3.4</v>
-      </c>
       <c r="P42" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q42" t="n">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="R42" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="S42" t="n">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="T42" t="n">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="U42" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X42" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
         <v>1.33</v>
       </c>
-      <c r="V42" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AH42" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="M43" t="n">
-        <v>3.01</v>
+        <v>3.45</v>
       </c>
       <c r="N43" t="n">
-        <v>2.83</v>
+        <v>4.33</v>
       </c>
       <c r="O43" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="P43" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.67</v>
+        <v>4.55</v>
       </c>
       <c r="R43" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S43" t="n">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="T43" t="n">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="U43" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="V43" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W43" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X43" t="n">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AA43" t="n">
         <v>3.44</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.52</v>
+        <v>2.17</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="M48" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="N48" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="O48" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P48" t="n">
         <v>2.01</v>
       </c>
-      <c r="M48" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="N48" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="O48" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P48" t="n">
-        <v>2.05</v>
-      </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="R48" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S48" t="n">
         <v>2.6</v>
       </c>
       <c r="T48" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="U48" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V48" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W48" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="X48" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="Y48" t="n">
         <v>2.25</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.51</v>
+        <v>2.01</v>
       </c>
       <c r="M49" t="n">
-        <v>3.09</v>
+        <v>2.94</v>
       </c>
       <c r="N49" t="n">
-        <v>2.51</v>
+        <v>3.53</v>
       </c>
       <c r="O49" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="P49" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="R49" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S49" t="n">
         <v>2.6</v>
       </c>
       <c r="T49" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="U49" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W49" t="n">
         <v>1.32</v>
       </c>
-      <c r="V49" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.38</v>
-      </c>
       <c r="X49" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="Y49" t="n">
         <v>2.25</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AA49" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="M4" t="n">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>2.59</v>
+        <v>2.9</v>
       </c>
       <c r="O4" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="P4" t="n">
         <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.01</v>
+        <v>3.55</v>
       </c>
       <c r="R4" t="n">
         <v>1.4</v>
@@ -954,7 +954,7 @@
         <v>2.9</v>
       </c>
       <c r="U4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AI4" t="n">
         <v>1.81</v>
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="N5" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O5" t="n">
         <v>2.87</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1443,34 +1443,34 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
         <v>2.38</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="P8" t="n">
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.29</v>
+        <v>3.18</v>
       </c>
       <c r="R8" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="T8" t="n">
         <v>2.89</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V8" t="n">
         <v>1.02</v>
@@ -1479,19 +1479,19 @@
         <v>1.29</v>
       </c>
       <c r="X8" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AA8" t="n">
         <v>3.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AC8" t="n">
         <v>1.7</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AI8" t="n">
         <v>1.99</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,22 +1701,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.9</v>
+        <v>2.32</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>3.49</v>
       </c>
       <c r="O10" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
         <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1774,10 +1774,10 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45950.41666666666</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.35</v>
+        <v>1.9</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="N11" t="n">
-        <v>1.7</v>
+        <v>3.98</v>
       </c>
       <c r="O11" t="n">
-        <v>4.8</v>
+        <v>2.62</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.24</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.76</v>
+        <v>2.75</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.99</v>
+        <v>1.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.66</v>
+        <v>1.72</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.51</v>
+        <v>2.87</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45950.41666666666</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45950.41666666666</v>
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,19 +2155,19 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45950.45833333334</v>
+        <v>45950.41666666666</v>
       </c>
     </row>
     <row r="14">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.32</v>
+        <v>2.11</v>
       </c>
       <c r="M14" t="n">
-        <v>2.6</v>
+        <v>3.19</v>
       </c>
       <c r="N14" t="n">
-        <v>3.49</v>
+        <v>3.15</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>2.69</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45950.45833333334</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>1.39</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>4.35</v>
       </c>
       <c r="N15" t="n">
-        <v>2.5</v>
+        <v>7.7</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,16 +2413,16 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45950.47916666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.33</v>
+        <v>2.6</v>
       </c>
       <c r="M16" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45950.47916666666</v>
@@ -2604,19 +2604,19 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N17" t="n">
-        <v>5.3</v>
+        <v>4.75</v>
       </c>
       <c r="O17" t="n">
         <v>2.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="Q17" t="n">
         <v>5.25</v>
@@ -2640,13 +2640,13 @@
         <v>1.35</v>
       </c>
       <c r="X17" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AA17" t="n">
         <v>3.35</v>
@@ -2655,7 +2655,7 @@
         <v>1.31</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AD17" t="n">
         <v>1.83</v>
@@ -2733,28 +2733,28 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.2</v>
+        <v>2.62</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>1.6</v>
+        <v>2.31</v>
       </c>
       <c r="O18" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
         <v>2.75</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T18" t="n">
         <v>2.5</v>
@@ -2772,13 +2772,13 @@
         <v>4.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="Z18" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="AB18" t="n">
         <v>1.42</v>
@@ -2787,7 +2787,7 @@
         <v>1.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI18" t="n">
         <v>1.95</v>
@@ -2862,37 +2862,37 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="M19" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="O19" t="n">
-        <v>6.71</v>
+        <v>5.13</v>
       </c>
       <c r="P19" t="n">
         <v>2.13</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="R19" t="n">
         <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="T19" t="n">
         <v>2.75</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V19" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
         <v>1.22</v>
@@ -2901,13 +2901,13 @@
         <v>3.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="AB19" t="n">
         <v>1.3</v>
@@ -2916,7 +2916,7 @@
         <v>1.98</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.21</v>
+        <v>2.71</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AI19" t="n">
         <v>3.5</v>
@@ -2991,28 +2991,28 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9</v>
+        <v>3.29</v>
       </c>
       <c r="N20" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O20" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="P20" t="n">
         <v>2.04</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="S20" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T20" t="n">
         <v>3.5</v>
@@ -3021,31 +3021,31 @@
         <v>1.25</v>
       </c>
       <c r="V20" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W20" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="X20" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AA20" t="n">
         <v>4.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45950.52083333334</v>
@@ -3120,16 +3120,16 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="M21" t="n">
         <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O21" t="n">
-        <v>4.22</v>
+        <v>4.18</v>
       </c>
       <c r="P21" t="n">
         <v>2.2</v>
@@ -3138,7 +3138,7 @@
         <v>2.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
         <v>3.15</v>
@@ -3147,34 +3147,34 @@
         <v>2.38</v>
       </c>
       <c r="U21" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="V21" t="n">
         <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="X21" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="Y21" t="n">
         <v>2.04</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3190,13 +3190,13 @@
         <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45950.54166666666</v>
@@ -3249,46 +3249,46 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N22" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="O22" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="P22" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.77</v>
+        <v>4.52</v>
       </c>
       <c r="R22" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S22" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="T22" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="U22" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="V22" t="n">
         <v>1.04</v>
       </c>
       <c r="W22" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="X22" t="n">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="Z22" t="n">
         <v>1.46</v>
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45950.5625</v>
@@ -3378,16 +3378,16 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="N23" t="n">
-        <v>4.05</v>
+        <v>3.92</v>
       </c>
       <c r="O23" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="P23" t="n">
         <v>1.75</v>
@@ -3396,7 +3396,7 @@
         <v>4.72</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="S23" t="n">
         <v>2.06</v>
@@ -3405,34 +3405,34 @@
         <v>4.25</v>
       </c>
       <c r="U23" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="V23" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="W23" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="X23" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.21</v>
+        <v>2.97</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AB23" t="n">
         <v>1.06</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,16 +3445,16 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45950.5625</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,40 +3507,40 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.84</v>
+        <v>2.45</v>
       </c>
       <c r="M24" t="n">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>3.63</v>
+        <v>2.5</v>
       </c>
       <c r="O24" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="P24" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>3.02</v>
       </c>
       <c r="R24" t="n">
         <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>2.85</v>
+        <v>2.91</v>
       </c>
       <c r="T24" t="n">
-        <v>2.55</v>
+        <v>2.74</v>
       </c>
       <c r="U24" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W24" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X24" t="n">
         <v>3.42</v>
@@ -3552,13 +3552,13 @@
         <v>1.85</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.87</v>
+        <v>3.08</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AD24" t="n">
         <v>2</v>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45950.58333333334</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="M25" t="n">
-        <v>3.34</v>
+        <v>3.53</v>
       </c>
       <c r="N25" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="O25" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="P25" t="n">
         <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.87</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="T25" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="U25" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="V25" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="X25" t="n">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.11</v>
+        <v>1.92</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.81</v>
+        <v>2.91</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AC25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.75</v>
       </c>
-      <c r="AD25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45950.58333333334</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="M26" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="P26" t="n">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.33</v>
+        <v>3.85</v>
       </c>
       <c r="R26" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="T26" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U26" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V26" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X26" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45950.58333333334</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="M27" t="n">
-        <v>3.38</v>
+        <v>3.75</v>
       </c>
       <c r="N27" t="n">
+        <v>4</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA27" t="n">
         <v>2.5</v>
       </c>
-      <c r="O27" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X27" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3.08</v>
-      </c>
       <c r="AB27" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AD27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH27" t="n">
         <v>2</v>
       </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45950.58333333334</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.82</v>
+        <v>5.25</v>
       </c>
       <c r="M28" t="n">
-        <v>3.36</v>
+        <v>4.1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.67</v>
+        <v>1.52</v>
       </c>
       <c r="O28" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T28" t="n">
         <v>2.4</v>
       </c>
-      <c r="P28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.8</v>
-      </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W28" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="X28" t="n">
-        <v>3.12</v>
+        <v>4</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.94</v>
+        <v>1.58</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.76</v>
+        <v>2.09</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.6</v>
+        <v>2.71</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.77</v>
+        <v>1.08</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45950.58333333334</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
-        <v>3.69</v>
+        <v>3.1</v>
       </c>
       <c r="N29" t="n">
-        <v>3.89</v>
+        <v>3.45</v>
       </c>
       <c r="O29" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y29" t="n">
         <v>2.25</v>
       </c>
-      <c r="P29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>4</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X29" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.57</v>
-      </c>
       <c r="Z29" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.35</v>
+        <v>4.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.6</v>
+        <v>1.21</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AH29" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45950.58333333334</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>5.4</v>
+        <v>1.82</v>
       </c>
       <c r="M30" t="n">
-        <v>3.99</v>
+        <v>3.36</v>
       </c>
       <c r="N30" t="n">
-        <v>1.46</v>
+        <v>3.67</v>
       </c>
       <c r="O30" t="n">
-        <v>5.57</v>
+        <v>2.48</v>
       </c>
       <c r="P30" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>4.63</v>
       </c>
       <c r="R30" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="S30" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X30" t="n">
         <v>3.25</v>
       </c>
-      <c r="T30" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X30" t="n">
-        <v>4.06</v>
-      </c>
       <c r="Y30" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.1</v>
+        <v>1.76</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.71</v>
+        <v>3.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>2.38</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.1</v>
+        <v>1.83</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45950.58333333334</v>
@@ -4419,7 +4419,7 @@
         <v>2.54</v>
       </c>
       <c r="O31" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P31" t="n">
         <v>2.17</v>
@@ -4458,10 +4458,10 @@
         <v>3</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AD31" t="n">
         <v>2.15</v>
@@ -4477,16 +4477,16 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH31" t="n">
         <v>1.48</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45950.59027777778</v>
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="M32" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="N32" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="O32" t="n">
         <v>4</v>
@@ -4578,13 +4578,13 @@
         <v>2.85</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.94</v>
+        <v>2.33</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AB32" t="n">
         <v>1.22</v>
@@ -4593,7 +4593,7 @@
         <v>1.96</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4609,13 +4609,13 @@
         <v>1.28</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45950.60416666666</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="M33" t="n">
-        <v>3.45</v>
+        <v>4.85</v>
       </c>
       <c r="N33" t="n">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="O33" t="n">
-        <v>2.99</v>
+        <v>4.75</v>
       </c>
       <c r="P33" t="n">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.85</v>
+        <v>1.9</v>
       </c>
       <c r="R33" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="S33" t="n">
-        <v>3.52</v>
+        <v>4.2</v>
       </c>
       <c r="T33" t="n">
-        <v>2.23</v>
+        <v>1.9</v>
       </c>
       <c r="U33" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="V33" t="n">
         <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X33" t="n">
-        <v>4.85</v>
+        <v>6.55</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.53</v>
+        <v>1.34</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.38</v>
+        <v>3.04</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.31</v>
+        <v>1.86</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.58</v>
+        <v>1.94</v>
       </c>
       <c r="AC33" t="n">
         <v>1.44</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.48</v>
+        <v>1.13</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="M34" t="n">
-        <v>4.85</v>
+        <v>3.45</v>
       </c>
       <c r="N34" t="n">
-        <v>1.44</v>
+        <v>2.5</v>
       </c>
       <c r="O34" t="n">
-        <v>4.75</v>
+        <v>2.99</v>
       </c>
       <c r="P34" t="n">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.9</v>
+        <v>2.85</v>
       </c>
       <c r="R34" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="S34" t="n">
-        <v>4.2</v>
+        <v>3.52</v>
       </c>
       <c r="T34" t="n">
-        <v>1.9</v>
+        <v>2.23</v>
       </c>
       <c r="U34" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="V34" t="n">
         <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X34" t="n">
-        <v>6.55</v>
+        <v>4.85</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.04</v>
+        <v>2.38</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.86</v>
+        <v>2.31</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.94</v>
+        <v>1.58</v>
       </c>
       <c r="AC34" t="n">
         <v>1.44</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.13</v>
+        <v>1.48</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="M36" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>2.7</v>
+        <v>2.14</v>
       </c>
       <c r="O36" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="P36" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="R36" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,16 +5122,16 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45950.625</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="M37" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.13</v>
+        <v>3.1</v>
       </c>
       <c r="M38" t="n">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="N38" t="n">
-        <v>3.77</v>
+        <v>2.17</v>
       </c>
       <c r="O38" t="n">
-        <v>2.75</v>
+        <v>4.05</v>
       </c>
       <c r="P38" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.25</v>
+        <v>2.82</v>
       </c>
       <c r="R38" t="n">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="S38" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Y38" t="n">
         <v>2.25</v>
       </c>
-      <c r="T38" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Z38" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AA38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,16 +5380,16 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.66</v>
+        <v>1.26</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45950.64583333334</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,61 +5442,61 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.27</v>
+        <v>3.6</v>
       </c>
       <c r="M39" t="n">
-        <v>3.08</v>
+        <v>2.82</v>
       </c>
       <c r="N39" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="O39" t="n">
-        <v>4.05</v>
+        <v>4.4</v>
       </c>
       <c r="P39" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="R39" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="S39" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="T39" t="n">
-        <v>3.18</v>
+        <v>3.28</v>
       </c>
       <c r="U39" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="V39" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W39" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="X39" t="n">
-        <v>2.85</v>
+        <v>2.55</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AA39" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AC39" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,16 +5509,16 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45950.64583333334</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.82</v>
+        <v>2.08</v>
       </c>
       <c r="M40" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="N40" t="n">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="O40" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="P40" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.69</v>
+        <v>4.25</v>
       </c>
       <c r="R40" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="S40" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="T40" t="n">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="U40" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="V40" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W40" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="X40" t="n">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.25</v>
+        <v>2.83</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="AA40" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,16 +5638,16 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.16</v>
+        <v>1.63</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45950.64583333334</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.88</v>
+        <v>1.7</v>
       </c>
       <c r="M41" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N41" t="n">
-        <v>2.49</v>
+        <v>4.55</v>
       </c>
       <c r="O41" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="P41" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q41" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="R41" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="S41" t="n">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="T41" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U41" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V41" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W41" t="n">
         <v>1.33</v>
       </c>
       <c r="X41" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,16 +5767,16 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.55</v>
+        <v>1.26</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45950.65625</v>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="M42" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="N42" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="O42" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P42" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.67</v>
+        <v>3.81</v>
       </c>
       <c r="R42" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S42" t="n">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="T42" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="U42" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V42" t="n">
         <v>1.02</v>
       </c>
       <c r="W42" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X42" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
         <v>1.3</v>
       </c>
-      <c r="X42" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH42" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45950.65625</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.67</v>
+        <v>3.15</v>
       </c>
       <c r="M43" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N43" t="n">
-        <v>4.33</v>
+        <v>2.45</v>
       </c>
       <c r="O43" t="n">
-        <v>2.2</v>
+        <v>3.85</v>
       </c>
       <c r="P43" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.55</v>
+        <v>3</v>
       </c>
       <c r="R43" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="S43" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T43" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="U43" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V43" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W43" t="n">
         <v>1.33</v>
       </c>
       <c r="X43" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,16 +6025,16 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.27</v>
+        <v>1.55</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.17</v>
+        <v>1.4</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45950.65625</v>
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="M44" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N44" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="O44" t="n">
         <v>2.9</v>
@@ -6123,25 +6123,25 @@
         <v>1.27</v>
       </c>
       <c r="X44" t="n">
-        <v>3.85</v>
+        <v>3.38</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="Z44" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AA44" t="n">
         <v>3.24</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AC44" t="n">
         <v>1.71</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6160,10 +6160,10 @@
         <v>1.49</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45950.66666666666</v>
@@ -6219,10 +6219,10 @@
         <v>2.25</v>
       </c>
       <c r="M45" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N45" t="n">
-        <v>3.3</v>
+        <v>3.54</v>
       </c>
       <c r="O45" t="n">
         <v>2.9</v>
@@ -6237,7 +6237,7 @@
         <v>1.57</v>
       </c>
       <c r="S45" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="T45" t="n">
         <v>3.3</v>
@@ -6258,7 +6258,7 @@
         <v>2.46</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AA45" t="n">
         <v>4.4</v>
@@ -6289,10 +6289,10 @@
         <v>1.6</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45950.66666666666</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.51</v>
+        <v>2.01</v>
       </c>
       <c r="M48" t="n">
-        <v>3.09</v>
+        <v>2.94</v>
       </c>
       <c r="N48" t="n">
-        <v>2.51</v>
+        <v>3.53</v>
       </c>
       <c r="O48" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="P48" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S48" t="n">
         <v>2.6</v>
       </c>
       <c r="T48" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="U48" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W48" t="n">
         <v>1.32</v>
       </c>
-      <c r="V48" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.38</v>
-      </c>
       <c r="X48" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="Y48" t="n">
         <v>2.25</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AA48" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="O49" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P49" t="n">
         <v>2.01</v>
       </c>
-      <c r="M49" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="N49" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="O49" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P49" t="n">
-        <v>2.05</v>
-      </c>
       <c r="Q49" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="R49" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S49" t="n">
         <v>2.6</v>
       </c>
       <c r="T49" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="U49" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V49" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W49" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="X49" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="Y49" t="n">
         <v>2.25</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AA49" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="M51" t="n">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="N51" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="O51" t="n">
-        <v>2.55</v>
+        <v>2.18</v>
       </c>
       <c r="P51" t="n">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.86</v>
+        <v>5.95</v>
       </c>
       <c r="R51" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="S51" t="n">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="T51" t="n">
-        <v>2.58</v>
+        <v>3.04</v>
       </c>
       <c r="U51" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="V51" t="n">
         <v>1.01</v>
       </c>
       <c r="W51" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="X51" t="n">
-        <v>3.76</v>
+        <v>2.94</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.83</v>
+        <v>3.82</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,10 +7057,10 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.69</v>
+        <v>2.27</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="M52" t="n">
-        <v>3.53</v>
+        <v>3.6</v>
       </c>
       <c r="N52" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="O52" t="n">
-        <v>2.18</v>
+        <v>2.55</v>
       </c>
       <c r="P52" t="n">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.95</v>
+        <v>3.86</v>
       </c>
       <c r="R52" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S52" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="U52" t="n">
         <v>1.42</v>
-      </c>
-      <c r="S52" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T52" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.33</v>
       </c>
       <c r="V52" t="n">
         <v>1.01</v>
       </c>
       <c r="W52" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="X52" t="n">
-        <v>2.94</v>
+        <v>3.76</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AA52" t="n">
-        <v>3.82</v>
+        <v>2.83</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AH52" t="n">
-        <v>2.27</v>
+        <v>1.69</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -927,25 +927,25 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="M4" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
         <v>2.9</v>
       </c>
       <c r="O4" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="P4" t="n">
         <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.55</v>
+        <v>3.88</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
         <v>2.69</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45950.29166666666</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45950.29166666666</v>
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="M8" t="n">
         <v>3.15</v>
       </c>
       <c r="N8" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="O8" t="n">
         <v>2.94</v>
@@ -1458,19 +1458,19 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="R8" t="n">
         <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="T8" t="n">
         <v>2.89</v>
       </c>
       <c r="U8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="V8" t="n">
         <v>1.02</v>
@@ -1479,25 +1479,25 @@
         <v>1.29</v>
       </c>
       <c r="X8" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Z8" t="n">
         <v>1.79</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AC8" t="n">
         <v>1.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>1.42</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AI8" t="n">
         <v>1.99</v>
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45950.38541666666</v>
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="M10" t="n">
         <v>2.6</v>
       </c>
       <c r="N10" t="n">
-        <v>3.49</v>
+        <v>3.26</v>
       </c>
       <c r="O10" t="n">
         <v>3.1</v>
@@ -1734,16 +1734,16 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45950.41666666666</v>
@@ -1968,19 +1968,19 @@
         <v>1.7</v>
       </c>
       <c r="O12" t="n">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="P12" t="n">
         <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="T12" t="n">
         <v>2.5</v>
@@ -1992,16 +1992,16 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X12" t="n">
-        <v>3.7</v>
+        <v>3.88</v>
       </c>
       <c r="Y12" t="n">
         <v>1.76</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AA12" t="n">
         <v>2.83</v>
@@ -2010,10 +2010,10 @@
         <v>1.38</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AI12" t="n">
         <v>2.66</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45950.41666666666</v>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="M14" t="n">
         <v>3.19</v>
@@ -2259,7 +2259,7 @@
         <v>2.49</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="AA14" t="n">
         <v>4.3</v>
@@ -2271,7 +2271,7 @@
         <v>1.98</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="AI14" t="n">
         <v>1.84</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.39</v>
+        <v>2.7</v>
       </c>
       <c r="M15" t="n">
-        <v>4.35</v>
+        <v>2.92</v>
       </c>
       <c r="N15" t="n">
-        <v>7.7</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
-        <v>1.85</v>
+        <v>2.98</v>
       </c>
       <c r="P15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y15" t="n">
         <v>2.35</v>
       </c>
-      <c r="Q15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.91</v>
-      </c>
       <c r="Z15" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.08</v>
+        <v>4.05</v>
       </c>
       <c r="AB15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
         <v>1.3</v>
       </c>
-      <c r="AC15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AH15" t="n">
-        <v>2.75</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45950.47916666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>1.39</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="N16" t="n">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45950.47916666666</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.65</v>
+        <v>4.2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>4.75</v>
+        <v>1.6</v>
       </c>
       <c r="O17" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.25</v>
+        <v>2.75</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="T17" t="n">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="U17" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="V17" t="n">
         <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
-        <v>3.14</v>
+        <v>4.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.14</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.95</v>
+        <v>1.89</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45950.5</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.62</v>
+        <v>5.6</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>2.31</v>
+        <v>1.44</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>5.13</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.75</v>
+        <v>1.98</v>
       </c>
       <c r="R18" t="n">
         <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U18" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X18" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.5</v>
+        <v>1.98</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.15</v>
+        <v>1.74</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>2.67</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.44</v>
+        <v>1.07</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.89</v>
+        <v>1.34</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45950.5</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.6</v>
+        <v>1.7</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>1.41</v>
+        <v>4.75</v>
       </c>
       <c r="O19" t="n">
-        <v>5.13</v>
+        <v>2.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.13</v>
+        <v>2.28</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.98</v>
+        <v>5.25</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>3.08</v>
+        <v>2.77</v>
       </c>
       <c r="T19" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="U19" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="X19" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z19" t="n">
         <v>1.82</v>
       </c>
-      <c r="Z19" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AA19" t="n">
-        <v>2.97</v>
+        <v>3.35</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>2.71</v>
+        <v>1.23</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.07</v>
+        <v>2.12</v>
       </c>
       <c r="AI19" t="n">
-        <v>3.5</v>
+        <v>1.55</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.34</v>
+        <v>2.95</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45950.5</v>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.29</v>
+        <v>3.07</v>
       </c>
       <c r="N20" t="n">
         <v>3.4</v>
@@ -3009,7 +3009,7 @@
         <v>4.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="S20" t="n">
         <v>2.36</v>
@@ -3033,19 +3033,19 @@
         <v>2.38</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AA20" t="n">
         <v>4.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AH20" t="n">
         <v>1.75</v>
@@ -3126,7 +3126,7 @@
         <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="O21" t="n">
         <v>4.18</v>
@@ -3135,34 +3135,34 @@
         <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="T21" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="U21" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
         <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="X21" t="n">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="Y21" t="n">
         <v>2.04</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AA21" t="n">
         <v>3.34</v>
@@ -3171,10 +3171,10 @@
         <v>1.24</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AI21" t="n">
         <v>2.4</v>
@@ -3252,7 +3252,7 @@
         <v>1.75</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="N22" t="n">
         <v>4.4</v>
@@ -3267,10 +3267,10 @@
         <v>4.52</v>
       </c>
       <c r="R22" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S22" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T22" t="n">
         <v>3.58</v>
@@ -3282,28 +3282,28 @@
         <v>1.04</v>
       </c>
       <c r="W22" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="X22" t="n">
-        <v>2.58</v>
+        <v>2.49</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="Z22" t="n">
         <v>1.46</v>
       </c>
       <c r="AA22" t="n">
-        <v>4.9</v>
+        <v>4.85</v>
       </c>
       <c r="AB22" t="n">
         <v>1.11</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3381,13 +3381,13 @@
         <v>2.18</v>
       </c>
       <c r="M23" t="n">
-        <v>3.11</v>
+        <v>2.69</v>
       </c>
       <c r="N23" t="n">
         <v>3.92</v>
       </c>
       <c r="O23" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="P23" t="n">
         <v>1.75</v>
@@ -3396,43 +3396,43 @@
         <v>4.72</v>
       </c>
       <c r="R23" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="S23" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="T23" t="n">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="U23" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="V23" t="n">
         <v>1.16</v>
       </c>
       <c r="W23" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="X23" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AA23" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AI23" t="n">
         <v>1.81</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,62 +3507,62 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="O24" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X24" t="n">
         <v>3.25</v>
       </c>
-      <c r="P24" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.42</v>
-      </c>
       <c r="Y24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.85</v>
       </c>
-      <c r="Z24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2</v>
-      </c>
       <c r="AE24" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="AI24" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45950.58333333334</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,55 +3636,55 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.97</v>
+        <v>2.45</v>
       </c>
       <c r="M25" t="n">
-        <v>3.53</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="O25" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="P25" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>3.02</v>
       </c>
       <c r="R25" t="n">
         <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="T25" t="n">
-        <v>2.55</v>
+        <v>2.74</v>
       </c>
       <c r="U25" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W25" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X25" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AC25" t="n">
         <v>1.67</v>
@@ -3703,16 +3703,16 @@
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45950.58333333334</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.25</v>
+        <v>5.4</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.99</v>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>1.46</v>
       </c>
       <c r="O26" t="n">
-        <v>2.75</v>
+        <v>5.57</v>
       </c>
       <c r="P26" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.85</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S26" t="n">
-        <v>2.63</v>
+        <v>3.12</v>
       </c>
       <c r="T26" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="U26" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="V26" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W26" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="X26" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.11</v>
+        <v>1.65</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.85</v>
+        <v>2.71</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.2</v>
+        <v>1.45</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45950.58333333334</v>
@@ -3894,10 +3894,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="M27" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N27" t="n">
         <v>4</v>
@@ -3936,7 +3936,7 @@
         <v>1.54</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="AA27" t="n">
         <v>2.5</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>5.25</v>
+        <v>2.4</v>
       </c>
       <c r="M28" t="n">
-        <v>4.1</v>
+        <v>3.16</v>
       </c>
       <c r="N28" t="n">
-        <v>1.52</v>
+        <v>3.07</v>
       </c>
       <c r="O28" t="n">
-        <v>5.57</v>
+        <v>2.75</v>
       </c>
       <c r="P28" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>3.85</v>
       </c>
       <c r="R28" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>3.12</v>
+        <v>2.69</v>
       </c>
       <c r="T28" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="U28" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="V28" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="W28" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="X28" t="n">
-        <v>4</v>
+        <v>2.99</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.58</v>
+        <v>2.11</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.09</v>
+        <v>1.83</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.71</v>
+        <v>3.85</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.08</v>
+        <v>1.6</v>
       </c>
       <c r="AI28" t="n">
-        <v>3</v>
+        <v>1.85</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45950.58333333334</v>
@@ -4152,10 +4152,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="M29" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N29" t="n">
         <v>3.45</v>
@@ -4164,16 +4164,16 @@
         <v>2.62</v>
       </c>
       <c r="P29" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="R29" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S29" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="T29" t="n">
         <v>3.1</v>
@@ -4188,25 +4188,25 @@
         <v>1.41</v>
       </c>
       <c r="X29" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AA29" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AB29" t="n">
         <v>1.21</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="M30" t="n">
-        <v>3.36</v>
+        <v>3.53</v>
       </c>
       <c r="N30" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="O30" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="P30" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.63</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>2.69</v>
+        <v>3.05</v>
       </c>
       <c r="T30" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="U30" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V30" t="n">
         <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X30" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.6</v>
+        <v>2.91</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45950.58333333334</v>
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="M31" t="n">
-        <v>3.26</v>
+        <v>3.52</v>
       </c>
       <c r="N31" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -4425,7 +4425,7 @@
         <v>2.17</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="R31" t="n">
         <v>1.35</v>
@@ -4449,19 +4449,19 @@
         <v>4.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AA31" t="n">
         <v>3</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AD31" t="n">
         <v>2.15</v>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AI31" t="n">
         <v>2</v>
@@ -4548,25 +4548,25 @@
         <v>2.05</v>
       </c>
       <c r="O32" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P32" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="R32" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S32" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="T32" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U32" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="V32" t="n">
         <v>1.03</v>
@@ -4575,25 +4575,25 @@
         <v>1.39</v>
       </c>
       <c r="X32" t="n">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AA32" t="n">
         <v>4.3</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
         <v>1.21</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5.5</v>
+        <v>2.64</v>
       </c>
       <c r="M33" t="n">
-        <v>4.85</v>
+        <v>3.6</v>
       </c>
       <c r="N33" t="n">
-        <v>1.44</v>
+        <v>2.39</v>
       </c>
       <c r="O33" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>2.65</v>
+        <v>2.34</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="R33" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="S33" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="T33" t="n">
-        <v>1.9</v>
+        <v>2.23</v>
       </c>
       <c r="U33" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="V33" t="n">
         <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="X33" t="n">
-        <v>6.55</v>
+        <v>5.22</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.04</v>
+        <v>2.4</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.86</v>
+        <v>2.32</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.94</v>
+        <v>1.57</v>
       </c>
       <c r="AC33" t="n">
         <v>1.44</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.13</v>
+        <v>1.45</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45950.625</v>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="M34" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="O34" t="n">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="P34" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="R34" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="T34" t="n">
         <v>2.23</v>
       </c>
       <c r="U34" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W34" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X34" t="n">
-        <v>4.85</v>
+        <v>4.78</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45950.625</v>
@@ -4926,16 +4926,16 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="M35" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N35" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O35" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="P35" t="n">
         <v>2.55</v>
@@ -4944,16 +4944,16 @@
         <v>3.3</v>
       </c>
       <c r="R35" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S35" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T35" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="U35" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="V35" t="n">
         <v>1.01</v>
@@ -4965,22 +4965,22 @@
         <v>5.6</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AB35" t="n">
         <v>1.62</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.76</v>
+        <v>2.61</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AH35" t="n">
         <v>1.68</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45950.625</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="M36" t="n">
-        <v>3.4</v>
+        <v>4.45</v>
       </c>
       <c r="N36" t="n">
-        <v>2.14</v>
+        <v>1.41</v>
       </c>
       <c r="O36" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="P36" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.1</v>
+        <v>1.83</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="Y36" t="n">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.8</v>
+        <v>3.04</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,16 +5122,16 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI36" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.95</v>
+        <v>1.45</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45950.625</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.3</v>
+        <v>3.55</v>
       </c>
       <c r="M37" t="n">
         <v>3.25</v>
       </c>
       <c r="N37" t="n">
-        <v>2.7</v>
+        <v>1.83</v>
       </c>
       <c r="O37" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="P37" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="R37" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,16 +5251,16 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45950.625</v>
@@ -5334,10 +5334,10 @@
         <v>1.46</v>
       </c>
       <c r="S38" t="n">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="T38" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="U38" t="n">
         <v>1.31</v>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AI38" t="n">
         <v>2.3</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.6</v>
+        <v>2.08</v>
       </c>
       <c r="M39" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y39" t="n">
         <v>2.82</v>
       </c>
-      <c r="N39" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="O39" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X39" t="n">
+      <c r="Z39" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ39" t="n">
         <v>2.55</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.76</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45950.64583333334</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,61 +5571,61 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.08</v>
+        <v>3.7</v>
       </c>
       <c r="M40" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="N40" t="n">
-        <v>3.75</v>
+        <v>1.98</v>
       </c>
       <c r="O40" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q40" t="n">
         <v>2.75</v>
       </c>
-      <c r="P40" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>4.25</v>
-      </c>
       <c r="R40" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="S40" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="T40" t="n">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="U40" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="V40" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W40" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="X40" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AA40" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,16 +5638,16 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.63</v>
+        <v>1.16</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.55</v>
+        <v>1.76</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45950.64583333334</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="M41" t="n">
-        <v>3.4</v>
+        <v>3.01</v>
       </c>
       <c r="N41" t="n">
-        <v>4.55</v>
+        <v>2.83</v>
       </c>
       <c r="O41" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="P41" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="R41" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="S41" t="n">
-        <v>2.69</v>
+        <v>2.58</v>
       </c>
       <c r="T41" t="n">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="U41" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V41" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W41" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X41" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
         <v>1.33</v>
       </c>
-      <c r="X41" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH41" t="n">
-        <v>2.05</v>
+        <v>1.54</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45950.65625</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.33</v>
+        <v>3.15</v>
       </c>
       <c r="M42" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O42" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T42" t="n">
         <v>3</v>
       </c>
-      <c r="N42" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O42" t="n">
-        <v>3</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.88</v>
-      </c>
       <c r="U42" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V42" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W42" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="X42" t="n">
         <v>3</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,16 +5896,16 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AJ42" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45950.65625</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.15</v>
+        <v>1.67</v>
       </c>
       <c r="M43" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N43" t="n">
-        <v>2.45</v>
+        <v>4.33</v>
       </c>
       <c r="O43" t="n">
-        <v>3.85</v>
+        <v>2.2</v>
       </c>
       <c r="P43" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="Q43" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="R43" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="S43" t="n">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="T43" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U43" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V43" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W43" t="n">
         <v>1.33</v>
       </c>
       <c r="X43" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,16 +6025,16 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.55</v>
+        <v>1.26</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="AI43" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45950.65625</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.53</v>
+        <v>2.25</v>
       </c>
       <c r="M44" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N44" t="n">
-        <v>2.8</v>
+        <v>3.54</v>
       </c>
       <c r="O44" t="n">
         <v>2.9</v>
       </c>
       <c r="P44" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="R44" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="T44" t="n">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="U44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W44" t="n">
         <v>1.44</v>
       </c>
-      <c r="V44" t="n">
-        <v>1</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.27</v>
-      </c>
       <c r="X44" t="n">
-        <v>3.38</v>
+        <v>2.6</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.9</v>
+        <v>2.46</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.92</v>
+        <v>1.54</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.24</v>
+        <v>4.45</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.22</v>
+        <v>1.73</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6157,13 +6157,13 @@
         <v>1.33</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AJ44" t="n">
-        <v>2.05</v>
+        <v>2.47</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45950.66666666666</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="M45" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="N45" t="n">
-        <v>3.54</v>
+        <v>2.8</v>
       </c>
       <c r="O45" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P45" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="R45" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="S45" t="n">
-        <v>2.39</v>
+        <v>2.93</v>
       </c>
       <c r="T45" t="n">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="U45" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X45" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AB45" t="n">
         <v>1.3</v>
       </c>
-      <c r="V45" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X45" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AC45" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.73</v>
+        <v>2.26</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6286,13 +6286,13 @@
         <v>1.33</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AJ45" t="n">
-        <v>2.47</v>
+        <v>2.05</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45950.66666666666</v>
@@ -6354,7 +6354,7 @@
         <v>1.86</v>
       </c>
       <c r="O46" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="P46" t="n">
         <v>2.41</v>
@@ -6363,25 +6363,25 @@
         <v>2.35</v>
       </c>
       <c r="R46" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S46" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="T46" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U46" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V46" t="n">
         <v>1.01</v>
       </c>
       <c r="W46" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X46" t="n">
-        <v>5.95</v>
+        <v>5.4</v>
       </c>
       <c r="Y46" t="n">
         <v>1.4</v>
@@ -6396,10 +6396,10 @@
         <v>1.8</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6415,13 +6415,13 @@
         <v>1.25</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45950.67708333334</v>
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.8</v>
+        <v>2.51</v>
       </c>
       <c r="M47" t="n">
-        <v>3.5</v>
+        <v>3.09</v>
       </c>
       <c r="N47" t="n">
-        <v>4.15</v>
+        <v>2.51</v>
       </c>
       <c r="O47" t="n">
-        <v>2.45</v>
+        <v>3.25</v>
       </c>
       <c r="P47" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.85</v>
+        <v>3.35</v>
       </c>
       <c r="R47" t="n">
         <v>1.4</v>
       </c>
       <c r="S47" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="T47" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="U47" t="n">
         <v>1.32</v>
       </c>
       <c r="V47" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W47" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="X47" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="M48" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="N48" t="n">
-        <v>3.53</v>
+        <v>3.9</v>
       </c>
       <c r="O48" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S48" t="n">
         <v>2.7</v>
       </c>
-      <c r="P48" t="n">
+      <c r="T48" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X48" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y48" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q48" t="n">
-        <v>4</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T48" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X48" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Z48" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,16 +6670,16 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45950.79166666666</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.51</v>
+        <v>2.01</v>
       </c>
       <c r="M49" t="n">
-        <v>3.09</v>
+        <v>2.94</v>
       </c>
       <c r="N49" t="n">
-        <v>2.51</v>
+        <v>3.53</v>
       </c>
       <c r="O49" t="n">
-        <v>3.25</v>
+        <v>2.65</v>
       </c>
       <c r="P49" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="R49" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S49" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="T49" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="U49" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V49" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W49" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="X49" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="Y49" t="n">
         <v>2.25</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AA49" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,16 +6799,16 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45950.79166666666</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="M51" t="n">
-        <v>3.53</v>
+        <v>3.25</v>
       </c>
       <c r="N51" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="O51" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="P51" t="n">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="Q51" t="n">
-        <v>5.95</v>
+        <v>3.98</v>
       </c>
       <c r="R51" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="S51" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="T51" t="n">
-        <v>3.04</v>
+        <v>2.55</v>
       </c>
       <c r="U51" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="V51" t="n">
         <v>1.01</v>
       </c>
       <c r="W51" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="X51" t="n">
-        <v>2.94</v>
+        <v>3.76</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AA51" t="n">
-        <v>3.82</v>
+        <v>2.83</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AC51" t="n">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,16 +7057,16 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AH51" t="n">
-        <v>2.27</v>
+        <v>1.68</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45950.89583333334</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="M52" t="n">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="N52" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="O52" t="n">
-        <v>2.55</v>
+        <v>2.18</v>
       </c>
       <c r="P52" t="n">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.86</v>
+        <v>5.95</v>
       </c>
       <c r="R52" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="S52" t="n">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="T52" t="n">
-        <v>2.58</v>
+        <v>3.04</v>
       </c>
       <c r="U52" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="V52" t="n">
         <v>1.01</v>
       </c>
       <c r="W52" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="X52" t="n">
-        <v>3.76</v>
+        <v>2.94</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.75</v>
+        <v>2.17</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.83</v>
+        <v>3.82</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.69</v>
+        <v>2.27</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nairobi United</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Nairobi United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1224,7 +1224,7 @@
         <v>2.83</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="Z6" t="n">
         <v>1.62</v>
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M9" t="n">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="N9" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="P9" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="R9" t="n">
         <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="T9" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="U9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V9" t="n">
         <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AI9" t="n">
         <v>1.4</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45950.41666666666</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45950.41666666666</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.9</v>
+        <v>4.35</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>3.86</v>
+        <v>1.7</v>
       </c>
       <c r="O13" t="n">
-        <v>2.65</v>
+        <v>4.95</v>
       </c>
       <c r="P13" t="n">
-        <v>1.86</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.25</v>
+        <v>2.2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.58</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
-        <v>2.24</v>
+        <v>3.02</v>
       </c>
       <c r="T13" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.21</v>
+        <v>1.45</v>
       </c>
       <c r="V13" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>2.3</v>
+        <v>1.24</v>
       </c>
       <c r="X13" t="n">
-        <v>1.55</v>
+        <v>3.88</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.65</v>
+        <v>1.76</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.42</v>
+        <v>1.97</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.2</v>
+        <v>2.83</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.1</v>
+        <v>1.38</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.28</v>
+        <v>1.73</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.55</v>
+        <v>1.97</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.72</v>
+        <v>1.14</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.72</v>
+        <v>2.66</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.87</v>
+        <v>1.51</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45950.41666666666</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.7</v>
+        <v>1.39</v>
       </c>
       <c r="M15" t="n">
-        <v>2.92</v>
+        <v>4.4</v>
       </c>
       <c r="N15" t="n">
+        <v>8</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH15" t="n">
         <v>2.75</v>
       </c>
-      <c r="O15" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AI15" t="n">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45950.47916666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,58 +2475,58 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.39</v>
+        <v>2.33</v>
       </c>
       <c r="M16" t="n">
-        <v>4.4</v>
+        <v>2.84</v>
       </c>
       <c r="N16" t="n">
-        <v>8</v>
+        <v>3.14</v>
       </c>
       <c r="O16" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="P16" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.5</v>
+        <v>3.3</v>
       </c>
       <c r="R16" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="S16" t="n">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.65</v>
+        <v>3.45</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="V16" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="W16" t="n">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="X16" t="n">
-        <v>3.42</v>
+        <v>2.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.08</v>
+        <v>4.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
         <v>1.67</v>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.75</v>
+        <v>1.4</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.36</v>
+        <v>1.9</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45950.47916666666</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>1.6</v>
+        <v>4.75</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.75</v>
+        <v>5.25</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>3.2</v>
+        <v>2.77</v>
       </c>
       <c r="T17" t="n">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="U17" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="V17" t="n">
         <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="X17" t="n">
-        <v>4.1</v>
+        <v>3.14</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="Z17" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>2.12</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.89</v>
+        <v>2.95</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45950.5</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.44</v>
       </c>
-      <c r="O18" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AI18" t="n">
-        <v>3.5</v>
+        <v>1.95</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.34</v>
+        <v>1.89</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45950.5</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.7</v>
+        <v>5.6</v>
       </c>
       <c r="M19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O19" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X19" t="n">
         <v>3.5</v>
       </c>
-      <c r="N19" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X19" t="n">
-        <v>3.14</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.35</v>
+        <v>3.04</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.23</v>
+        <v>2.67</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.12</v>
+        <v>1.07</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.55</v>
+        <v>3.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.95</v>
+        <v>1.34</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45950.5</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="O24" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.63</v>
+        <v>4.33</v>
       </c>
       <c r="R24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W24" t="n">
         <v>1.41</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.28</v>
-      </c>
       <c r="X24" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45950.58333333334</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5.4</v>
+        <v>1.73</v>
       </c>
       <c r="M26" t="n">
-        <v>3.99</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>1.46</v>
+        <v>4</v>
       </c>
       <c r="O26" t="n">
-        <v>5.57</v>
+        <v>2.25</v>
       </c>
       <c r="P26" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S26" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="T26" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V26" t="n">
         <v>1.04</v>
       </c>
       <c r="W26" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X26" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="AI26" t="n">
-        <v>3</v>
+        <v>1.61</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.45</v>
+        <v>2.37</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45950.58333333334</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="M27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N27" t="n">
         <v>3.6</v>
       </c>
-      <c r="N27" t="n">
-        <v>4</v>
-      </c>
       <c r="O27" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="P27" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>4.63</v>
       </c>
       <c r="R27" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB27" t="n">
         <v>1.29</v>
       </c>
-      <c r="S27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X27" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AC27" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45950.58333333334</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="O28" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T28" t="n">
         <v>2.4</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="N28" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.9</v>
-      </c>
       <c r="U28" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="V28" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W28" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="X28" t="n">
-        <v>2.99</v>
+        <v>4</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.11</v>
+        <v>1.65</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.85</v>
+        <v>2.71</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.2</v>
+        <v>1.45</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45950.58333333334</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>3.53</v>
       </c>
       <c r="N29" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O29" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="P29" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="T29" t="n">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="U29" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="V29" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="X29" t="n">
-        <v>2.7</v>
+        <v>3.42</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.24</v>
+        <v>1.9</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.61</v>
+        <v>2.02</v>
       </c>
       <c r="AA29" t="n">
-        <v>4</v>
+        <v>2.91</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45950.58333333334</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.53</v>
+        <v>3.16</v>
       </c>
       <c r="N30" t="n">
-        <v>3.5</v>
+        <v>3.07</v>
       </c>
       <c r="O30" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="P30" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="R30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
         <v>1.36</v>
       </c>
-      <c r="S30" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X30" t="n">
-        <v>3.42</v>
+        <v>2.99</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.9</v>
+        <v>2.11</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.91</v>
+        <v>3.85</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45950.58333333334</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.64</v>
+        <v>2.07</v>
       </c>
       <c r="M33" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N33" t="n">
-        <v>2.39</v>
+        <v>3.15</v>
       </c>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="P33" t="n">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="R33" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="S33" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="T33" t="n">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="U33" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="V33" t="n">
         <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X33" t="n">
-        <v>5.22</v>
+        <v>5.6</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.32</v>
+        <v>2.19</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.45</v>
+        <v>1.68</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45950.625</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.3</v>
+        <v>3.55</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N34" t="n">
-        <v>2.65</v>
+        <v>1.83</v>
       </c>
       <c r="O34" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="P34" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45950.625</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.07</v>
+        <v>2.64</v>
       </c>
       <c r="M35" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N35" t="n">
-        <v>3.15</v>
+        <v>2.39</v>
       </c>
       <c r="O35" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="P35" t="n">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="R35" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="T35" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="U35" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="V35" t="n">
         <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X35" t="n">
-        <v>5.6</v>
+        <v>5.22</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45950.625</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>5.5</v>
+        <v>2.3</v>
       </c>
       <c r="M36" t="n">
-        <v>4.45</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>1.41</v>
+        <v>2.65</v>
       </c>
       <c r="O36" t="n">
-        <v>5</v>
+        <v>2.85</v>
       </c>
       <c r="P36" t="n">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="R36" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="S36" t="n">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="T36" t="n">
-        <v>1.9</v>
+        <v>2.23</v>
       </c>
       <c r="U36" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X36" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AI36" t="n">
         <v>1.8</v>
       </c>
-      <c r="V36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X36" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AJ36" t="n">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45950.625</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.55</v>
+        <v>5.5</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>4.45</v>
       </c>
       <c r="N37" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O37" t="n">
+        <v>5</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q37" t="n">
         <v>1.83</v>
       </c>
-      <c r="O37" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>3.1</v>
-      </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="Y37" t="n">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.8</v>
+        <v>3.04</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,16 +5251,16 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI37" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.95</v>
+        <v>1.45</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45950.625</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.1</v>
+        <v>2.08</v>
       </c>
       <c r="M38" t="n">
-        <v>3.04</v>
+        <v>2.98</v>
       </c>
       <c r="N38" t="n">
-        <v>2.17</v>
+        <v>3.75</v>
       </c>
       <c r="O38" t="n">
-        <v>4.05</v>
+        <v>2.75</v>
       </c>
       <c r="P38" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="Q38" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y38" t="n">
         <v>2.82</v>
       </c>
-      <c r="R38" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Z38" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="AA38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,16 +5380,16 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="AI38" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.8</v>
+        <v>2.55</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45950.64583333334</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.08</v>
+        <v>3.27</v>
       </c>
       <c r="M39" t="n">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="N39" t="n">
-        <v>3.75</v>
+        <v>2.13</v>
       </c>
       <c r="O39" t="n">
-        <v>2.75</v>
+        <v>4.05</v>
       </c>
       <c r="P39" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.25</v>
+        <v>2.82</v>
       </c>
       <c r="R39" t="n">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="S39" t="n">
-        <v>2.25</v>
+        <v>2.57</v>
       </c>
       <c r="T39" t="n">
-        <v>3.75</v>
+        <v>3.17</v>
       </c>
       <c r="U39" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="V39" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="W39" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
         <v>1.56</v>
       </c>
-      <c r="X39" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH39" t="n">
-        <v>1.65</v>
+        <v>1.26</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AJ39" t="n">
-        <v>2.55</v>
+        <v>1.8</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45950.64583333334</v>
@@ -5571,28 +5571,28 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="M40" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N40" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O40" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="P40" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="R40" t="n">
         <v>1.52</v>
       </c>
       <c r="S40" t="n">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="T40" t="n">
         <v>3.28</v>
@@ -5610,10 +5610,10 @@
         <v>2.55</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AA40" t="n">
         <v>4.3</v>
@@ -5625,7 +5625,7 @@
         <v>2.05</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AH40" t="n">
         <v>1.16</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.3</v>
+        <v>3.15</v>
       </c>
       <c r="M41" t="n">
-        <v>3.01</v>
+        <v>3.06</v>
       </c>
       <c r="N41" t="n">
-        <v>2.83</v>
+        <v>2.45</v>
       </c>
       <c r="O41" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T41" t="n">
         <v>3</v>
-      </c>
-      <c r="P41" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S41" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T41" t="n">
-        <v>3.04</v>
       </c>
       <c r="U41" t="n">
         <v>1.33</v>
       </c>
       <c r="V41" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W41" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="X41" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="Y41" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC41" t="n">
         <v>1.93</v>
       </c>
-      <c r="Z41" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AD41" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5770,13 +5770,13 @@
         <v>1.33</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45950.65625</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="M42" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="N42" t="n">
-        <v>2.45</v>
+        <v>2.83</v>
       </c>
       <c r="O42" t="n">
-        <v>3.88</v>
+        <v>3</v>
       </c>
       <c r="P42" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="R42" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="S42" t="n">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="T42" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="U42" t="n">
         <v>1.33</v>
       </c>
       <c r="V42" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W42" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="X42" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.32</v>
+        <v>1.93</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="AA42" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5899,13 +5899,13 @@
         <v>1.33</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AI42" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45950.65625</v>
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="M43" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N43" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="O43" t="n">
         <v>2.2</v>
@@ -5985,7 +5985,7 @@
         <v>2.8</v>
       </c>
       <c r="U43" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="V43" t="n">
         <v>1</v>
@@ -5994,25 +5994,25 @@
         <v>1.33</v>
       </c>
       <c r="X43" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AA43" t="n">
         <v>3.38</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AC43" t="n">
         <v>1.99</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AI43" t="n">
         <v>1.6</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="M44" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N44" t="n">
-        <v>3.54</v>
+        <v>2.8</v>
       </c>
       <c r="O44" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P44" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="R44" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="S44" t="n">
-        <v>2.62</v>
+        <v>2.93</v>
       </c>
       <c r="T44" t="n">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="U44" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X44" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AB44" t="n">
         <v>1.3</v>
       </c>
-      <c r="V44" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X44" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AC44" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.73</v>
+        <v>2.26</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6157,13 +6157,13 @@
         <v>1.33</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AJ44" t="n">
-        <v>2.47</v>
+        <v>2.05</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45950.66666666666</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="M45" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T45" t="n">
         <v>3.3</v>
       </c>
-      <c r="N45" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O45" t="n">
-        <v>3</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S45" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.92</v>
-      </c>
       <c r="U45" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="V45" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="W45" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="X45" t="n">
-        <v>3.38</v>
+        <v>2.6</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.9</v>
+        <v>2.46</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.95</v>
+        <v>1.54</v>
       </c>
       <c r="AA45" t="n">
-        <v>3.18</v>
+        <v>4.45</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.26</v>
+        <v>1.73</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6286,13 +6286,13 @@
         <v>1.33</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AJ45" t="n">
-        <v>2.05</v>
+        <v>2.47</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45950.66666666666</v>
@@ -6345,16 +6345,16 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="M46" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="N46" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="O46" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="P46" t="n">
         <v>2.41</v>
@@ -6363,10 +6363,10 @@
         <v>2.35</v>
       </c>
       <c r="R46" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="T46" t="n">
         <v>1.95</v>
@@ -6381,25 +6381,25 @@
         <v>1.12</v>
       </c>
       <c r="X46" t="n">
-        <v>5.4</v>
+        <v>5.95</v>
       </c>
       <c r="Y46" t="n">
         <v>1.4</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AI46" t="n">
         <v>2.15</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,58 +6474,58 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.51</v>
+        <v>2</v>
       </c>
       <c r="M47" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="N47" t="n">
-        <v>2.51</v>
+        <v>3.5</v>
       </c>
       <c r="O47" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="P47" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="R47" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S47" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="T47" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="U47" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V47" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W47" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="X47" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AA47" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AD47" t="n">
         <v>1.85</v>
@@ -6541,16 +6541,16 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45950.79166666666</v>
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="M48" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N48" t="n">
-        <v>3.9</v>
+        <v>4.85</v>
       </c>
       <c r="O48" t="n">
-        <v>2.43</v>
+        <v>2.19</v>
       </c>
       <c r="P48" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.5</v>
+        <v>6.07</v>
       </c>
       <c r="R48" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S48" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="T48" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="U48" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V48" t="n">
         <v>1.03</v>
       </c>
       <c r="W48" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="X48" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Z48" t="n">
         <v>1.67</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.68</v>
+        <v>3.74</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.9</v>
+        <v>2.13</v>
       </c>
       <c r="AI48" t="n">
         <v>1.6</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,34 +6732,34 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.01</v>
+        <v>2.8</v>
       </c>
       <c r="M49" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="N49" t="n">
-        <v>3.53</v>
+        <v>2.5</v>
       </c>
       <c r="O49" t="n">
-        <v>2.65</v>
+        <v>3.46</v>
       </c>
       <c r="P49" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Q49" t="n">
-        <v>4</v>
+        <v>3.31</v>
       </c>
       <c r="R49" t="n">
         <v>1.44</v>
       </c>
       <c r="S49" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="T49" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="U49" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V49" t="n">
         <v>1.02</v>
@@ -6771,23 +6771,23 @@
         <v>2.9</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AA49" t="n">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AC49" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD49" t="n">
         <v>1.83</v>
       </c>
-      <c r="AD49" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AE49" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6799,16 +6799,16 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.74</v>
+        <v>2.1</v>
       </c>
       <c r="AJ49" t="n">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45950.79166666666</v>
@@ -6861,28 +6861,28 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.4</v>
+        <v>2.82</v>
       </c>
       <c r="M50" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="N50" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="O50" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="P50" t="n">
         <v>1.92</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="R50" t="n">
         <v>1.52</v>
       </c>
       <c r="S50" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="T50" t="n">
         <v>3.34</v>
@@ -6894,19 +6894,19 @@
         <v>1.04</v>
       </c>
       <c r="W50" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="X50" t="n">
         <v>2.57</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AA50" t="n">
-        <v>4.3</v>
+        <v>4.75</v>
       </c>
       <c r="AB50" t="n">
         <v>1.15</v>
@@ -6928,7 +6928,7 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AH50" t="n">
         <v>1.41</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.9</v>
+        <v>1.56</v>
       </c>
       <c r="M51" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="N51" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="O51" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="P51" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.98</v>
+        <v>5.8</v>
       </c>
       <c r="R51" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="U51" t="n">
         <v>1.33</v>
       </c>
-      <c r="S51" t="n">
-        <v>3</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.45</v>
-      </c>
       <c r="V51" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W51" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="X51" t="n">
-        <v>3.76</v>
+        <v>3.1</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.83</v>
+        <v>4.2</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.63</v>
+        <v>2.08</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.12</v>
+        <v>1.67</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,16 +7057,16 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.68</v>
+        <v>2.29</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AJ51" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45950.89583333334</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="M52" t="n">
-        <v>3.53</v>
+        <v>3.25</v>
       </c>
       <c r="N52" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="O52" t="n">
-        <v>2.18</v>
+        <v>2.53</v>
       </c>
       <c r="P52" t="n">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.95</v>
+        <v>4.06</v>
       </c>
       <c r="R52" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="S52" t="n">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="T52" t="n">
-        <v>3.04</v>
+        <v>2.5</v>
       </c>
       <c r="U52" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="V52" t="n">
         <v>1.01</v>
       </c>
       <c r="W52" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="X52" t="n">
-        <v>2.94</v>
+        <v>3.7</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="AA52" t="n">
-        <v>3.82</v>
+        <v>2.8</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.6</v>
+        <v>2.09</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,16 +7186,16 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AH52" t="n">
-        <v>2.27</v>
+        <v>1.71</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45950.89583333334</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -794,7 +794,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -927,19 +927,19 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="M4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N4" t="n">
         <v>3</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.9</v>
       </c>
       <c r="O4" t="n">
         <v>2.94</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q4" t="n">
         <v>3.88</v>
@@ -948,7 +948,7 @@
         <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="T4" t="n">
         <v>2.9</v>
@@ -960,16 +960,16 @@
         <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="X4" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="Y4" t="n">
         <v>1.95</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AA4" t="n">
         <v>3.28</v>
@@ -1224,7 +1224,7 @@
         <v>2.83</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="Z6" t="n">
         <v>1.62</v>
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="M8" t="n">
         <v>3.15</v>
       </c>
       <c r="N8" t="n">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="O8" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="P8" t="n">
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="T8" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="U8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="X8" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="AB8" t="n">
         <v>1.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AI8" t="n">
         <v>1.99</v>
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="M9" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="N9" t="n">
-        <v>7.5</v>
+        <v>6.2</v>
       </c>
       <c r="O9" t="n">
         <v>1.83</v>
@@ -1611,10 +1611,10 @@
         <v>3.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AA9" t="n">
         <v>3.1</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.28</v>
+        <v>4.35</v>
       </c>
       <c r="M10" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>3.26</v>
+        <v>1.7</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>4.95</v>
       </c>
       <c r="P10" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>2.39</v>
+        <v>1.24</v>
       </c>
       <c r="X10" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.51</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>2.5</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45950.41666666666</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45950.41666666666</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,22 +1959,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1992,16 +1992,16 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2032,10 +2032,10 @@
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45950.41666666666</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.35</v>
+        <v>1.84</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>2.97</v>
       </c>
       <c r="N13" t="n">
-        <v>1.7</v>
+        <v>4.31</v>
       </c>
       <c r="O13" t="n">
-        <v>4.95</v>
+        <v>2.65</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>1.86</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.2</v>
+        <v>5.25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="S13" t="n">
-        <v>3.02</v>
+        <v>2.23</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="U13" t="n">
-        <v>1.45</v>
+        <v>1.21</v>
       </c>
       <c r="V13" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="W13" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="X13" t="n">
-        <v>3.88</v>
+        <v>2.28</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.76</v>
+        <v>2.75</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.97</v>
+        <v>1.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.83</v>
+        <v>5.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.38</v>
+        <v>1.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.73</v>
+        <v>2.28</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.97</v>
+        <v>1.55</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.14</v>
+        <v>1.72</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.66</v>
+        <v>1.72</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.51</v>
+        <v>2.87</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45950.41666666666</v>
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="M14" t="n">
-        <v>3.19</v>
+        <v>2.9</v>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
         <v>2.69</v>
@@ -2235,7 +2235,7 @@
         <v>3.58</v>
       </c>
       <c r="R14" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="S14" t="n">
         <v>2.44</v>
@@ -2244,7 +2244,7 @@
         <v>3.35</v>
       </c>
       <c r="U14" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
         <v>1.03</v>
@@ -2253,13 +2253,13 @@
         <v>1.39</v>
       </c>
       <c r="X14" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AA14" t="n">
         <v>4.3</v>
@@ -2271,7 +2271,7 @@
         <v>1.98</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="M15" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="N15" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="O15" t="n">
         <v>1.9</v>
@@ -2364,7 +2364,7 @@
         <v>6.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S15" t="n">
         <v>2.88</v>
@@ -2379,13 +2379,13 @@
         <v>1</v>
       </c>
       <c r="W15" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X15" t="n">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="Z15" t="n">
         <v>1.89</v>
@@ -2416,7 +2416,7 @@
         <v>1.12</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="AI15" t="n">
         <v>1.36</v>
@@ -2604,19 +2604,19 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="M17" t="n">
         <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>4.75</v>
+        <v>5.3</v>
       </c>
       <c r="O17" t="n">
         <v>2.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="Q17" t="n">
         <v>5.25</v>
@@ -2625,7 +2625,7 @@
         <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
         <v>2.81</v>
@@ -2640,13 +2640,13 @@
         <v>1.35</v>
       </c>
       <c r="X17" t="n">
-        <v>3.14</v>
+        <v>3.47</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AA17" t="n">
         <v>3.35</v>
@@ -2655,7 +2655,7 @@
         <v>1.26</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AD17" t="n">
         <v>1.83</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="N18" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>6.35</v>
       </c>
       <c r="P18" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.75</v>
+        <v>1.94</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
       <c r="U18" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="X18" t="n">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.44</v>
+        <v>1.1</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.89</v>
+        <v>1.34</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45950.5</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="N19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.44</v>
       </c>
-      <c r="O19" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AI19" t="n">
-        <v>3.5</v>
+        <v>1.95</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.34</v>
+        <v>1.89</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45950.5</v>
@@ -2991,28 +2991,28 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="N20" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O20" t="n">
         <v>2.71</v>
       </c>
       <c r="P20" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q20" t="n">
         <v>4.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="S20" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T20" t="n">
         <v>3.5</v>
@@ -3021,19 +3021,19 @@
         <v>1.25</v>
       </c>
       <c r="V20" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W20" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="X20" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AA20" t="n">
         <v>4.65</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,62 +3249,62 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="P22" t="n">
         <v>1.75</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="N22" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.93</v>
-      </c>
       <c r="Q22" t="n">
-        <v>4.52</v>
+        <v>4.72</v>
       </c>
       <c r="R22" t="n">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="S22" t="n">
-        <v>2.36</v>
+        <v>2.05</v>
       </c>
       <c r="T22" t="n">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="U22" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="V22" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="W22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.48</v>
       </c>
-      <c r="X22" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AE22" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45950.5625</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC23" t="n">
         <v>2.18</v>
       </c>
-      <c r="M23" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AD23" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,16 +3445,16 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45950.5625</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>3.07</v>
       </c>
       <c r="O24" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="R24" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="T24" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W24" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="X24" t="n">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="AA24" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,16 +3574,16 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.76</v>
+        <v>1.59</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.52</v>
+        <v>2.2</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45950.58333333334</v>
@@ -3765,31 +3765,31 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>3.69</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="O26" t="n">
         <v>2.25</v>
       </c>
       <c r="P26" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="Q26" t="n">
         <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="S26" t="n">
         <v>3.4</v>
       </c>
       <c r="T26" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="U26" t="n">
         <v>1.53</v>
@@ -3798,28 +3798,28 @@
         <v>1.04</v>
       </c>
       <c r="W26" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X26" t="n">
-        <v>4.7</v>
+        <v>4.87</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>1.2</v>
       </c>
       <c r="AH26" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AI26" t="n">
         <v>1.61</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.98</v>
+        <v>5.4</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>3.99</v>
       </c>
       <c r="N27" t="n">
-        <v>3.6</v>
+        <v>1.46</v>
       </c>
       <c r="O27" t="n">
-        <v>2.48</v>
+        <v>5.62</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.63</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="S27" t="n">
-        <v>2.69</v>
+        <v>3.12</v>
       </c>
       <c r="T27" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W27" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="X27" t="n">
-        <v>3.25</v>
+        <v>3.98</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.6</v>
+        <v>2.61</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.83</v>
+        <v>1.1</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.55</v>
+        <v>1.45</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45950.58333333334</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>5.4</v>
+        <v>1.98</v>
       </c>
       <c r="M28" t="n">
-        <v>3.99</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>1.46</v>
+        <v>3.6</v>
       </c>
       <c r="O28" t="n">
-        <v>5.57</v>
+        <v>2.48</v>
       </c>
       <c r="P28" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>4.63</v>
       </c>
       <c r="R28" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="S28" t="n">
-        <v>3.12</v>
+        <v>2.69</v>
       </c>
       <c r="T28" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="U28" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="X28" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.71</v>
+        <v>3.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.1</v>
+        <v>1.83</v>
       </c>
       <c r="AI28" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.45</v>
+        <v>2.55</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45950.58333333334</v>
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.96</v>
+        <v>1.84</v>
       </c>
       <c r="M29" t="n">
-        <v>3.53</v>
+        <v>3.33</v>
       </c>
       <c r="N29" t="n">
-        <v>3.5</v>
+        <v>3.63</v>
       </c>
       <c r="O29" t="n">
         <v>2.5</v>
@@ -4170,16 +4170,16 @@
         <v>4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S29" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="T29" t="n">
         <v>2.55</v>
       </c>
       <c r="U29" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V29" t="n">
         <v>1.01</v>
@@ -4188,19 +4188,19 @@
         <v>1.25</v>
       </c>
       <c r="X29" t="n">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AC29" t="n">
         <v>1.7</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="M30" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="N30" t="n">
-        <v>3.07</v>
+        <v>4.3</v>
       </c>
       <c r="O30" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.85</v>
+        <v>4.33</v>
       </c>
       <c r="R30" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S30" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="T30" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="U30" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V30" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="X30" t="n">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.2</v>
+        <v>2.52</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45950.58333333334</v>
@@ -4539,28 +4539,28 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="N32" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="O32" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="P32" t="n">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="S32" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="T32" t="n">
         <v>3.2</v>
@@ -4569,31 +4569,31 @@
         <v>1.27</v>
       </c>
       <c r="V32" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W32" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X32" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.35</v>
+        <v>1.94</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AI32" t="n">
         <v>2.6</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.07</v>
+        <v>5.5</v>
       </c>
       <c r="M33" t="n">
-        <v>3.75</v>
+        <v>4.45</v>
       </c>
       <c r="N33" t="n">
-        <v>3.15</v>
+        <v>1.41</v>
       </c>
       <c r="O33" t="n">
-        <v>2.55</v>
+        <v>5</v>
       </c>
       <c r="P33" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.3</v>
+        <v>1.83</v>
       </c>
       <c r="R33" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="T33" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="U33" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="V33" t="n">
         <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="X33" t="n">
-        <v>5.6</v>
+        <v>6.55</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.6</v>
+        <v>3.04</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.19</v>
+        <v>1.88</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.68</v>
+        <v>1.11</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.77</v>
+        <v>2.75</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45950.625</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.55</v>
+        <v>2.3</v>
       </c>
       <c r="M34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S34" t="n">
         <v>3.25</v>
       </c>
-      <c r="N34" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="O34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="Y34" t="n">
-        <v>2</v>
+        <v>1.58</v>
       </c>
       <c r="Z34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AI34" t="n">
         <v>1.8</v>
       </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AJ34" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45950.625</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.64</v>
+        <v>2.07</v>
       </c>
       <c r="M35" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N35" t="n">
-        <v>2.39</v>
+        <v>3.15</v>
       </c>
       <c r="O35" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="P35" t="n">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="R35" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="S35" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="T35" t="n">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="U35" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="V35" t="n">
         <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X35" t="n">
-        <v>5.22</v>
+        <v>5.6</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.32</v>
+        <v>2.19</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.45</v>
+        <v>1.68</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45950.625</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,62 +5055,62 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="M36" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N36" t="n">
-        <v>2.65</v>
+        <v>2.39</v>
       </c>
       <c r="O36" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="P36" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="R36" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="S36" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="T36" t="n">
         <v>2.23</v>
       </c>
       <c r="U36" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="V36" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X36" t="n">
-        <v>4.78</v>
+        <v>5.22</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AA36" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD36" t="n">
         <v>2.5</v>
       </c>
-      <c r="AB36" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AE36" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5122,16 +5122,16 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AJ36" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45950.625</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>5.5</v>
+        <v>2.85</v>
       </c>
       <c r="M37" t="n">
-        <v>4.45</v>
+        <v>3.4</v>
       </c>
       <c r="N37" t="n">
-        <v>1.41</v>
+        <v>2.3</v>
       </c>
       <c r="O37" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="P37" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="Q37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
         <v>1.83</v>
       </c>
-      <c r="R37" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S37" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X37" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.29</v>
-      </c>
       <c r="Z37" t="n">
-        <v>3.04</v>
+        <v>1.87</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,16 +5251,16 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45950.625</v>
@@ -5313,25 +5313,25 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="M38" t="n">
         <v>2.98</v>
       </c>
       <c r="N38" t="n">
-        <v>3.75</v>
+        <v>3.77</v>
       </c>
       <c r="O38" t="n">
         <v>2.75</v>
       </c>
       <c r="P38" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="Q38" t="n">
         <v>4.25</v>
       </c>
       <c r="R38" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S38" t="n">
         <v>2.25</v>
@@ -5346,16 +5346,16 @@
         <v>1.08</v>
       </c>
       <c r="W38" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="X38" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AA38" t="n">
         <v>5</v>
@@ -5700,25 +5700,25 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="M41" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="N41" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="O41" t="n">
-        <v>3.88</v>
+        <v>3.4</v>
       </c>
       <c r="P41" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.88</v>
+        <v>3.16</v>
       </c>
       <c r="R41" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S41" t="n">
         <v>2.63</v>
@@ -5736,22 +5736,22 @@
         <v>1.41</v>
       </c>
       <c r="X41" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AA41" t="n">
         <v>4.2</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AD41" t="n">
         <v>1.85</v>
@@ -5841,7 +5841,7 @@
         <v>3</v>
       </c>
       <c r="P42" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="Q42" t="n">
         <v>3.8</v>
@@ -5853,7 +5853,7 @@
         <v>2.58</v>
       </c>
       <c r="T42" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="U42" t="n">
         <v>1.33</v>
@@ -5880,7 +5880,7 @@
         <v>1.22</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AD42" t="n">
         <v>1.9</v>
@@ -5958,49 +5958,49 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="M43" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N43" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="O43" t="n">
         <v>2.2</v>
       </c>
       <c r="P43" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.7</v>
+        <v>4.33</v>
       </c>
       <c r="R43" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S43" t="n">
         <v>2.69</v>
       </c>
       <c r="T43" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="U43" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="V43" t="n">
         <v>1</v>
       </c>
       <c r="W43" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="X43" t="n">
         <v>3.3</v>
       </c>
       <c r="Y43" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AA43" t="n">
         <v>3.38</v>
@@ -6009,10 +6009,10 @@
         <v>1.24</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6087,34 +6087,34 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="M44" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N44" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="O44" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P44" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q44" t="n">
         <v>3.4</v>
       </c>
       <c r="R44" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S44" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="T44" t="n">
         <v>2.92</v>
       </c>
       <c r="U44" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="V44" t="n">
         <v>1</v>
@@ -6123,13 +6123,13 @@
         <v>1.27</v>
       </c>
       <c r="X44" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AA44" t="n">
         <v>3.18</v>
@@ -6141,7 +6141,7 @@
         <v>1.68</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>1.33</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AI44" t="n">
         <v>1.9</v>
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="M46" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="N46" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="O46" t="n">
         <v>3.54</v>
@@ -6387,13 +6387,13 @@
         <v>1.4</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AC46" t="n">
         <v>1.36</v>
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="M47" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="N47" t="n">
-        <v>3.5</v>
+        <v>4.85</v>
       </c>
       <c r="O47" t="n">
-        <v>2.75</v>
+        <v>2.19</v>
       </c>
       <c r="P47" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q47" t="n">
-        <v>4</v>
+        <v>6.07</v>
       </c>
       <c r="R47" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S47" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="T47" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="U47" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V47" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W47" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="X47" t="n">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.58</v>
+        <v>3.74</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.83</v>
+        <v>2.03</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.7</v>
+        <v>2.13</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="AJ47" t="n">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45950.79166666666</v>
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,61 +6603,61 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.55</v>
+        <v>2.51</v>
       </c>
       <c r="M48" t="n">
-        <v>3.8</v>
+        <v>3.09</v>
       </c>
       <c r="N48" t="n">
-        <v>4.85</v>
+        <v>2.51</v>
       </c>
       <c r="O48" t="n">
-        <v>2.19</v>
+        <v>3.46</v>
       </c>
       <c r="P48" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Q48" t="n">
-        <v>6.07</v>
+        <v>3.31</v>
       </c>
       <c r="R48" t="n">
         <v>1.44</v>
       </c>
       <c r="S48" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="T48" t="n">
-        <v>3.05</v>
+        <v>3.22</v>
       </c>
       <c r="U48" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="V48" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W48" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="X48" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AA48" t="n">
-        <v>3.74</v>
+        <v>4.2</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,16 +6670,16 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="AH48" t="n">
-        <v>2.13</v>
+        <v>1.37</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AJ48" t="n">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45950.79166666666</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.8</v>
+        <v>2.01</v>
       </c>
       <c r="M49" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="N49" t="n">
-        <v>2.5</v>
+        <v>3.53</v>
       </c>
       <c r="O49" t="n">
-        <v>3.46</v>
+        <v>2.75</v>
       </c>
       <c r="P49" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.31</v>
+        <v>4</v>
       </c>
       <c r="R49" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S49" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="T49" t="n">
-        <v>3.22</v>
+        <v>3.12</v>
       </c>
       <c r="U49" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V49" t="n">
         <v>1.02</v>
       </c>
       <c r="W49" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="X49" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AA49" t="n">
-        <v>4.2</v>
+        <v>3.58</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,16 +6799,16 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="AI49" t="n">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="AJ49" t="n">
-        <v>2</v>
+        <v>2.46</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45950.79166666666</v>
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="M50" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="N50" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="O50" t="n">
         <v>3.64</v>
@@ -6900,10 +6900,10 @@
         <v>2.57</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AA50" t="n">
         <v>4.75</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,83 +6990,83 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.56</v>
+        <v>1.85</v>
       </c>
       <c r="M51" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N51" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="O51" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="P51" t="n">
         <v>2.16</v>
       </c>
-      <c r="P51" t="n">
-        <v>2.04</v>
-      </c>
       <c r="Q51" t="n">
-        <v>5.8</v>
+        <v>4.06</v>
       </c>
       <c r="R51" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="S51" t="n">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="T51" t="n">
-        <v>3.16</v>
+        <v>2.5</v>
       </c>
       <c r="U51" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X51" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB51" t="n">
         <v>1.33</v>
       </c>
-      <c r="V51" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X51" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Z51" t="n">
+      <c r="AC51" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AI51" t="n">
         <v>1.73</v>
       </c>
-      <c r="AA51" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG51" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AJ51" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45950.89583333334</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="M52" t="n">
-        <v>3.25</v>
+        <v>3.53</v>
       </c>
       <c r="N52" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="O52" t="n">
-        <v>2.53</v>
+        <v>2.16</v>
       </c>
       <c r="P52" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.06</v>
+        <v>5.8</v>
       </c>
       <c r="R52" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W52" t="n">
         <v>1.31</v>
       </c>
-      <c r="S52" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T52" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U52" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.25</v>
-      </c>
       <c r="X52" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.97</v>
+        <v>1.76</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.66</v>
+        <v>2.08</v>
       </c>
       <c r="AD52" t="n">
-        <v>2.09</v>
+        <v>1.67</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,16 +7186,16 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.71</v>
+        <v>2.29</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AJ52" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45950.89583333334</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -933,22 +933,22 @@
         <v>3.2</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="O4" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="P4" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.88</v>
+        <v>3.72</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="S4" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="T4" t="n">
         <v>2.9</v>
@@ -957,28 +957,28 @@
         <v>1.35</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X4" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AD4" t="n">
         <v>1.95</v>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AI4" t="n">
         <v>1.81</v>
@@ -1194,19 +1194,19 @@
         <v>3.75</v>
       </c>
       <c r="O6" t="n">
-        <v>2.74</v>
+        <v>3.04</v>
       </c>
       <c r="P6" t="n">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="S6" t="n">
-        <v>2.58</v>
+        <v>2.31</v>
       </c>
       <c r="T6" t="n">
         <v>3.1</v>
@@ -1224,22 +1224,22 @@
         <v>2.83</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="Z6" t="n">
         <v>1.62</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.96</v>
+        <v>3.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AI6" t="n">
         <v>1.83</v>
@@ -1443,34 +1443,34 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="O8" t="n">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="P8" t="n">
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S8" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="T8" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="V8" t="n">
         <v>1</v>
@@ -1479,25 +1479,25 @@
         <v>1.26</v>
       </c>
       <c r="X8" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="Y8" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AA8" t="n">
         <v>3.28</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AI8" t="n">
         <v>1.99</v>
@@ -1581,16 +1581,16 @@
         <v>6.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.050000000000001</v>
+        <v>7</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S9" t="n">
         <v>2.9</v>
@@ -1602,13 +1602,13 @@
         <v>1.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
         <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="Y9" t="n">
         <v>1.88</v>
@@ -1617,16 +1617,16 @@
         <v>1.82</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AH9" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AI9" t="n">
         <v>1.4</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.35</v>
+        <v>2.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="N10" t="n">
-        <v>1.7</v>
+        <v>2.42</v>
       </c>
       <c r="O10" t="n">
-        <v>4.95</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>2.5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.51</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45950.41666666666</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45950.41666666666</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,22 +1959,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1992,16 +1992,16 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2032,10 +2032,10 @@
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45950.41666666666</v>
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="M13" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>4.31</v>
+        <v>4.1</v>
       </c>
       <c r="O13" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="P13" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
         <v>1.56</v>
       </c>
       <c r="S13" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="T13" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="U13" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="V13" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W13" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="X13" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.2</v>
+        <v>5.05</v>
       </c>
       <c r="AB13" t="n">
         <v>1.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AI13" t="n">
         <v>1.72</v>
@@ -2235,7 +2235,7 @@
         <v>3.58</v>
       </c>
       <c r="R14" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="S14" t="n">
         <v>2.44</v>
@@ -2244,16 +2244,16 @@
         <v>3.35</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W14" t="n">
         <v>1.39</v>
       </c>
       <c r="X14" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="Y14" t="n">
         <v>2.3</v>
@@ -2265,7 +2265,7 @@
         <v>4.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AC14" t="n">
         <v>1.98</v>
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
         <v>1.63</v>
@@ -2364,10 +2364,10 @@
         <v>6.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
         <v>2.65</v>
@@ -2397,10 +2397,10 @@
         <v>1.28</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.83</v>
+        <v>2.6</v>
       </c>
       <c r="AI15" t="n">
         <v>1.36</v>
@@ -2484,7 +2484,7 @@
         <v>3.14</v>
       </c>
       <c r="O16" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
         <v>1.85</v>
@@ -2493,7 +2493,7 @@
         <v>3.3</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S16" t="n">
         <v>2.3</v>
@@ -2502,16 +2502,16 @@
         <v>3.45</v>
       </c>
       <c r="U16" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V16" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="W16" t="n">
         <v>1.5</v>
       </c>
       <c r="X16" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Y16" t="n">
         <v>2.3</v>
@@ -2520,16 +2520,16 @@
         <v>1.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AC16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AI16" t="n">
         <v>1.9</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="O17" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.25</v>
+        <v>2.75</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="U17" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="V17" t="n">
         <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
-        <v>3.47</v>
+        <v>3.84</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.35</v>
+        <v>2.85</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.83</v>
+        <v>2.19</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2674,13 +2674,13 @@
         <v>1.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.12</v>
+        <v>1.39</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.95</v>
+        <v>1.89</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45950.5</v>
@@ -2742,22 +2742,22 @@
         <v>1.5</v>
       </c>
       <c r="O18" t="n">
-        <v>6.35</v>
+        <v>5.6</v>
       </c>
       <c r="P18" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="R18" t="n">
         <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="U18" t="n">
         <v>1.41</v>
@@ -2766,10 +2766,10 @@
         <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="X18" t="n">
-        <v>3.58</v>
+        <v>3.78</v>
       </c>
       <c r="Y18" t="n">
         <v>2.1</v>
@@ -2784,10 +2784,10 @@
         <v>1.31</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
         <v>1.1</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>4.2</v>
+        <v>1.55</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>2.22</v>
       </c>
       <c r="P19" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.75</v>
+        <v>4.28</v>
       </c>
       <c r="R19" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="U19" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="X19" t="n">
-        <v>3.7</v>
+        <v>3.56</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="Z19" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.44</v>
+        <v>2.16</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.89</v>
+        <v>2.95</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45950.5</v>
@@ -3009,7 +3009,7 @@
         <v>4.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="S20" t="n">
         <v>2.34</v>
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="M21" t="n">
         <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="O21" t="n">
         <v>4.18</v>
@@ -3135,13 +3135,13 @@
         <v>2.2</v>
       </c>
       <c r="Q21" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S21" t="n">
         <v>2.65</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.9</v>
       </c>
       <c r="T21" t="n">
         <v>2.65</v>
@@ -3153,7 +3153,7 @@
         <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="X21" t="n">
         <v>3.08</v>
@@ -3162,19 +3162,19 @@
         <v>2.04</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AA21" t="n">
         <v>3.34</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AI21" t="n">
         <v>2.4</v>
@@ -3258,7 +3258,7 @@
         <v>4.05</v>
       </c>
       <c r="O22" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="P22" t="n">
         <v>1.75</v>
@@ -3267,10 +3267,10 @@
         <v>4.72</v>
       </c>
       <c r="R22" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="S22" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="T22" t="n">
         <v>4.2</v>
@@ -3279,7 +3279,7 @@
         <v>1.16</v>
       </c>
       <c r="V22" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="W22" t="n">
         <v>1.55</v>
@@ -3294,13 +3294,13 @@
         <v>1.28</v>
       </c>
       <c r="AA22" t="n">
-        <v>6.15</v>
+        <v>6.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.63</v>
+        <v>2.46</v>
       </c>
       <c r="AD22" t="n">
         <v>1.48</v>
@@ -3316,7 +3316,7 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AH22" t="n">
         <v>1.69</v>
@@ -3387,25 +3387,25 @@
         <v>3.35</v>
       </c>
       <c r="O23" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="P23" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="Q23" t="n">
         <v>5.2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S23" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T23" t="n">
         <v>3.58</v>
       </c>
       <c r="U23" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="V23" t="n">
         <v>1.04</v>
@@ -3423,16 +3423,16 @@
         <v>1.46</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="AB23" t="n">
         <v>1.11</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AH23" t="n">
         <v>1.87</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.3</v>
+        <v>1.69</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>3.69</v>
       </c>
       <c r="N24" t="n">
-        <v>3.07</v>
+        <v>3.89</v>
       </c>
       <c r="O24" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="P24" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH24" t="n">
         <v>2</v>
       </c>
-      <c r="Q24" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.59</v>
-      </c>
       <c r="AI24" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45950.58333333334</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="O25" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="P25" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.02</v>
+        <v>3.8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T25" t="n">
         <v>2.88</v>
       </c>
-      <c r="T25" t="n">
-        <v>2.74</v>
-      </c>
       <c r="U25" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="V25" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="X25" t="n">
-        <v>3.45</v>
+        <v>2.94</v>
       </c>
       <c r="Y25" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AI25" t="n">
         <v>1.85</v>
       </c>
-      <c r="Z25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>2</v>
-      </c>
       <c r="AJ25" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45950.58333333334</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="M26" t="n">
-        <v>3.69</v>
+        <v>3.33</v>
       </c>
       <c r="N26" t="n">
-        <v>3.89</v>
+        <v>3.63</v>
       </c>
       <c r="O26" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="P26" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="Q26" t="n">
         <v>4</v>
       </c>
       <c r="R26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
         <v>1.26</v>
       </c>
-      <c r="S26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X26" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AH26" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45950.58333333334</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,62 +3894,62 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.4</v>
+        <v>2.62</v>
       </c>
       <c r="M27" t="n">
-        <v>3.99</v>
+        <v>3.42</v>
       </c>
       <c r="N27" t="n">
-        <v>1.46</v>
+        <v>2.37</v>
       </c>
       <c r="O27" t="n">
-        <v>5.62</v>
+        <v>2.93</v>
       </c>
       <c r="P27" t="n">
-        <v>2.29</v>
+        <v>2.11</v>
       </c>
       <c r="Q27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD27" t="n">
         <v>2</v>
       </c>
-      <c r="R27" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X27" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AE27" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.1</v>
+        <v>1.37</v>
       </c>
       <c r="AI27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.45</v>
+        <v>1.9</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45950.58333333334</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N28" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="O28" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="P28" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.63</v>
+        <v>4.33</v>
       </c>
       <c r="R28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W28" t="n">
         <v>1.41</v>
       </c>
-      <c r="S28" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.28</v>
-      </c>
       <c r="X28" t="n">
-        <v>3.25</v>
+        <v>2.74</v>
       </c>
       <c r="Y28" t="n">
         <v>2.05</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4093,13 +4093,13 @@
         <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45950.58333333334</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="M29" t="n">
-        <v>3.33</v>
+        <v>3.36</v>
       </c>
       <c r="N29" t="n">
-        <v>3.63</v>
+        <v>3.67</v>
       </c>
       <c r="O29" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="P29" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>4.67</v>
       </c>
       <c r="R29" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S29" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="T29" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="U29" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W29" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="X29" t="n">
-        <v>3.48</v>
+        <v>3.18</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD29" t="n">
         <v>1.85</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4222,13 +4222,13 @@
         <v>1.26</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45950.58333333334</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.73</v>
+        <v>5.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.25</v>
+        <v>3.99</v>
       </c>
       <c r="N30" t="n">
-        <v>4.3</v>
+        <v>1.46</v>
       </c>
       <c r="O30" t="n">
-        <v>2.62</v>
+        <v>5.62</v>
       </c>
       <c r="P30" t="n">
-        <v>1.92</v>
+        <v>2.53</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.33</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="S30" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="T30" t="n">
-        <v>3.2</v>
+        <v>2.42</v>
       </c>
       <c r="U30" t="n">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="V30" t="n">
         <v>1.03</v>
       </c>
       <c r="W30" t="n">
-        <v>1.41</v>
+        <v>1.17</v>
       </c>
       <c r="X30" t="n">
-        <v>2.7</v>
+        <v>4.25</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.17</v>
+        <v>1.47</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.94</v>
+        <v>1.74</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.78</v>
+        <v>1.11</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.74</v>
+        <v>3</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.52</v>
+        <v>1.45</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45950.58333333334</v>
@@ -4410,34 +4410,34 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="M31" t="n">
-        <v>3.52</v>
+        <v>3.26</v>
       </c>
       <c r="N31" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P31" t="n">
-        <v>2.17</v>
+        <v>2.11</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="R31" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S31" t="n">
         <v>3.1</v>
       </c>
       <c r="T31" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="U31" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="V31" t="n">
         <v>1.04</v>
@@ -4446,13 +4446,13 @@
         <v>1.22</v>
       </c>
       <c r="X31" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AA31" t="n">
         <v>3</v>
@@ -4461,7 +4461,7 @@
         <v>1.33</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AD31" t="n">
         <v>2.15</v>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AI31" t="n">
         <v>2</v>
@@ -4548,34 +4548,34 @@
         <v>1.9</v>
       </c>
       <c r="O32" t="n">
-        <v>4.25</v>
+        <v>4.85</v>
       </c>
       <c r="P32" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="R32" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="S32" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="T32" t="n">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="U32" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="V32" t="n">
         <v>1.04</v>
       </c>
       <c r="W32" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X32" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="Y32" t="n">
         <v>1.94</v>
@@ -4584,16 +4584,16 @@
         <v>1.76</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AC32" t="n">
         <v>2.05</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AI32" t="n">
         <v>2.6</v>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5.5</v>
+        <v>2.22</v>
       </c>
       <c r="M33" t="n">
-        <v>4.45</v>
+        <v>3.45</v>
       </c>
       <c r="N33" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
         <v>1.41</v>
       </c>
-      <c r="O33" t="n">
-        <v>5</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S33" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U33" t="n">
+      <c r="AH33" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI33" t="n">
         <v>1.8</v>
       </c>
-      <c r="V33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X33" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AJ33" t="n">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45950.625</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="M34" t="n">
         <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="O34" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="P34" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,16 +4864,16 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45950.625</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.07</v>
+        <v>6.07</v>
       </c>
       <c r="M35" t="n">
-        <v>3.75</v>
+        <v>5.35</v>
       </c>
       <c r="N35" t="n">
-        <v>3.15</v>
+        <v>1.41</v>
       </c>
       <c r="O35" t="n">
-        <v>2.55</v>
+        <v>5.25</v>
       </c>
       <c r="P35" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.3</v>
+        <v>1.84</v>
       </c>
       <c r="R35" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="T35" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="U35" t="n">
-        <v>1.66</v>
+        <v>1.88</v>
       </c>
       <c r="V35" t="n">
         <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="X35" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.6</v>
+        <v>3.33</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.19</v>
+        <v>1.89</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,16 +4993,16 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.68</v>
+        <v>1.08</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.77</v>
+        <v>2.75</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45950.625</v>
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.64</v>
+        <v>2.79</v>
       </c>
       <c r="M36" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="N36" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
       </c>
       <c r="P36" t="n">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="Q36" t="n">
         <v>2.7</v>
       </c>
       <c r="R36" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S36" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="T36" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="U36" t="n">
         <v>1.6</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W36" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="X36" t="n">
-        <v>5.22</v>
+        <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z36" t="n">
         <v>2.4</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC36" t="n">
         <v>1.44</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AI36" t="n">
         <v>1.92</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.85</v>
+        <v>2.1</v>
       </c>
       <c r="M37" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N37" t="n">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="O37" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="P37" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X37" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ37" t="n">
         <v>2.1</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.95</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45950.625</v>
@@ -5322,19 +5322,19 @@
         <v>3.77</v>
       </c>
       <c r="O38" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="P38" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="R38" t="n">
         <v>1.62</v>
       </c>
       <c r="S38" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="T38" t="n">
         <v>3.75</v>
@@ -5343,7 +5343,7 @@
         <v>1.21</v>
       </c>
       <c r="V38" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W38" t="n">
         <v>1.53</v>
@@ -5358,10 +5358,10 @@
         <v>1.53</v>
       </c>
       <c r="AA38" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AC38" t="n">
         <v>2.2</v>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH38" t="n">
         <v>1.65</v>
@@ -5451,7 +5451,7 @@
         <v>2.13</v>
       </c>
       <c r="O39" t="n">
-        <v>4.05</v>
+        <v>4.22</v>
       </c>
       <c r="P39" t="n">
         <v>1.94</v>
@@ -5460,16 +5460,16 @@
         <v>2.82</v>
       </c>
       <c r="R39" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S39" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="T39" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="U39" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V39" t="n">
         <v>1.04</v>
@@ -5487,7 +5487,7 @@
         <v>1.6</v>
       </c>
       <c r="AA39" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AB39" t="n">
         <v>1.19</v>
@@ -5496,7 +5496,7 @@
         <v>1.9</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5580,25 +5580,25 @@
         <v>2</v>
       </c>
       <c r="O40" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="P40" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.63</v>
+        <v>2.71</v>
       </c>
       <c r="R40" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="S40" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="T40" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U40" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="V40" t="n">
         <v>1.05</v>
@@ -5622,10 +5622,10 @@
         <v>1.17</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AH40" t="n">
         <v>1.16</v>
@@ -5712,10 +5712,10 @@
         <v>3.4</v>
       </c>
       <c r="P41" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.16</v>
+        <v>3</v>
       </c>
       <c r="R41" t="n">
         <v>1.52</v>
@@ -5724,7 +5724,7 @@
         <v>2.63</v>
       </c>
       <c r="T41" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="U41" t="n">
         <v>1.33</v>
@@ -5733,10 +5733,10 @@
         <v>1.03</v>
       </c>
       <c r="W41" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X41" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Y41" t="n">
         <v>2.15</v>
@@ -5751,10 +5751,10 @@
         <v>1.2</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AI41" t="n">
         <v>2.2</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="M42" t="n">
-        <v>3.01</v>
+        <v>3.45</v>
       </c>
       <c r="N42" t="n">
-        <v>2.83</v>
+        <v>4.33</v>
       </c>
       <c r="O42" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="P42" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="R42" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S42" t="n">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="T42" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="U42" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V42" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="W42" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="X42" t="n">
-        <v>2.94</v>
+        <v>3.18</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.75</v>
+        <v>3.38</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,16 +5896,16 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.54</v>
+        <v>2.06</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AJ42" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45950.65625</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="M43" t="n">
-        <v>3.45</v>
+        <v>3.01</v>
       </c>
       <c r="N43" t="n">
-        <v>4.33</v>
+        <v>2.83</v>
       </c>
       <c r="O43" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="P43" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="R43" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S43" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="T43" t="n">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="U43" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V43" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W43" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="X43" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.38</v>
+        <v>3.75</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AC43" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,16 +6025,16 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.14</v>
+        <v>1.53</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AJ43" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45950.65625</v>
@@ -6105,13 +6105,13 @@
         <v>3.4</v>
       </c>
       <c r="R44" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="T44" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="U44" t="n">
         <v>1.44</v>
@@ -6120,7 +6120,7 @@
         <v>1</v>
       </c>
       <c r="W44" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X44" t="n">
         <v>3.4</v>
@@ -6138,10 +6138,10 @@
         <v>1.3</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AI44" t="n">
         <v>1.9</v>
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="M45" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="N45" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="O45" t="n">
         <v>2.9</v>
@@ -6231,16 +6231,16 @@
         <v>1.91</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="R45" t="n">
         <v>1.57</v>
       </c>
       <c r="S45" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="T45" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U45" t="n">
         <v>1.3</v>
@@ -6255,13 +6255,13 @@
         <v>2.6</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AA45" t="n">
-        <v>4.45</v>
+        <v>4.7</v>
       </c>
       <c r="AB45" t="n">
         <v>1.17</v>
@@ -6270,7 +6270,7 @@
         <v>2</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AI45" t="n">
         <v>1.92</v>
@@ -6354,10 +6354,10 @@
         <v>1.86</v>
       </c>
       <c r="O46" t="n">
-        <v>3.54</v>
+        <v>3.44</v>
       </c>
       <c r="P46" t="n">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="Q46" t="n">
         <v>2.35</v>
@@ -6366,19 +6366,19 @@
         <v>1.18</v>
       </c>
       <c r="S46" t="n">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="T46" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="U46" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V46" t="n">
         <v>1.01</v>
       </c>
       <c r="W46" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X46" t="n">
         <v>5.95</v>
@@ -6396,10 +6396,10 @@
         <v>1.8</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AI46" t="n">
         <v>2.15</v>
@@ -6474,62 +6474,62 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="M47" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N47" t="n">
-        <v>4.85</v>
+        <v>4.15</v>
       </c>
       <c r="O47" t="n">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="P47" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="Q47" t="n">
-        <v>6.07</v>
+        <v>5</v>
       </c>
       <c r="R47" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S47" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T47" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="U47" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V47" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W47" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X47" t="n">
-        <v>2.92</v>
+        <v>2.69</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="Z47" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD47" t="n">
         <v>1.67</v>
       </c>
-      <c r="AA47" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AE47" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AI47" t="n">
         <v>1.6</v>
@@ -6612,34 +6612,34 @@
         <v>2.51</v>
       </c>
       <c r="O48" t="n">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="P48" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
       <c r="R48" t="n">
         <v>1.44</v>
       </c>
       <c r="S48" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="T48" t="n">
         <v>3.22</v>
       </c>
       <c r="U48" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V48" t="n">
         <v>1.02</v>
       </c>
       <c r="W48" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="X48" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="Y48" t="n">
         <v>2.25</v>
@@ -6648,16 +6648,16 @@
         <v>1.65</v>
       </c>
       <c r="AA48" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AI48" t="n">
         <v>2.1</v>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6741,34 +6741,34 @@
         <v>3.53</v>
       </c>
       <c r="O49" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P49" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Q49" t="n">
         <v>4</v>
       </c>
       <c r="R49" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S49" t="n">
         <v>2.56</v>
       </c>
       <c r="T49" t="n">
-        <v>3.12</v>
+        <v>2.99</v>
       </c>
       <c r="U49" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V49" t="n">
         <v>1.02</v>
       </c>
       <c r="W49" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="X49" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="Y49" t="n">
         <v>2.25</v>
@@ -6777,16 +6777,16 @@
         <v>1.58</v>
       </c>
       <c r="AA49" t="n">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AC49" t="n">
         <v>1.83</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>2.46</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45950.79166666666</v>
+        <v>45950.8125</v>
       </c>
     </row>
     <row r="50">
@@ -6870,19 +6870,19 @@
         <v>2.67</v>
       </c>
       <c r="O50" t="n">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="P50" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="R50" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S50" t="n">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="T50" t="n">
         <v>3.34</v>
@@ -6906,13 +6906,13 @@
         <v>1.6</v>
       </c>
       <c r="AA50" t="n">
-        <v>4.75</v>
+        <v>4.3</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AD50" t="n">
         <v>1.76</v>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AI50" t="n">
         <v>2.2</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,61 +6990,61 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="M51" t="n">
-        <v>3.25</v>
+        <v>3.53</v>
       </c>
       <c r="N51" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="O51" t="n">
-        <v>2.53</v>
+        <v>2.13</v>
       </c>
       <c r="P51" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.06</v>
+        <v>5.4</v>
       </c>
       <c r="R51" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="S51" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="T51" t="n">
-        <v>2.5</v>
+        <v>3.16</v>
       </c>
       <c r="U51" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="V51" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W51" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X51" t="n">
-        <v>3.7</v>
+        <v>3.08</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.97</v>
+        <v>1.76</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.8</v>
+        <v>3.68</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.66</v>
+        <v>2.05</v>
       </c>
       <c r="AD51" t="n">
-        <v>2.09</v>
+        <v>1.7</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
@@ -7057,16 +7057,16 @@
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH51" t="n">
-        <v>1.71</v>
+        <v>2.33</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AJ51" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45950.89583333334</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="M52" t="n">
-        <v>3.53</v>
+        <v>3.6</v>
       </c>
       <c r="N52" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O52" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="P52" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q52" t="n">
         <v>4.2</v>
       </c>
-      <c r="O52" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="P52" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>5.8</v>
-      </c>
       <c r="R52" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="S52" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="T52" t="n">
-        <v>3.16</v>
+        <v>2.72</v>
       </c>
       <c r="U52" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V52" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="W52" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="X52" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AA52" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AC52" t="n">
-        <v>2.08</v>
+        <v>1.73</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,16 +7186,16 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AH52" t="n">
-        <v>2.29</v>
+        <v>1.75</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AJ52" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45950.89583333334</v>

--- a/jogos_2025-10-20.xlsx
+++ b/jogos_2025-10-20.xlsx
@@ -913,17 +913,17 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -990,7 +990,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AG4" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>6.02</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45950.29166666666</v>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1194,68 +1194,68 @@
         <v>3.75</v>
       </c>
       <c r="O6" t="n">
-        <v>3.04</v>
+        <v>2.68</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.3</v>
+        <v>5.05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="T6" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
         <v>1.33</v>
       </c>
-      <c r="X6" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH6" t="n">
-        <v>1.51</v>
+        <v>1.7</v>
       </c>
       <c r="AI6" t="n">
         <v>1.83</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1443,28 +1443,28 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S8" t="n">
         <v>2.73</v>
-      </c>
-      <c r="M8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.69</v>
       </c>
       <c r="T8" t="n">
         <v>2.85</v>
@@ -1473,7 +1473,7 @@
         <v>1.35</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
         <v>1.26</v>
@@ -1482,19 +1482,19 @@
         <v>3.22</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AA8" t="n">
         <v>3.28</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AD8" t="n">
         <v>2</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AI8" t="n">
         <v>1.99</v>
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="M9" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="N9" t="n">
-        <v>6.2</v>
+        <v>10.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="P9" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="Q9" t="n">
         <v>7</v>
       </c>
       <c r="R9" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="T9" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
         <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.12</v>
+        <v>2.27</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.85</v>
+        <v>3.18</v>
       </c>
       <c r="AI9" t="n">
         <v>1.4</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.7</v>
+        <v>1.85</v>
       </c>
       <c r="M10" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="N10" t="n">
-        <v>2.42</v>
+        <v>4.4</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>2.61</v>
       </c>
       <c r="P10" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>5.24</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="X10" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45950.41666666666</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45950.41666666666</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45950.41666666666</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.86</v>
+        <v>4.35</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.62</v>
+        <v>5.6</v>
       </c>
       <c r="P13" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>2.04</v>
       </c>
       <c r="R13" t="n">
-        <v>1.56</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
-        <v>2.28</v>
+        <v>3.06</v>
       </c>
       <c r="T13" t="n">
-        <v>3.52</v>
+        <v>2.56</v>
       </c>
       <c r="U13" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="V13" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="X13" t="n">
-        <v>2.3</v>
+        <v>3.84</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.65</v>
+        <v>1.73</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.42</v>
+        <v>1.97</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.05</v>
+        <v>2.74</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.1</v>
+        <v>1.35</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.25</v>
+        <v>1.76</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.56</v>
+        <v>1.89</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,